--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,8287 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122427605</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562687</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7039594</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122428692</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562502</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039635</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122429855</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562619</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039840</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122429005</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562522</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039596</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122427566</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562663</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039574</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122428124</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562630</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039565</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122428645</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562509</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039629</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122425310</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562650</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7039868</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122427407</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562761</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7039655</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122430183</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562911</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7039598</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122427459</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98185</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562755</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7039631</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122426079</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562676</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7039760</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122426422</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562642</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7039716</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122425397</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>562662</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7039854</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122430036</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79728</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>562621</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7039854</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122428034</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57527</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>562674</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7039543</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122429000</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>562984</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7039447</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122429588</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>562549</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7039854</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122428148</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>562707</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7039456</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122430816</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>562845</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7039809</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122425855</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90807</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>562731</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7039827</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122427401</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>562674</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7039653</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122428711</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>562889</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7039463</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122426080</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>562743</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7039807</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122427953</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>562661</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7039580</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122425700</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562678</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7039813</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122425516</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>562706</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7039810</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122429240</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78382</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>562497</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7039642</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122428307</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>562557</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7039552</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122425617</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>562648</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7039837</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122429056</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>562996</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7039422</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122426220</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>562671</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7039729</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122429992</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>562620</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7039839</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122430397</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562890</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7039728</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122430000</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>562623</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7039843</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122425414</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>562678</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7039855</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122427418</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>562680</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7039626</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122429819</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>562600</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7039877</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122425703</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>562654</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7039819</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122425278</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>562673</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7039869</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122427743</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>562670</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7039613</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122427618</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>562674</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7039582</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122428173</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>562701</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7039441</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122425284</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>562657</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7039870</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122425242</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>562659</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7039871</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122425536</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>562710</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7039834</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122425754</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>562652</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7039805</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122428693</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>562933</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7039394</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122430062</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>562624</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7039856</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122429969</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>562604</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7039850</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122430719</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>562835</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7039750</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122429596</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>562565</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7039844</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122425405</v>
+      </c>
+      <c r="B57" t="n">
+        <v>74747</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>562648</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7039865</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122425331</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>562650</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7039856</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122426187</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>562759</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7039787</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122425191</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>562649</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7039883</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122427703</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>562784</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7039590</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122428074</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>562763</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7039478</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122425780</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>562725</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7039812</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122425539</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>562651</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7039827</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122425544</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78382</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>562672</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7039840</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122426059</v>
+      </c>
+      <c r="B66" t="n">
+        <v>82433</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>562673</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7039763</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>122429998</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>562999</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7039523</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122429996</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>562622</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7039843</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122427473</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>562684</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7039617</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122430274</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>562903</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7039649</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122425328</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>562678</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7039868</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122430780</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>562903</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7039567</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122428796</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>563001</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7039421</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122427985</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>562695</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7039574</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122426351</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>562771</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7039744</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122427824</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>562770</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7039566</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122427626</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78382</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>562773</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7039605</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122427645</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>562693</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7039587</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427605</v>
+        <v>122427626</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>78382</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,39 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562687</v>
+        <v>562773</v>
       </c>
       <c r="R5" t="n">
-        <v>7039594</v>
+        <v>7039605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,19 +1123,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122428692</v>
+        <v>122427618</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1181,7 +1171,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1190,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562502</v>
+        <v>562674</v>
       </c>
       <c r="R6" t="n">
-        <v>7039635</v>
+        <v>7039582</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1230,7 +1220,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429855</v>
+        <v>122427824</v>
       </c>
       <c r="B7" t="n">
         <v>79727</v>
@@ -1297,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562619</v>
+        <v>562770</v>
       </c>
       <c r="R7" t="n">
-        <v>7039840</v>
+        <v>7039566</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,9 +1320,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429005</v>
+        <v>122429000</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,42 +1375,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562522</v>
+        <v>562984</v>
       </c>
       <c r="R8" t="n">
-        <v>7039596</v>
+        <v>7039447</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,14 +1432,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,19 +1459,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122427566</v>
+        <v>122427418</v>
       </c>
       <c r="B9" t="n">
         <v>79727</v>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562663</v>
+        <v>562680</v>
       </c>
       <c r="R9" t="n">
-        <v>7039574</v>
+        <v>7039626</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428124</v>
+        <v>122425855</v>
       </c>
       <c r="B10" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562630</v>
+        <v>562731</v>
       </c>
       <c r="R10" t="n">
-        <v>7039565</v>
+        <v>7039827</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,9 +1646,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,22 +1673,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122428645</v>
+        <v>122426220</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,34 +1701,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562509</v>
+        <v>562671</v>
       </c>
       <c r="R11" t="n">
-        <v>7039629</v>
+        <v>7039729</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1751,6 +1766,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122425310</v>
+        <v>122426079</v>
       </c>
       <c r="B12" t="n">
         <v>78646</v>
@@ -1817,13 +1837,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562650</v>
+        <v>562676</v>
       </c>
       <c r="R12" t="n">
-        <v>7039868</v>
+        <v>7039760</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1850,19 +1870,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122427407</v>
+        <v>122430000</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,42 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562761</v>
+        <v>562623</v>
       </c>
       <c r="R13" t="n">
-        <v>7039655</v>
+        <v>7039843</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,24 +1972,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,22 +1989,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122430183</v>
+        <v>122425405</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>74747</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,42 +2017,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562911</v>
+        <v>562648</v>
       </c>
       <c r="R14" t="n">
-        <v>7039598</v>
+        <v>7039865</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,24 +2074,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,22 +2091,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122427459</v>
+        <v>122425278</v>
       </c>
       <c r="B15" t="n">
-        <v>98185</v>
+        <v>79727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,52 +2115,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562755</v>
+        <v>562673</v>
       </c>
       <c r="R15" t="n">
-        <v>7039631</v>
+        <v>7039869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,22 +2203,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122426079</v>
+        <v>122428692</v>
       </c>
       <c r="B16" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,34 +2231,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562676</v>
+        <v>562502</v>
       </c>
       <c r="R16" t="n">
-        <v>7039760</v>
+        <v>7039635</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2335,6 +2296,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122426422</v>
+        <v>122429596</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,42 +2343,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562642</v>
+        <v>562565</v>
       </c>
       <c r="R17" t="n">
-        <v>7039716</v>
+        <v>7039844</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2439,24 +2400,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,22 +2417,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122425397</v>
+        <v>122427645</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,39 +2445,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562662</v>
+        <v>562693</v>
       </c>
       <c r="R18" t="n">
-        <v>7039854</v>
+        <v>7039587</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,7 +2504,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,12 +2514,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,22 +2529,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122430036</v>
+        <v>122426351</v>
       </c>
       <c r="B19" t="n">
-        <v>79728</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2621,37 +2557,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562621</v>
+        <v>562771</v>
       </c>
       <c r="R19" t="n">
-        <v>7039854</v>
+        <v>7039744</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2678,9 +2619,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,22 +2651,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122428034</v>
+        <v>122429005</v>
       </c>
       <c r="B20" t="n">
-        <v>57527</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,31 +2679,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2756,13 +2708,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562674</v>
+        <v>562522</v>
       </c>
       <c r="R20" t="n">
-        <v>7039543</v>
+        <v>7039596</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2789,19 +2741,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,22 +2763,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122429000</v>
+        <v>122429334</v>
       </c>
       <c r="B21" t="n">
-        <v>79727</v>
+        <v>78382</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2844,37 +2791,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562984</v>
+        <v>562497</v>
       </c>
       <c r="R21" t="n">
-        <v>7039447</v>
+        <v>7039642</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2901,19 +2848,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,22 +2865,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122429588</v>
+        <v>122430183</v>
       </c>
       <c r="B22" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,37 +2893,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562549</v>
+        <v>562911</v>
       </c>
       <c r="R22" t="n">
-        <v>7039854</v>
+        <v>7039598</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3013,9 +2955,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,19 +2987,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122428148</v>
+        <v>122425328</v>
       </c>
       <c r="B23" t="n">
         <v>79727</v>
@@ -3078,14 +3035,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562707</v>
+        <v>562678</v>
       </c>
       <c r="R23" t="n">
-        <v>7039456</v>
+        <v>7039868</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3074,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3084,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,7 +3111,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122430816</v>
+        <v>122427985</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3199,10 +3156,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562845</v>
+        <v>562695</v>
       </c>
       <c r="R24" t="n">
-        <v>7039809</v>
+        <v>7039574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3191,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3201,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,22 +3221,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122425855</v>
+        <v>122425754</v>
       </c>
       <c r="B25" t="n">
-        <v>90807</v>
+        <v>57390</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,37 +3249,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562731</v>
+        <v>562652</v>
       </c>
       <c r="R25" t="n">
-        <v>7039827</v>
+        <v>7039805</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3344,19 +3311,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:07</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,22 +3333,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122427401</v>
+        <v>122425703</v>
       </c>
       <c r="B26" t="n">
-        <v>78646</v>
+        <v>57390</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3399,34 +3361,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562674</v>
+        <v>562654</v>
       </c>
       <c r="R26" t="n">
-        <v>7039653</v>
+        <v>7039819</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3485,10 +3452,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122428711</v>
+        <v>122425780</v>
       </c>
       <c r="B27" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,39 +3468,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562889</v>
+        <v>562725</v>
       </c>
       <c r="R27" t="n">
-        <v>7039463</v>
+        <v>7039812</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,7 +3527,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,12 +3537,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3595,22 +3557,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122426080</v>
+        <v>122428034</v>
       </c>
       <c r="B28" t="n">
-        <v>79727</v>
+        <v>57527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,34 +3585,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562743</v>
+        <v>562674</v>
       </c>
       <c r="R28" t="n">
-        <v>7039807</v>
+        <v>7039543</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3682,7 +3653,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3663,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,10 +3690,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122427953</v>
+        <v>122429998</v>
       </c>
       <c r="B29" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3735,37 +3706,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562661</v>
+        <v>562999</v>
       </c>
       <c r="R29" t="n">
-        <v>7039580</v>
+        <v>7039523</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,9 +3768,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,19 +3800,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122425700</v>
+        <v>122430397</v>
       </c>
       <c r="B30" t="n">
         <v>57374</v>
@@ -3857,7 +3848,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3866,10 +3857,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562678</v>
+        <v>562890</v>
       </c>
       <c r="R30" t="n">
-        <v>7039813</v>
+        <v>7039728</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,7 +3892,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,12 +3902,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425516</v>
+        <v>122425414</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -3988,10 +3979,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562706</v>
+        <v>562678</v>
       </c>
       <c r="R31" t="n">
-        <v>7039810</v>
+        <v>7039855</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +4014,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4024,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4065,10 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122429240</v>
+        <v>122428796</v>
       </c>
       <c r="B32" t="n">
-        <v>78382</v>
+        <v>57374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4081,37 +4072,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562497</v>
+        <v>563001</v>
       </c>
       <c r="R32" t="n">
-        <v>7039642</v>
+        <v>7039421</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4138,9 +4134,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4155,19 +4166,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122428307</v>
+        <v>122429056</v>
       </c>
       <c r="B33" t="n">
         <v>57374</v>
@@ -4208,17 +4219,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562557</v>
+        <v>562996</v>
       </c>
       <c r="R33" t="n">
-        <v>7039552</v>
+        <v>7039422</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4245,14 +4256,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4267,22 +4288,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122425617</v>
+        <v>122429969</v>
       </c>
       <c r="B34" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4295,21 +4316,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4319,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562648</v>
+        <v>562604</v>
       </c>
       <c r="R34" t="n">
-        <v>7039837</v>
+        <v>7039850</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4381,7 +4402,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122429056</v>
+        <v>122426422</v>
       </c>
       <c r="B35" t="n">
         <v>57374</v>
@@ -4417,19 +4438,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562996</v>
+        <v>562642</v>
       </c>
       <c r="R35" t="n">
-        <v>7039422</v>
+        <v>7039716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,7 +4482,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,12 +4492,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4503,10 +4524,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122426220</v>
+        <v>122425331</v>
       </c>
       <c r="B36" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4519,39 +4540,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562671</v>
+        <v>562650</v>
       </c>
       <c r="R36" t="n">
-        <v>7039729</v>
+        <v>7039856</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4584,11 +4600,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,7 +4626,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122429992</v>
+        <v>122428148</v>
       </c>
       <c r="B37" t="n">
         <v>79727</v>
@@ -4655,13 +4666,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562620</v>
+        <v>562707</v>
       </c>
       <c r="R37" t="n">
-        <v>7039839</v>
+        <v>7039456</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4688,9 +4699,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4705,22 +4726,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122430397</v>
+        <v>122429855</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4733,42 +4754,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562890</v>
+        <v>562619</v>
       </c>
       <c r="R38" t="n">
-        <v>7039728</v>
+        <v>7039840</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4795,24 +4811,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4827,22 +4828,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122430000</v>
+        <v>122427459</v>
       </c>
       <c r="B39" t="n">
-        <v>79727</v>
+        <v>98185</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4851,41 +4852,55 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562623</v>
+        <v>562755</v>
       </c>
       <c r="R39" t="n">
-        <v>7039843</v>
+        <v>7039631</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4912,9 +4927,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4929,22 +4954,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122425414</v>
+        <v>122426187</v>
       </c>
       <c r="B40" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,39 +4982,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562678</v>
+        <v>562759</v>
       </c>
       <c r="R40" t="n">
-        <v>7039855</v>
+        <v>7039787</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5021,7 +5041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5031,12 +5051,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5063,7 +5078,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122427418</v>
+        <v>122425284</v>
       </c>
       <c r="B41" t="n">
         <v>79727</v>
@@ -5099,14 +5114,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562680</v>
+        <v>562657</v>
       </c>
       <c r="R41" t="n">
-        <v>7039626</v>
+        <v>7039870</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5165,10 +5180,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122429819</v>
+        <v>122427953</v>
       </c>
       <c r="B42" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5181,21 +5196,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5205,10 +5220,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562600</v>
+        <v>562661</v>
       </c>
       <c r="R42" t="n">
-        <v>7039877</v>
+        <v>7039580</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5267,10 +5282,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122425703</v>
+        <v>122427605</v>
       </c>
       <c r="B43" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5283,16 +5298,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5303,7 +5318,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5312,13 +5327,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562654</v>
+        <v>562687</v>
       </c>
       <c r="R43" t="n">
-        <v>7039819</v>
+        <v>7039594</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5345,9 +5360,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5362,22 +5392,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122425278</v>
+        <v>122425397</v>
       </c>
       <c r="B44" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5390,34 +5420,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562673</v>
+        <v>562662</v>
       </c>
       <c r="R44" t="n">
-        <v>7039869</v>
+        <v>7039854</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5449,7 +5484,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5459,7 +5494,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5474,22 +5514,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122427743</v>
+        <v>122425539</v>
       </c>
       <c r="B45" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5502,42 +5542,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562670</v>
+        <v>562651</v>
       </c>
       <c r="R45" t="n">
-        <v>7039613</v>
+        <v>7039827</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5564,24 +5599,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5596,22 +5616,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122427618</v>
+        <v>122428124</v>
       </c>
       <c r="B46" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5624,39 +5644,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562674</v>
+        <v>562630</v>
       </c>
       <c r="R46" t="n">
-        <v>7039582</v>
+        <v>7039565</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5689,11 +5704,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5720,10 +5730,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428173</v>
+        <v>122427401</v>
       </c>
       <c r="B47" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5736,42 +5746,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562701</v>
+        <v>562674</v>
       </c>
       <c r="R47" t="n">
-        <v>7039441</v>
+        <v>7039653</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5798,24 +5803,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,22 +5820,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122425284</v>
+        <v>122426059</v>
       </c>
       <c r="B48" t="n">
-        <v>79727</v>
+        <v>82433</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5858,34 +5848,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562657</v>
+        <v>562673</v>
       </c>
       <c r="R48" t="n">
-        <v>7039870</v>
+        <v>7039763</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5944,7 +5934,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122425242</v>
+        <v>122430062</v>
       </c>
       <c r="B49" t="n">
         <v>79727</v>
@@ -5980,14 +5970,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562659</v>
+        <v>562624</v>
       </c>
       <c r="R49" t="n">
-        <v>7039871</v>
+        <v>7039856</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6046,10 +6036,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122425536</v>
+        <v>122429819</v>
       </c>
       <c r="B50" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6062,21 +6052,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6086,13 +6076,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562710</v>
+        <v>562600</v>
       </c>
       <c r="R50" t="n">
-        <v>7039834</v>
+        <v>7039877</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6119,19 +6109,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6146,22 +6126,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122425754</v>
+        <v>122425516</v>
       </c>
       <c r="B51" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6174,16 +6154,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6194,7 +6174,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6203,13 +6183,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562652</v>
+        <v>562706</v>
       </c>
       <c r="R51" t="n">
-        <v>7039805</v>
+        <v>7039810</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6236,14 +6216,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,22 +6248,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122428693</v>
+        <v>122425536</v>
       </c>
       <c r="B52" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6286,39 +6276,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562933</v>
+        <v>562710</v>
       </c>
       <c r="R52" t="n">
-        <v>7039394</v>
+        <v>7039834</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6350,7 +6335,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6360,12 +6345,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6392,10 +6372,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122430062</v>
+        <v>122427407</v>
       </c>
       <c r="B53" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6408,37 +6388,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562624</v>
+        <v>562761</v>
       </c>
       <c r="R53" t="n">
-        <v>7039856</v>
+        <v>7039655</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6465,9 +6450,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,22 +6482,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122429969</v>
+        <v>122425544</v>
       </c>
       <c r="B54" t="n">
-        <v>78646</v>
+        <v>78382</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6534,13 +6534,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562604</v>
+        <v>562672</v>
       </c>
       <c r="R54" t="n">
-        <v>7039850</v>
+        <v>7039840</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6567,9 +6567,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6584,19 +6594,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122430719</v>
+        <v>122428693</v>
       </c>
       <c r="B55" t="n">
         <v>57374</v>
@@ -6637,14 +6647,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562835</v>
+        <v>562933</v>
       </c>
       <c r="R55" t="n">
-        <v>7039750</v>
+        <v>7039394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6676,7 +6686,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6686,7 +6696,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6706,19 +6716,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122429596</v>
+        <v>122429996</v>
       </c>
       <c r="B56" t="n">
         <v>79727</v>
@@ -6758,10 +6768,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562565</v>
+        <v>562622</v>
       </c>
       <c r="R56" t="n">
-        <v>7039844</v>
+        <v>7039843</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6820,10 +6830,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122425405</v>
+        <v>122427703</v>
       </c>
       <c r="B57" t="n">
-        <v>74747</v>
+        <v>57374</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6836,37 +6846,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562648</v>
+        <v>562784</v>
       </c>
       <c r="R57" t="n">
-        <v>7039865</v>
+        <v>7039590</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6893,9 +6908,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6910,22 +6940,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122425331</v>
+        <v>122425700</v>
       </c>
       <c r="B58" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6938,37 +6968,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562650</v>
+        <v>562678</v>
       </c>
       <c r="R58" t="n">
-        <v>7039856</v>
+        <v>7039813</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6995,9 +7030,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7012,22 +7062,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122426187</v>
+        <v>122430274</v>
       </c>
       <c r="B59" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7040,34 +7090,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562759</v>
+        <v>562903</v>
       </c>
       <c r="R59" t="n">
-        <v>7039787</v>
+        <v>7039649</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7099,7 +7154,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7109,7 +7164,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7124,19 +7184,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122425191</v>
+        <v>122427566</v>
       </c>
       <c r="B60" t="n">
         <v>79727</v>
@@ -7172,14 +7232,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562649</v>
+        <v>562663</v>
       </c>
       <c r="R60" t="n">
-        <v>7039883</v>
+        <v>7039574</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7238,10 +7298,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122427703</v>
+        <v>122430780</v>
       </c>
       <c r="B61" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7254,16 +7314,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7283,10 +7343,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562784</v>
+        <v>562903</v>
       </c>
       <c r="R61" t="n">
-        <v>7039590</v>
+        <v>7039567</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7318,7 +7378,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7328,12 +7388,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7348,22 +7403,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122428074</v>
+        <v>122425242</v>
       </c>
       <c r="B62" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7376,42 +7431,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562763</v>
+        <v>562659</v>
       </c>
       <c r="R62" t="n">
-        <v>7039478</v>
+        <v>7039871</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7438,24 +7488,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7470,19 +7505,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122425780</v>
+        <v>122425617</v>
       </c>
       <c r="B63" t="n">
         <v>79727</v>
@@ -7522,13 +7557,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562725</v>
+        <v>562648</v>
       </c>
       <c r="R63" t="n">
-        <v>7039812</v>
+        <v>7039837</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7555,24 +7590,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7587,22 +7607,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122425539</v>
+        <v>122428711</v>
       </c>
       <c r="B64" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7615,37 +7635,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562651</v>
+        <v>562889</v>
       </c>
       <c r="R64" t="n">
-        <v>7039827</v>
+        <v>7039463</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7672,9 +7697,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7689,22 +7729,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122425544</v>
+        <v>122428074</v>
       </c>
       <c r="B65" t="n">
-        <v>78382</v>
+        <v>57374</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7717,34 +7757,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562672</v>
+        <v>562763</v>
       </c>
       <c r="R65" t="n">
-        <v>7039840</v>
+        <v>7039478</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7776,7 +7821,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7786,7 +7831,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7813,10 +7863,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122426059</v>
+        <v>122429992</v>
       </c>
       <c r="B66" t="n">
-        <v>82433</v>
+        <v>79727</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7829,21 +7879,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7853,10 +7903,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562673</v>
+        <v>562620</v>
       </c>
       <c r="R66" t="n">
-        <v>7039763</v>
+        <v>7039839</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7915,7 +7965,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429998</v>
+        <v>122427473</v>
       </c>
       <c r="B67" t="n">
         <v>57374</v>
@@ -7951,22 +8001,22 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562999</v>
+        <v>562684</v>
       </c>
       <c r="R67" t="n">
-        <v>7039523</v>
+        <v>7039617</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7993,24 +8043,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8025,19 +8065,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122429996</v>
+        <v>122425191</v>
       </c>
       <c r="B68" t="n">
         <v>79727</v>
@@ -8073,14 +8113,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562622</v>
+        <v>562649</v>
       </c>
       <c r="R68" t="n">
-        <v>7039843</v>
+        <v>7039883</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8139,7 +8179,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122427473</v>
+        <v>122428307</v>
       </c>
       <c r="B69" t="n">
         <v>57374</v>
@@ -8175,7 +8215,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8184,10 +8224,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562684</v>
+        <v>562557</v>
       </c>
       <c r="R69" t="n">
-        <v>7039617</v>
+        <v>7039552</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8224,7 +8264,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8251,7 +8291,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122430274</v>
+        <v>122427743</v>
       </c>
       <c r="B70" t="n">
         <v>57374</v>
@@ -8287,7 +8327,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8296,10 +8336,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562903</v>
+        <v>562670</v>
       </c>
       <c r="R70" t="n">
-        <v>7039649</v>
+        <v>7039613</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8331,7 +8371,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8341,12 +8381,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8361,19 +8401,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425328</v>
+        <v>122429588</v>
       </c>
       <c r="B71" t="n">
         <v>79727</v>
@@ -8409,17 +8449,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562678</v>
+        <v>562549</v>
       </c>
       <c r="R71" t="n">
-        <v>7039868</v>
+        <v>7039854</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8446,19 +8486,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8473,22 +8503,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122430780</v>
+        <v>122430036</v>
       </c>
       <c r="B72" t="n">
-        <v>57390</v>
+        <v>79728</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8501,42 +8531,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562903</v>
+        <v>562621</v>
       </c>
       <c r="R72" t="n">
-        <v>7039567</v>
+        <v>7039854</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8563,19 +8588,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8590,22 +8605,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122428796</v>
+        <v>122425310</v>
       </c>
       <c r="B73" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8618,39 +8633,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>563001</v>
+        <v>562650</v>
       </c>
       <c r="R73" t="n">
-        <v>7039421</v>
+        <v>7039868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8682,7 +8692,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8692,12 +8702,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8712,19 +8717,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122427985</v>
+        <v>122428173</v>
       </c>
       <c r="B74" t="n">
         <v>57374</v>
@@ -8769,10 +8774,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562695</v>
+        <v>562701</v>
       </c>
       <c r="R74" t="n">
-        <v>7039574</v>
+        <v>7039441</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8804,7 +8809,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8814,12 +8819,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8846,10 +8851,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122426351</v>
+        <v>122428645</v>
       </c>
       <c r="B75" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8862,42 +8867,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562771</v>
+        <v>562509</v>
       </c>
       <c r="R75" t="n">
-        <v>7039744</v>
+        <v>7039629</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8924,24 +8924,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8956,19 +8941,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122427824</v>
+        <v>122426080</v>
       </c>
       <c r="B76" t="n">
         <v>79727</v>
@@ -9008,10 +8993,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562770</v>
+        <v>562743</v>
       </c>
       <c r="R76" t="n">
-        <v>7039566</v>
+        <v>7039807</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,7 +9028,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9053,7 +9038,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9068,22 +9053,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122427626</v>
+        <v>122430719</v>
       </c>
       <c r="B77" t="n">
-        <v>78382</v>
+        <v>57374</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9096,34 +9081,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562773</v>
+        <v>562835</v>
       </c>
       <c r="R77" t="n">
-        <v>7039605</v>
+        <v>7039750</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9155,7 +9145,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9165,7 +9155,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9192,10 +9187,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122427645</v>
+        <v>122430816</v>
       </c>
       <c r="B78" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9208,34 +9203,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562693</v>
+        <v>562845</v>
       </c>
       <c r="R78" t="n">
-        <v>7039587</v>
+        <v>7039809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427626</v>
+        <v>122429000</v>
       </c>
       <c r="B5" t="n">
-        <v>78382</v>
+        <v>79727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,34 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562773</v>
+        <v>562984</v>
       </c>
       <c r="R5" t="n">
-        <v>7039605</v>
+        <v>7039447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427618</v>
+        <v>122427418</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,39 +1151,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562674</v>
+        <v>562680</v>
       </c>
       <c r="R6" t="n">
-        <v>7039582</v>
+        <v>7039626</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1216,11 +1211,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427824</v>
+        <v>122427626</v>
       </c>
       <c r="B7" t="n">
-        <v>79727</v>
+        <v>78382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562770</v>
+        <v>562773</v>
       </c>
       <c r="R7" t="n">
-        <v>7039566</v>
+        <v>7039605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429000</v>
+        <v>122427618</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,37 +1365,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562984</v>
+        <v>562674</v>
       </c>
       <c r="R8" t="n">
-        <v>7039447</v>
+        <v>7039582</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,19 +1427,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:08</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,19 +1449,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122427418</v>
+        <v>122427824</v>
       </c>
       <c r="B9" t="n">
         <v>79727</v>
@@ -1511,13 +1501,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562680</v>
+        <v>562770</v>
       </c>
       <c r="R9" t="n">
-        <v>7039626</v>
+        <v>7039566</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,9 +1534,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1561,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425855</v>
+        <v>122426220</v>
       </c>
       <c r="B10" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,37 +1589,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562731</v>
+        <v>562671</v>
       </c>
       <c r="R10" t="n">
-        <v>7039827</v>
+        <v>7039729</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,19 +1651,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:07</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,22 +1673,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122426220</v>
+        <v>122426079</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,39 +1701,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562671</v>
+        <v>562676</v>
       </c>
       <c r="R11" t="n">
-        <v>7039729</v>
+        <v>7039760</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1766,11 +1761,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122426079</v>
+        <v>122430000</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1803,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562676</v>
+        <v>562623</v>
       </c>
       <c r="R12" t="n">
-        <v>7039760</v>
+        <v>7039843</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1899,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122430000</v>
+        <v>122425855</v>
       </c>
       <c r="B13" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1939,13 +1929,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562623</v>
+        <v>562731</v>
       </c>
       <c r="R13" t="n">
-        <v>7039843</v>
+        <v>7039827</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,9 +1962,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,22 +1989,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122425405</v>
+        <v>122429596</v>
       </c>
       <c r="B14" t="n">
-        <v>74747</v>
+        <v>79727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562648</v>
+        <v>562565</v>
       </c>
       <c r="R14" t="n">
-        <v>7039865</v>
+        <v>7039844</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122425278</v>
+        <v>122425405</v>
       </c>
       <c r="B15" t="n">
-        <v>79727</v>
+        <v>74747</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,37 +2119,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562673</v>
+        <v>562648</v>
       </c>
       <c r="R15" t="n">
-        <v>7039869</v>
+        <v>7039865</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,19 +2176,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,22 +2193,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122428692</v>
+        <v>122425278</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,42 +2221,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562502</v>
+        <v>562673</v>
       </c>
       <c r="R16" t="n">
-        <v>7039635</v>
+        <v>7039869</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,14 +2278,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,22 +2305,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122429596</v>
+        <v>122428692</v>
       </c>
       <c r="B17" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,34 +2333,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562565</v>
+        <v>562502</v>
       </c>
       <c r="R17" t="n">
-        <v>7039844</v>
+        <v>7039635</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2403,6 +2398,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -5404,10 +5404,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122425397</v>
+        <v>122427401</v>
       </c>
       <c r="B44" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5420,42 +5420,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562662</v>
+        <v>562674</v>
       </c>
       <c r="R44" t="n">
-        <v>7039854</v>
+        <v>7039653</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5482,24 +5477,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5514,22 +5494,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122425539</v>
+        <v>122425397</v>
       </c>
       <c r="B45" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5542,37 +5522,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562651</v>
+        <v>562662</v>
       </c>
       <c r="R45" t="n">
-        <v>7039827</v>
+        <v>7039854</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5599,9 +5584,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,19 +5616,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428124</v>
+        <v>122425539</v>
       </c>
       <c r="B46" t="n">
         <v>79727</v>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562630</v>
+        <v>562651</v>
       </c>
       <c r="R46" t="n">
-        <v>7039565</v>
+        <v>7039827</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122427401</v>
+        <v>122428124</v>
       </c>
       <c r="B47" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562674</v>
+        <v>562630</v>
       </c>
       <c r="R47" t="n">
-        <v>7039653</v>
+        <v>7039565</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122429819</v>
+        <v>122427407</v>
       </c>
       <c r="B50" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6052,37 +6052,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562600</v>
+        <v>562761</v>
       </c>
       <c r="R50" t="n">
-        <v>7039877</v>
+        <v>7039655</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6109,9 +6114,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6126,12 +6146,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6372,10 +6392,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122427407</v>
+        <v>122429819</v>
       </c>
       <c r="B53" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6388,42 +6408,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562761</v>
+        <v>562600</v>
       </c>
       <c r="R53" t="n">
-        <v>7039655</v>
+        <v>7039877</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6450,24 +6465,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,12 +6482,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122430274</v>
+        <v>122430780</v>
       </c>
       <c r="B59" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7090,16 +7090,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7110,7 +7110,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7122,7 +7122,7 @@
         <v>562903</v>
       </c>
       <c r="R59" t="n">
-        <v>7039649</v>
+        <v>7039567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7164,12 +7164,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7184,22 +7179,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427566</v>
+        <v>122430274</v>
       </c>
       <c r="B60" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7212,37 +7207,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562663</v>
+        <v>562903</v>
       </c>
       <c r="R60" t="n">
-        <v>7039574</v>
+        <v>7039649</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7269,9 +7269,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7286,22 +7301,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122430780</v>
+        <v>122427566</v>
       </c>
       <c r="B61" t="n">
-        <v>57390</v>
+        <v>79727</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7314,42 +7329,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562903</v>
+        <v>562663</v>
       </c>
       <c r="R61" t="n">
-        <v>7039567</v>
+        <v>7039574</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7376,19 +7386,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7403,22 +7403,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122425242</v>
+        <v>122427473</v>
       </c>
       <c r="B62" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,34 +7431,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562659</v>
+        <v>562684</v>
       </c>
       <c r="R62" t="n">
-        <v>7039871</v>
+        <v>7039617</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7491,6 +7496,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7517,7 +7527,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122425617</v>
+        <v>122425242</v>
       </c>
       <c r="B63" t="n">
         <v>79727</v>
@@ -7553,14 +7563,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562648</v>
+        <v>562659</v>
       </c>
       <c r="R63" t="n">
-        <v>7039837</v>
+        <v>7039871</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7619,10 +7629,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122428711</v>
+        <v>122425617</v>
       </c>
       <c r="B64" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7635,42 +7645,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562889</v>
+        <v>562648</v>
       </c>
       <c r="R64" t="n">
-        <v>7039463</v>
+        <v>7039837</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7697,24 +7702,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7729,19 +7719,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122428074</v>
+        <v>122428711</v>
       </c>
       <c r="B65" t="n">
         <v>57374</v>
@@ -7786,10 +7776,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562763</v>
+        <v>562889</v>
       </c>
       <c r="R65" t="n">
-        <v>7039478</v>
+        <v>7039463</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7821,7 +7811,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7831,12 +7821,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7863,10 +7853,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122429992</v>
+        <v>122428074</v>
       </c>
       <c r="B66" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7879,37 +7869,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562620</v>
+        <v>562763</v>
       </c>
       <c r="R66" t="n">
-        <v>7039839</v>
+        <v>7039478</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7936,9 +7931,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7953,22 +7963,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427473</v>
+        <v>122429992</v>
       </c>
       <c r="B67" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7981,39 +7991,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562684</v>
+        <v>562620</v>
       </c>
       <c r="R67" t="n">
-        <v>7039617</v>
+        <v>7039839</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8046,11 +8051,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429000</v>
+        <v>122429588</v>
       </c>
       <c r="B5" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,17 +1059,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562984</v>
+        <v>562549</v>
       </c>
       <c r="R5" t="n">
-        <v>7039447</v>
+        <v>7039854</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1096,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1113,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427418</v>
+        <v>122429000</v>
       </c>
       <c r="B6" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,17 +1161,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562680</v>
+        <v>562984</v>
       </c>
       <c r="R6" t="n">
-        <v>7039626</v>
+        <v>7039447</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,9 +1198,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427626</v>
+        <v>122429855</v>
       </c>
       <c r="B7" t="n">
-        <v>78382</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562773</v>
+        <v>562619</v>
       </c>
       <c r="R7" t="n">
-        <v>7039605</v>
+        <v>7039840</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,19 +1310,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,22 +1327,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427618</v>
+        <v>122426059</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>82438</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,39 +1355,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562674</v>
+        <v>562673</v>
       </c>
       <c r="R8" t="n">
-        <v>7039582</v>
+        <v>7039763</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1430,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122427824</v>
+        <v>122425855</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>90819</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562770</v>
+        <v>562731</v>
       </c>
       <c r="R9" t="n">
-        <v>7039566</v>
+        <v>7039827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1541,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122426220</v>
+        <v>122428711</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,13 +1598,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562671</v>
+        <v>562889</v>
       </c>
       <c r="R10" t="n">
-        <v>7039729</v>
+        <v>7039463</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,14 +1631,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack, gammeltall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,22 +1663,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122426079</v>
+        <v>122427605</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,37 +1691,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562676</v>
+        <v>562687</v>
       </c>
       <c r="R11" t="n">
-        <v>7039760</v>
+        <v>7039594</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,9 +1753,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,22 +1785,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122430000</v>
+        <v>122427626</v>
       </c>
       <c r="B12" t="n">
-        <v>79727</v>
+        <v>78387</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1837,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562623</v>
+        <v>562773</v>
       </c>
       <c r="R12" t="n">
-        <v>7039843</v>
+        <v>7039605</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,9 +1870,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,22 +1897,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122425855</v>
+        <v>122428074</v>
       </c>
       <c r="B13" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,34 +1925,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562731</v>
+        <v>562763</v>
       </c>
       <c r="R13" t="n">
-        <v>7039827</v>
+        <v>7039478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1999,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,22 +2019,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122429596</v>
+        <v>122429056</v>
       </c>
       <c r="B14" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,37 +2047,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562565</v>
+        <v>562996</v>
       </c>
       <c r="R14" t="n">
-        <v>7039844</v>
+        <v>7039422</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,9 +2109,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122425405</v>
+        <v>122430274</v>
       </c>
       <c r="B15" t="n">
-        <v>74747</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,37 +2169,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562648</v>
+        <v>562903</v>
       </c>
       <c r="R15" t="n">
-        <v>7039865</v>
+        <v>7039649</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,9 +2231,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,22 +2263,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122425278</v>
+        <v>122425754</v>
       </c>
       <c r="B16" t="n">
-        <v>79727</v>
+        <v>57395</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,37 +2291,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562673</v>
+        <v>562652</v>
       </c>
       <c r="R16" t="n">
-        <v>7039869</v>
+        <v>7039805</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2278,19 +2353,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,22 +2375,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122428692</v>
+        <v>122428034</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57532</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,27 +2403,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2362,13 +2436,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562502</v>
+        <v>562674</v>
       </c>
       <c r="R17" t="n">
-        <v>7039635</v>
+        <v>7039543</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2395,14 +2469,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,22 +2496,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122427645</v>
+        <v>122429992</v>
       </c>
       <c r="B18" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,13 +2548,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562693</v>
+        <v>562620</v>
       </c>
       <c r="R18" t="n">
-        <v>7039587</v>
+        <v>7039839</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2502,19 +2581,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,22 +2598,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122426351</v>
+        <v>122429596</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2557,42 +2626,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562771</v>
+        <v>562565</v>
       </c>
       <c r="R19" t="n">
-        <v>7039744</v>
+        <v>7039844</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2619,24 +2683,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,22 +2700,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122429005</v>
+        <v>122428693</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,22 +2748,22 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562522</v>
+        <v>562933</v>
       </c>
       <c r="R20" t="n">
-        <v>7039596</v>
+        <v>7039394</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,14 +2790,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,22 +2822,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122429334</v>
+        <v>122430397</v>
       </c>
       <c r="B21" t="n">
-        <v>78382</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,37 +2850,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562497</v>
+        <v>562890</v>
       </c>
       <c r="R21" t="n">
-        <v>7039642</v>
+        <v>7039728</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2848,9 +2912,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,22 +2944,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122430183</v>
+        <v>122427407</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,10 +3001,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562911</v>
+        <v>562761</v>
       </c>
       <c r="R22" t="n">
-        <v>7039598</v>
+        <v>7039655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2967,7 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2987,22 +3066,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122425328</v>
+        <v>122428645</v>
       </c>
       <c r="B23" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,37 +3094,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562678</v>
+        <v>562509</v>
       </c>
       <c r="R23" t="n">
-        <v>7039868</v>
+        <v>7039629</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3072,19 +3151,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3099,22 +3168,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122427985</v>
+        <v>122427401</v>
       </c>
       <c r="B24" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3127,42 +3196,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562695</v>
+        <v>562674</v>
       </c>
       <c r="R24" t="n">
-        <v>7039574</v>
+        <v>7039653</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3189,24 +3253,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3221,22 +3270,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122425754</v>
+        <v>122426220</v>
       </c>
       <c r="B25" t="n">
-        <v>57390</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3249,16 +3298,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3269,7 +3318,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3278,10 +3327,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562652</v>
+        <v>562671</v>
       </c>
       <c r="R25" t="n">
-        <v>7039805</v>
+        <v>7039729</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3318,7 +3367,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3345,10 +3394,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122425703</v>
+        <v>122429819</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3361,39 +3410,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562654</v>
+        <v>562600</v>
       </c>
       <c r="R26" t="n">
-        <v>7039819</v>
+        <v>7039877</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3452,10 +3496,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122425780</v>
+        <v>122430062</v>
       </c>
       <c r="B27" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3492,13 +3536,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562725</v>
+        <v>562624</v>
       </c>
       <c r="R27" t="n">
-        <v>7039812</v>
+        <v>7039856</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,24 +3569,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,22 +3586,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122428034</v>
+        <v>122425700</v>
       </c>
       <c r="B28" t="n">
-        <v>57527</v>
+        <v>57379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3585,31 +3614,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3618,10 +3643,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562674</v>
+        <v>562678</v>
       </c>
       <c r="R28" t="n">
-        <v>7039543</v>
+        <v>7039813</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,7 +3678,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3663,7 +3688,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,22 +3708,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122429998</v>
+        <v>122428173</v>
       </c>
       <c r="B29" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,14 +3761,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562999</v>
+        <v>562701</v>
       </c>
       <c r="R29" t="n">
-        <v>7039523</v>
+        <v>7039441</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3770,7 +3800,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3780,7 +3810,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3800,22 +3830,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122430397</v>
+        <v>122430719</v>
       </c>
       <c r="B30" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3848,7 +3878,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3857,10 +3887,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562890</v>
+        <v>562835</v>
       </c>
       <c r="R30" t="n">
-        <v>7039728</v>
+        <v>7039750</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3892,7 +3922,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3902,12 +3932,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425414</v>
+        <v>122425397</v>
       </c>
       <c r="B31" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3979,10 +4009,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562678</v>
+        <v>562662</v>
       </c>
       <c r="R31" t="n">
-        <v>7039855</v>
+        <v>7039854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4014,7 +4044,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4024,7 +4054,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4044,12 +4074,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4059,7 +4089,7 @@
         <v>122428796</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4178,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122429056</v>
+        <v>122427473</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4214,22 +4244,22 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562996</v>
+        <v>562684</v>
       </c>
       <c r="R33" t="n">
-        <v>7039422</v>
+        <v>7039617</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4256,24 +4286,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4288,22 +4308,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122429969</v>
+        <v>122426080</v>
       </c>
       <c r="B34" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4316,21 +4336,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4340,13 +4360,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562604</v>
+        <v>562743</v>
       </c>
       <c r="R34" t="n">
-        <v>7039850</v>
+        <v>7039807</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4373,9 +4393,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,22 +4420,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122426422</v>
+        <v>122429240</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>78387</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,42 +4448,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562642</v>
+        <v>562497</v>
       </c>
       <c r="R35" t="n">
-        <v>7039716</v>
+        <v>7039642</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4480,24 +4505,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,22 +4522,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122425331</v>
+        <v>122425516</v>
       </c>
       <c r="B36" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4540,37 +4550,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562650</v>
+        <v>562706</v>
       </c>
       <c r="R36" t="n">
-        <v>7039856</v>
+        <v>7039810</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4597,9 +4612,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,22 +4644,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122428148</v>
+        <v>122427703</v>
       </c>
       <c r="B37" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4642,34 +4672,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562707</v>
+        <v>562784</v>
       </c>
       <c r="R37" t="n">
-        <v>7039456</v>
+        <v>7039590</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4701,7 +4736,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4711,7 +4746,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,22 +4766,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429855</v>
+        <v>122427618</v>
       </c>
       <c r="B38" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4754,34 +4794,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562619</v>
+        <v>562674</v>
       </c>
       <c r="R38" t="n">
-        <v>7039840</v>
+        <v>7039582</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4814,6 +4859,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4840,10 +4890,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122427459</v>
+        <v>122430183</v>
       </c>
       <c r="B39" t="n">
-        <v>98185</v>
+        <v>57379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4852,40 +4902,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4894,10 +4935,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562755</v>
+        <v>562911</v>
       </c>
       <c r="R39" t="n">
-        <v>7039631</v>
+        <v>7039598</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4929,7 +4970,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4980,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4966,10 +5012,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122426187</v>
+        <v>122430816</v>
       </c>
       <c r="B40" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,34 +5028,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562759</v>
+        <v>562845</v>
       </c>
       <c r="R40" t="n">
-        <v>7039787</v>
+        <v>7039809</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5041,7 +5092,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,7 +5102,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,22 +5117,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122425284</v>
+        <v>122429996</v>
       </c>
       <c r="B41" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5114,14 +5165,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562657</v>
+        <v>562622</v>
       </c>
       <c r="R41" t="n">
-        <v>7039870</v>
+        <v>7039843</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5180,10 +5231,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122427953</v>
+        <v>122426187</v>
       </c>
       <c r="B42" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5220,13 +5271,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562661</v>
+        <v>562759</v>
       </c>
       <c r="R42" t="n">
-        <v>7039580</v>
+        <v>7039787</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5253,9 +5304,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5270,22 +5331,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427605</v>
+        <v>122425242</v>
       </c>
       <c r="B43" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5298,42 +5359,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562687</v>
+        <v>562659</v>
       </c>
       <c r="R43" t="n">
-        <v>7039594</v>
+        <v>7039871</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5360,24 +5416,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5392,22 +5433,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122427401</v>
+        <v>122430000</v>
       </c>
       <c r="B44" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5420,21 +5461,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5444,10 +5485,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562674</v>
+        <v>562623</v>
       </c>
       <c r="R44" t="n">
-        <v>7039653</v>
+        <v>7039843</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5506,10 +5547,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122425397</v>
+        <v>122427645</v>
       </c>
       <c r="B45" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5522,39 +5563,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562662</v>
+        <v>562693</v>
       </c>
       <c r="R45" t="n">
-        <v>7039854</v>
+        <v>7039587</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5586,7 +5622,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5596,12 +5632,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,22 +5647,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122425539</v>
+        <v>122429005</v>
       </c>
       <c r="B46" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5644,34 +5675,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562651</v>
+        <v>562522</v>
       </c>
       <c r="R46" t="n">
-        <v>7039827</v>
+        <v>7039596</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5704,6 +5740,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5730,10 +5771,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428124</v>
+        <v>122425191</v>
       </c>
       <c r="B47" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5766,14 +5807,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562630</v>
+        <v>562649</v>
       </c>
       <c r="R47" t="n">
-        <v>7039565</v>
+        <v>7039883</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5832,10 +5873,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122426059</v>
+        <v>122427566</v>
       </c>
       <c r="B48" t="n">
-        <v>82433</v>
+        <v>79732</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5848,21 +5889,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5872,10 +5913,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562673</v>
+        <v>562663</v>
       </c>
       <c r="R48" t="n">
-        <v>7039763</v>
+        <v>7039574</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5934,10 +5975,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122430062</v>
+        <v>122425617</v>
       </c>
       <c r="B49" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5974,10 +6015,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562624</v>
+        <v>562648</v>
       </c>
       <c r="R49" t="n">
-        <v>7039856</v>
+        <v>7039837</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6036,10 +6077,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122427407</v>
+        <v>122427418</v>
       </c>
       <c r="B50" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6052,42 +6093,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562761</v>
+        <v>562680</v>
       </c>
       <c r="R50" t="n">
-        <v>7039655</v>
+        <v>7039626</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6114,24 +6150,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6146,22 +6167,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122425516</v>
+        <v>122425310</v>
       </c>
       <c r="B51" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6174,39 +6195,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562706</v>
+        <v>562650</v>
       </c>
       <c r="R51" t="n">
-        <v>7039810</v>
+        <v>7039868</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6238,7 +6254,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6248,12 +6264,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6268,22 +6279,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122425536</v>
+        <v>122425780</v>
       </c>
       <c r="B52" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6320,10 +6331,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562710</v>
+        <v>562725</v>
       </c>
       <c r="R52" t="n">
-        <v>7039834</v>
+        <v>7039812</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6355,7 +6366,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6365,7 +6376,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6392,10 +6408,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122429819</v>
+        <v>122428148</v>
       </c>
       <c r="B53" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6408,21 +6424,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6432,13 +6448,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562600</v>
+        <v>562707</v>
       </c>
       <c r="R53" t="n">
-        <v>7039877</v>
+        <v>7039456</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6465,9 +6481,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,22 +6508,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122425544</v>
+        <v>122428124</v>
       </c>
       <c r="B54" t="n">
-        <v>78382</v>
+        <v>79732</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6510,21 +6536,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6534,13 +6560,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562672</v>
+        <v>562630</v>
       </c>
       <c r="R54" t="n">
-        <v>7039840</v>
+        <v>7039565</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6567,19 +6593,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6594,22 +6610,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428693</v>
+        <v>122426422</v>
       </c>
       <c r="B55" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6642,19 +6658,19 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562933</v>
+        <v>562642</v>
       </c>
       <c r="R55" t="n">
-        <v>7039394</v>
+        <v>7039716</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6686,7 +6702,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6696,12 +6712,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6716,22 +6732,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122429996</v>
+        <v>122425331</v>
       </c>
       <c r="B56" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6744,21 +6760,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6768,10 +6784,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562622</v>
+        <v>562650</v>
       </c>
       <c r="R56" t="n">
-        <v>7039843</v>
+        <v>7039856</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6830,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427703</v>
+        <v>122427743</v>
       </c>
       <c r="B57" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6875,10 +6891,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562784</v>
+        <v>562670</v>
       </c>
       <c r="R57" t="n">
-        <v>7039590</v>
+        <v>7039613</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6910,7 +6926,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6920,12 +6936,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6940,22 +6956,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122425700</v>
+        <v>122427824</v>
       </c>
       <c r="B58" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6968,39 +6984,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562678</v>
+        <v>562770</v>
       </c>
       <c r="R58" t="n">
-        <v>7039813</v>
+        <v>7039566</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7032,7 +7043,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7042,12 +7053,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7074,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122430780</v>
+        <v>122427985</v>
       </c>
       <c r="B59" t="n">
-        <v>57390</v>
+        <v>57379</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7090,16 +7096,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7119,10 +7125,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562903</v>
+        <v>562695</v>
       </c>
       <c r="R59" t="n">
-        <v>7039567</v>
+        <v>7039574</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7154,7 +7160,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7164,7 +7170,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7191,10 +7202,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122430274</v>
+        <v>122428307</v>
       </c>
       <c r="B60" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7227,7 +7238,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7236,13 +7247,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562903</v>
+        <v>562557</v>
       </c>
       <c r="R60" t="n">
-        <v>7039649</v>
+        <v>7039552</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7269,24 +7280,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7301,22 +7302,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122427566</v>
+        <v>122429969</v>
       </c>
       <c r="B61" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7329,21 +7330,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7353,10 +7354,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562663</v>
+        <v>562604</v>
       </c>
       <c r="R61" t="n">
-        <v>7039574</v>
+        <v>7039850</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7415,10 +7416,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427473</v>
+        <v>122425536</v>
       </c>
       <c r="B62" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,42 +7432,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562684</v>
+        <v>562710</v>
       </c>
       <c r="R62" t="n">
-        <v>7039617</v>
+        <v>7039834</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7493,14 +7489,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7515,22 +7516,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122425242</v>
+        <v>122427953</v>
       </c>
       <c r="B63" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7563,14 +7564,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562659</v>
+        <v>562661</v>
       </c>
       <c r="R63" t="n">
-        <v>7039871</v>
+        <v>7039580</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7629,10 +7630,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122425617</v>
+        <v>122425539</v>
       </c>
       <c r="B64" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7669,10 +7670,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562648</v>
+        <v>562651</v>
       </c>
       <c r="R64" t="n">
-        <v>7039837</v>
+        <v>7039827</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7731,10 +7732,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122428711</v>
+        <v>122425414</v>
       </c>
       <c r="B65" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7776,10 +7777,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562889</v>
+        <v>562678</v>
       </c>
       <c r="R65" t="n">
-        <v>7039463</v>
+        <v>7039855</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7811,7 +7812,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7821,12 +7822,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7841,22 +7842,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122428074</v>
+        <v>122425703</v>
       </c>
       <c r="B66" t="n">
-        <v>57374</v>
+        <v>57395</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7869,16 +7870,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7889,7 +7890,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7898,13 +7899,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562763</v>
+        <v>562654</v>
       </c>
       <c r="R66" t="n">
-        <v>7039478</v>
+        <v>7039819</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7931,24 +7932,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7963,22 +7949,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429992</v>
+        <v>122430780</v>
       </c>
       <c r="B67" t="n">
-        <v>79727</v>
+        <v>57395</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7991,37 +7977,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562620</v>
+        <v>562903</v>
       </c>
       <c r="R67" t="n">
-        <v>7039839</v>
+        <v>7039567</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8048,9 +8039,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8065,22 +8066,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122425191</v>
+        <v>122427459</v>
       </c>
       <c r="B68" t="n">
-        <v>79727</v>
+        <v>98197</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8089,41 +8090,55 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562649</v>
+        <v>562755</v>
       </c>
       <c r="R68" t="n">
-        <v>7039883</v>
+        <v>7039631</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8150,9 +8165,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8167,22 +8192,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122428307</v>
+        <v>122426079</v>
       </c>
       <c r="B69" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8195,39 +8220,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562557</v>
+        <v>562676</v>
       </c>
       <c r="R69" t="n">
-        <v>7039552</v>
+        <v>7039760</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8260,11 +8280,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8291,10 +8306,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122427743</v>
+        <v>122430036</v>
       </c>
       <c r="B70" t="n">
-        <v>57374</v>
+        <v>79733</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8307,42 +8322,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562670</v>
+        <v>562621</v>
       </c>
       <c r="R70" t="n">
-        <v>7039613</v>
+        <v>7039854</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8369,24 +8379,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8401,22 +8396,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122429588</v>
+        <v>122425405</v>
       </c>
       <c r="B71" t="n">
-        <v>79727</v>
+        <v>74752</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8429,21 +8424,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8453,10 +8448,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562549</v>
+        <v>562648</v>
       </c>
       <c r="R71" t="n">
-        <v>7039854</v>
+        <v>7039865</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8515,10 +8510,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122430036</v>
+        <v>122425544</v>
       </c>
       <c r="B72" t="n">
-        <v>79728</v>
+        <v>78387</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8531,21 +8526,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8555,13 +8550,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562621</v>
+        <v>562672</v>
       </c>
       <c r="R72" t="n">
-        <v>7039854</v>
+        <v>7039840</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8588,9 +8583,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8605,22 +8610,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122425310</v>
+        <v>122425278</v>
       </c>
       <c r="B73" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8633,34 +8638,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562650</v>
+        <v>562673</v>
       </c>
       <c r="R73" t="n">
-        <v>7039868</v>
+        <v>7039869</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8692,7 +8697,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8702,7 +8707,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8717,22 +8722,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122428173</v>
+        <v>122425328</v>
       </c>
       <c r="B74" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8745,39 +8750,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562701</v>
+        <v>562678</v>
       </c>
       <c r="R74" t="n">
-        <v>7039441</v>
+        <v>7039868</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8819,12 +8819,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8851,10 +8846,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122428645</v>
+        <v>122428692</v>
       </c>
       <c r="B75" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8867,34 +8862,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562509</v>
+        <v>562502</v>
       </c>
       <c r="R75" t="n">
-        <v>7039629</v>
+        <v>7039635</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8927,6 +8927,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8953,10 +8958,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122426080</v>
+        <v>122429998</v>
       </c>
       <c r="B76" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8969,34 +8974,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562743</v>
+        <v>562999</v>
       </c>
       <c r="R76" t="n">
-        <v>7039807</v>
+        <v>7039523</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9028,7 +9038,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9038,7 +9048,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9053,22 +9068,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122430719</v>
+        <v>122426351</v>
       </c>
       <c r="B77" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9110,10 +9125,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562835</v>
+        <v>562771</v>
       </c>
       <c r="R77" t="n">
-        <v>7039750</v>
+        <v>7039744</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9145,7 +9160,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9155,12 +9170,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9175,22 +9190,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122430816</v>
+        <v>122425284</v>
       </c>
       <c r="B78" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9203,42 +9218,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562845</v>
+        <v>562657</v>
       </c>
       <c r="R78" t="n">
-        <v>7039809</v>
+        <v>7039870</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9265,19 +9275,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429588</v>
+        <v>122430397</v>
       </c>
       <c r="B5" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,37 +1039,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562549</v>
+        <v>562890</v>
       </c>
       <c r="R5" t="n">
-        <v>7039854</v>
+        <v>7039728</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,9 +1101,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,19 +1133,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429000</v>
+        <v>122430062</v>
       </c>
       <c r="B6" t="n">
         <v>79732</v>
@@ -1161,17 +1181,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562984</v>
+        <v>562624</v>
       </c>
       <c r="R6" t="n">
-        <v>7039447</v>
+        <v>7039856</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,19 +1218,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429855</v>
+        <v>122425397</v>
       </c>
       <c r="B7" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,37 +1263,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562619</v>
+        <v>562662</v>
       </c>
       <c r="R7" t="n">
-        <v>7039840</v>
+        <v>7039854</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,9 +1325,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,22 +1357,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122426059</v>
+        <v>122429000</v>
       </c>
       <c r="B8" t="n">
-        <v>82438</v>
+        <v>79732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,37 +1385,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562673</v>
+        <v>562984</v>
       </c>
       <c r="R8" t="n">
-        <v>7039763</v>
+        <v>7039447</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,9 +1442,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425855</v>
+        <v>122426079</v>
       </c>
       <c r="B9" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,21 +1497,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,13 +1521,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562731</v>
+        <v>562676</v>
       </c>
       <c r="R9" t="n">
-        <v>7039827</v>
+        <v>7039760</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,19 +1554,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,22 +1571,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428711</v>
+        <v>122427824</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,39 +1599,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562889</v>
+        <v>562770</v>
       </c>
       <c r="R10" t="n">
-        <v>7039463</v>
+        <v>7039566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,12 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122427605</v>
+        <v>122430036</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,42 +1711,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562687</v>
+        <v>562621</v>
       </c>
       <c r="R11" t="n">
-        <v>7039594</v>
+        <v>7039854</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,24 +1768,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,19 +1785,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122427626</v>
+        <v>122429240</v>
       </c>
       <c r="B12" t="n">
         <v>78387</v>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562773</v>
+        <v>562497</v>
       </c>
       <c r="R12" t="n">
-        <v>7039605</v>
+        <v>7039642</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,19 +1870,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,19 +1887,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122428074</v>
+        <v>122430183</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1954,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562763</v>
+        <v>562911</v>
       </c>
       <c r="R13" t="n">
-        <v>7039478</v>
+        <v>7039598</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2031,7 +2021,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122429056</v>
+        <v>122427407</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2072,14 +2062,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562996</v>
+        <v>562761</v>
       </c>
       <c r="R14" t="n">
-        <v>7039422</v>
+        <v>7039655</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,12 +2111,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2131,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122430274</v>
+        <v>122427566</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,42 +2159,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562903</v>
+        <v>562663</v>
       </c>
       <c r="R15" t="n">
-        <v>7039649</v>
+        <v>7039574</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,24 +2216,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,22 +2233,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122425754</v>
+        <v>122427645</v>
       </c>
       <c r="B16" t="n">
-        <v>57395</v>
+        <v>79732</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,42 +2261,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562652</v>
+        <v>562693</v>
       </c>
       <c r="R16" t="n">
-        <v>7039805</v>
+        <v>7039587</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2353,14 +2318,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stor bohål i aso</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,22 +2345,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122428034</v>
+        <v>122425617</v>
       </c>
       <c r="B17" t="n">
-        <v>57532</v>
+        <v>79732</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,46 +2373,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562674</v>
+        <v>562648</v>
       </c>
       <c r="R17" t="n">
-        <v>7039543</v>
+        <v>7039837</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,19 +2430,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,19 +2447,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122429992</v>
+        <v>122425539</v>
       </c>
       <c r="B18" t="n">
         <v>79732</v>
@@ -2548,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562620</v>
+        <v>562651</v>
       </c>
       <c r="R18" t="n">
-        <v>7039839</v>
+        <v>7039827</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2610,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122429596</v>
+        <v>122428173</v>
       </c>
       <c r="B19" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,37 +2577,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562565</v>
+        <v>562701</v>
       </c>
       <c r="R19" t="n">
-        <v>7039844</v>
+        <v>7039441</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2683,9 +2639,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,19 +2671,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122428693</v>
+        <v>122427605</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2753,14 +2724,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562933</v>
+        <v>562687</v>
       </c>
       <c r="R20" t="n">
-        <v>7039394</v>
+        <v>7039594</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,7 +2763,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2802,7 +2773,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2834,7 +2805,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122430397</v>
+        <v>122428692</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2879,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562890</v>
+        <v>562502</v>
       </c>
       <c r="R21" t="n">
-        <v>7039728</v>
+        <v>7039635</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2912,24 +2883,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,19 +2905,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427407</v>
+        <v>122425700</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -3001,10 +2962,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562761</v>
+        <v>562678</v>
       </c>
       <c r="R22" t="n">
-        <v>7039655</v>
+        <v>7039813</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3066,22 +3027,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122428645</v>
+        <v>122427953</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3094,21 +3055,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3118,10 +3079,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562509</v>
+        <v>562661</v>
       </c>
       <c r="R23" t="n">
-        <v>7039629</v>
+        <v>7039580</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3180,10 +3141,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122427401</v>
+        <v>122425278</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3196,37 +3157,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562674</v>
+        <v>562673</v>
       </c>
       <c r="R24" t="n">
-        <v>7039653</v>
+        <v>7039869</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3253,9 +3214,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,19 +3241,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122426220</v>
+        <v>122427618</v>
       </c>
       <c r="B25" t="n">
         <v>57379</v>
@@ -3327,10 +3298,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562671</v>
+        <v>562674</v>
       </c>
       <c r="R25" t="n">
-        <v>7039729</v>
+        <v>7039582</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3367,7 +3338,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack, gammeltall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3394,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429819</v>
+        <v>122429998</v>
       </c>
       <c r="B26" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,37 +3381,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562600</v>
+        <v>562999</v>
       </c>
       <c r="R26" t="n">
-        <v>7039877</v>
+        <v>7039523</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3467,9 +3443,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,19 +3475,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122430062</v>
+        <v>122425242</v>
       </c>
       <c r="B27" t="n">
         <v>79732</v>
@@ -3532,14 +3523,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562624</v>
+        <v>562659</v>
       </c>
       <c r="R27" t="n">
-        <v>7039856</v>
+        <v>7039871</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3598,10 +3589,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122425700</v>
+        <v>122426059</v>
       </c>
       <c r="B28" t="n">
-        <v>57379</v>
+        <v>82438</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,42 +3605,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562678</v>
+        <v>562673</v>
       </c>
       <c r="R28" t="n">
-        <v>7039813</v>
+        <v>7039763</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3676,24 +3662,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,22 +3679,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122428173</v>
+        <v>122426080</v>
       </c>
       <c r="B29" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3736,39 +3707,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562701</v>
+        <v>562743</v>
       </c>
       <c r="R29" t="n">
-        <v>7039441</v>
+        <v>7039807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,7 +3766,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3810,12 +3776,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3842,10 +3803,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122430719</v>
+        <v>122425284</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,42 +3819,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562835</v>
+        <v>562657</v>
       </c>
       <c r="R30" t="n">
-        <v>7039750</v>
+        <v>7039870</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3920,24 +3876,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,22 +3893,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425397</v>
+        <v>122425544</v>
       </c>
       <c r="B31" t="n">
-        <v>57379</v>
+        <v>78387</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3980,39 +3921,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562662</v>
+        <v>562672</v>
       </c>
       <c r="R31" t="n">
-        <v>7039854</v>
+        <v>7039840</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,7 +3980,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4054,12 +3990,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4086,10 +4017,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122428796</v>
+        <v>122425703</v>
       </c>
       <c r="B32" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4102,16 +4033,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4122,22 +4053,22 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563001</v>
+        <v>562654</v>
       </c>
       <c r="R32" t="n">
-        <v>7039421</v>
+        <v>7039819</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4164,24 +4095,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,19 +4112,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122427473</v>
+        <v>122426351</v>
       </c>
       <c r="B33" t="n">
         <v>57379</v>
@@ -4244,7 +4160,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4253,13 +4169,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562684</v>
+        <v>562771</v>
       </c>
       <c r="R33" t="n">
-        <v>7039617</v>
+        <v>7039744</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4286,14 +4202,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4308,22 +4234,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122426080</v>
+        <v>122427401</v>
       </c>
       <c r="B34" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4336,21 +4262,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4360,13 +4286,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562743</v>
+        <v>562674</v>
       </c>
       <c r="R34" t="n">
-        <v>7039807</v>
+        <v>7039653</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4393,19 +4319,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,22 +4336,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122429240</v>
+        <v>122428148</v>
       </c>
       <c r="B35" t="n">
-        <v>78387</v>
+        <v>79732</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4448,21 +4364,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4472,13 +4388,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562497</v>
+        <v>562707</v>
       </c>
       <c r="R35" t="n">
-        <v>7039642</v>
+        <v>7039456</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4505,9 +4421,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4522,12 +4448,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4656,7 +4582,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122427703</v>
+        <v>122430719</v>
       </c>
       <c r="B37" t="n">
         <v>57379</v>
@@ -4701,10 +4627,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562784</v>
+        <v>562835</v>
       </c>
       <c r="R37" t="n">
-        <v>7039590</v>
+        <v>7039750</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4736,7 +4662,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4746,7 +4672,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4778,7 +4704,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122427618</v>
+        <v>122429005</v>
       </c>
       <c r="B38" t="n">
         <v>57379</v>
@@ -4814,7 +4740,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4823,10 +4749,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562674</v>
+        <v>562522</v>
       </c>
       <c r="R38" t="n">
-        <v>7039582</v>
+        <v>7039596</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4863,7 +4789,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4890,10 +4816,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122430183</v>
+        <v>122425754</v>
       </c>
       <c r="B39" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4906,16 +4832,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4926,7 +4852,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4935,13 +4861,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562911</v>
+        <v>562652</v>
       </c>
       <c r="R39" t="n">
-        <v>7039598</v>
+        <v>7039805</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4968,24 +4894,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5000,22 +4916,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122430816</v>
+        <v>122425405</v>
       </c>
       <c r="B40" t="n">
-        <v>57379</v>
+        <v>74752</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5028,42 +4944,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562845</v>
+        <v>562648</v>
       </c>
       <c r="R40" t="n">
-        <v>7039809</v>
+        <v>7039865</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5090,19 +5001,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5117,22 +5018,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122429996</v>
+        <v>122425331</v>
       </c>
       <c r="B41" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5145,21 +5046,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5169,10 +5070,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562622</v>
+        <v>562650</v>
       </c>
       <c r="R41" t="n">
-        <v>7039843</v>
+        <v>7039856</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5231,10 +5132,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122426187</v>
+        <v>122427985</v>
       </c>
       <c r="B42" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5247,34 +5148,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562759</v>
+        <v>562695</v>
       </c>
       <c r="R42" t="n">
-        <v>7039787</v>
+        <v>7039574</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5306,7 +5212,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5316,7 +5222,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5343,7 +5254,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122425242</v>
+        <v>122425536</v>
       </c>
       <c r="B43" t="n">
         <v>79732</v>
@@ -5379,17 +5290,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562659</v>
+        <v>562710</v>
       </c>
       <c r="R43" t="n">
-        <v>7039871</v>
+        <v>7039834</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5416,9 +5327,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5433,19 +5354,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122430000</v>
+        <v>122429996</v>
       </c>
       <c r="B44" t="n">
         <v>79732</v>
@@ -5485,7 +5406,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562623</v>
+        <v>562622</v>
       </c>
       <c r="R44" t="n">
         <v>7039843</v>
@@ -5547,7 +5468,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122427645</v>
+        <v>122429588</v>
       </c>
       <c r="B45" t="n">
         <v>79732</v>
@@ -5587,13 +5508,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562693</v>
+        <v>562549</v>
       </c>
       <c r="R45" t="n">
-        <v>7039587</v>
+        <v>7039854</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5620,19 +5541,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,22 +5558,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122429005</v>
+        <v>122428645</v>
       </c>
       <c r="B46" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5675,39 +5586,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562522</v>
+        <v>562509</v>
       </c>
       <c r="R46" t="n">
-        <v>7039596</v>
+        <v>7039629</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5740,11 +5646,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5771,10 +5672,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122425191</v>
+        <v>122426220</v>
       </c>
       <c r="B47" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5787,34 +5688,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562649</v>
+        <v>562671</v>
       </c>
       <c r="R47" t="n">
-        <v>7039883</v>
+        <v>7039729</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5847,6 +5753,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5873,10 +5784,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122427566</v>
+        <v>122427473</v>
       </c>
       <c r="B48" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5889,34 +5800,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562663</v>
+        <v>562684</v>
       </c>
       <c r="R48" t="n">
-        <v>7039574</v>
+        <v>7039617</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5949,6 +5865,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5975,10 +5896,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122425617</v>
+        <v>122429056</v>
       </c>
       <c r="B49" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5991,37 +5912,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562648</v>
+        <v>562996</v>
       </c>
       <c r="R49" t="n">
-        <v>7039837</v>
+        <v>7039422</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6048,9 +5974,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6065,22 +6006,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122427418</v>
+        <v>122427459</v>
       </c>
       <c r="B50" t="n">
-        <v>79732</v>
+        <v>98202</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,41 +6030,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562680</v>
+        <v>562755</v>
       </c>
       <c r="R50" t="n">
-        <v>7039626</v>
+        <v>7039631</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6150,9 +6105,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6167,22 +6132,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122425310</v>
+        <v>122430816</v>
       </c>
       <c r="B51" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6195,34 +6160,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562650</v>
+        <v>562845</v>
       </c>
       <c r="R51" t="n">
-        <v>7039868</v>
+        <v>7039809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6254,7 +6224,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6264,7 +6234,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6291,10 +6261,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122425780</v>
+        <v>122428711</v>
       </c>
       <c r="B52" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6307,34 +6277,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562725</v>
+        <v>562889</v>
       </c>
       <c r="R52" t="n">
-        <v>7039812</v>
+        <v>7039463</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6366,7 +6341,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6376,12 +6351,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Lunglav på rönn</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6396,22 +6371,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122428148</v>
+        <v>122426422</v>
       </c>
       <c r="B53" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6424,34 +6399,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562707</v>
+        <v>562642</v>
       </c>
       <c r="R53" t="n">
-        <v>7039456</v>
+        <v>7039716</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6483,7 +6463,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6493,7 +6473,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6508,22 +6493,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428124</v>
+        <v>122429819</v>
       </c>
       <c r="B54" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6536,21 +6521,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6560,10 +6545,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562630</v>
+        <v>562600</v>
       </c>
       <c r="R54" t="n">
-        <v>7039565</v>
+        <v>7039877</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6622,10 +6607,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122426422</v>
+        <v>122425310</v>
       </c>
       <c r="B55" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6638,39 +6623,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562642</v>
+        <v>562650</v>
       </c>
       <c r="R55" t="n">
-        <v>7039716</v>
+        <v>7039868</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6702,7 +6682,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6712,12 +6692,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6744,10 +6719,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122425331</v>
+        <v>122430780</v>
       </c>
       <c r="B56" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6760,37 +6735,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562650</v>
+        <v>562903</v>
       </c>
       <c r="R56" t="n">
-        <v>7039856</v>
+        <v>7039567</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6817,9 +6797,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6834,22 +6824,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427743</v>
+        <v>122427626</v>
       </c>
       <c r="B57" t="n">
-        <v>57379</v>
+        <v>78387</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6862,39 +6852,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562670</v>
+        <v>562773</v>
       </c>
       <c r="R57" t="n">
-        <v>7039613</v>
+        <v>7039605</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6926,7 +6911,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6936,12 +6921,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6956,19 +6936,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122427824</v>
+        <v>122427418</v>
       </c>
       <c r="B58" t="n">
         <v>79732</v>
@@ -7008,13 +6988,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562770</v>
+        <v>562680</v>
       </c>
       <c r="R58" t="n">
-        <v>7039566</v>
+        <v>7039626</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7041,19 +7021,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7068,22 +7038,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427985</v>
+        <v>122429855</v>
       </c>
       <c r="B59" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7096,42 +7066,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562695</v>
+        <v>562619</v>
       </c>
       <c r="R59" t="n">
-        <v>7039574</v>
+        <v>7039840</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7158,24 +7123,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7190,22 +7140,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122428307</v>
+        <v>122429596</v>
       </c>
       <c r="B60" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7218,39 +7168,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562557</v>
+        <v>562565</v>
       </c>
       <c r="R60" t="n">
-        <v>7039552</v>
+        <v>7039844</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7283,11 +7228,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7314,10 +7254,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122429969</v>
+        <v>122430274</v>
       </c>
       <c r="B61" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7330,37 +7270,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562604</v>
+        <v>562903</v>
       </c>
       <c r="R61" t="n">
-        <v>7039850</v>
+        <v>7039649</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7387,9 +7332,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7404,22 +7364,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122425536</v>
+        <v>122425414</v>
       </c>
       <c r="B62" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7432,34 +7392,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562710</v>
+        <v>562678</v>
       </c>
       <c r="R62" t="n">
-        <v>7039834</v>
+        <v>7039855</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7491,7 +7456,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7501,7 +7466,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,10 +7498,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122427953</v>
+        <v>122428074</v>
       </c>
       <c r="B63" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7544,37 +7514,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562661</v>
+        <v>562763</v>
       </c>
       <c r="R63" t="n">
-        <v>7039580</v>
+        <v>7039478</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7601,9 +7576,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7618,19 +7608,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122425539</v>
+        <v>122429992</v>
       </c>
       <c r="B64" t="n">
         <v>79732</v>
@@ -7670,10 +7660,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562651</v>
+        <v>562620</v>
       </c>
       <c r="R64" t="n">
-        <v>7039827</v>
+        <v>7039839</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7732,10 +7722,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122425414</v>
+        <v>122430000</v>
       </c>
       <c r="B65" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7748,42 +7738,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562678</v>
+        <v>562623</v>
       </c>
       <c r="R65" t="n">
-        <v>7039855</v>
+        <v>7039843</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7810,24 +7795,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7842,22 +7812,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122425703</v>
+        <v>122425191</v>
       </c>
       <c r="B66" t="n">
-        <v>57395</v>
+        <v>79732</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7870,39 +7840,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562654</v>
+        <v>562649</v>
       </c>
       <c r="R66" t="n">
-        <v>7039819</v>
+        <v>7039883</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7961,10 +7926,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122430780</v>
+        <v>122428796</v>
       </c>
       <c r="B67" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7977,16 +7942,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8002,14 +7967,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562903</v>
+        <v>563001</v>
       </c>
       <c r="R67" t="n">
-        <v>7039567</v>
+        <v>7039421</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8041,7 +8006,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8016,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,10 +8048,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122427459</v>
+        <v>122426187</v>
       </c>
       <c r="B68" t="n">
-        <v>98197</v>
+        <v>79732</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8090,52 +8060,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562755</v>
+        <v>562759</v>
       </c>
       <c r="R68" t="n">
-        <v>7039631</v>
+        <v>7039787</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8167,7 +8123,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8177,7 +8133,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8192,22 +8148,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122426079</v>
+        <v>122425780</v>
       </c>
       <c r="B69" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8220,21 +8176,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8244,13 +8200,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562676</v>
+        <v>562725</v>
       </c>
       <c r="R69" t="n">
-        <v>7039760</v>
+        <v>7039812</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8277,9 +8233,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8294,22 +8265,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122430036</v>
+        <v>122425328</v>
       </c>
       <c r="B70" t="n">
-        <v>79733</v>
+        <v>79732</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8322,37 +8293,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562621</v>
+        <v>562678</v>
       </c>
       <c r="R70" t="n">
-        <v>7039854</v>
+        <v>7039868</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8379,9 +8350,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8396,22 +8377,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425405</v>
+        <v>122427703</v>
       </c>
       <c r="B71" t="n">
-        <v>74752</v>
+        <v>57379</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8424,37 +8405,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562648</v>
+        <v>562784</v>
       </c>
       <c r="R71" t="n">
-        <v>7039865</v>
+        <v>7039590</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8481,9 +8467,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8498,22 +8499,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122425544</v>
+        <v>122429969</v>
       </c>
       <c r="B72" t="n">
-        <v>78387</v>
+        <v>78651</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8526,21 +8527,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8550,13 +8551,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562672</v>
+        <v>562604</v>
       </c>
       <c r="R72" t="n">
-        <v>7039840</v>
+        <v>7039850</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8583,19 +8584,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8610,19 +8601,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122425278</v>
+        <v>122428124</v>
       </c>
       <c r="B73" t="n">
         <v>79732</v>
@@ -8658,17 +8649,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562673</v>
+        <v>562630</v>
       </c>
       <c r="R73" t="n">
-        <v>7039869</v>
+        <v>7039565</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8695,19 +8686,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8722,22 +8703,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122425328</v>
+        <v>122425855</v>
       </c>
       <c r="B74" t="n">
-        <v>79732</v>
+        <v>90826</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8750,34 +8731,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562678</v>
+        <v>562731</v>
       </c>
       <c r="R74" t="n">
-        <v>7039868</v>
+        <v>7039827</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8809,7 +8790,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8819,7 +8800,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8846,7 +8827,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122428692</v>
+        <v>122428307</v>
       </c>
       <c r="B75" t="n">
         <v>57379</v>
@@ -8882,7 +8863,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8891,10 +8872,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562502</v>
+        <v>562557</v>
       </c>
       <c r="R75" t="n">
-        <v>7039635</v>
+        <v>7039552</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8931,7 +8912,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8958,7 +8939,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122429998</v>
+        <v>122427743</v>
       </c>
       <c r="B76" t="n">
         <v>57379</v>
@@ -8999,14 +8980,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562999</v>
+        <v>562670</v>
       </c>
       <c r="R76" t="n">
-        <v>7039523</v>
+        <v>7039613</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9038,7 +9019,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9048,12 +9029,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9068,19 +9049,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122426351</v>
+        <v>122428693</v>
       </c>
       <c r="B77" t="n">
         <v>57379</v>
@@ -9121,14 +9102,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562771</v>
+        <v>562933</v>
       </c>
       <c r="R77" t="n">
-        <v>7039744</v>
+        <v>7039394</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9160,7 +9141,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9170,12 +9151,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9202,10 +9183,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122425284</v>
+        <v>122428034</v>
       </c>
       <c r="B78" t="n">
-        <v>79732</v>
+        <v>57532</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9218,37 +9199,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562657</v>
+        <v>562674</v>
       </c>
       <c r="R78" t="n">
-        <v>7039870</v>
+        <v>7039543</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9275,9 +9265,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122425516</v>
+        <v>122425405</v>
       </c>
       <c r="B36" t="n">
-        <v>57379</v>
+        <v>74752</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4476,42 +4476,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562706</v>
+        <v>562648</v>
       </c>
       <c r="R36" t="n">
-        <v>7039810</v>
+        <v>7039865</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4538,24 +4533,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,22 +4550,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122430719</v>
+        <v>122425331</v>
       </c>
       <c r="B37" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4598,42 +4578,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562835</v>
+        <v>562650</v>
       </c>
       <c r="R37" t="n">
-        <v>7039750</v>
+        <v>7039856</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4660,24 +4635,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4692,19 +4652,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429005</v>
+        <v>122425516</v>
       </c>
       <c r="B38" t="n">
         <v>57379</v>
@@ -4740,7 +4700,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4749,13 +4709,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562522</v>
+        <v>562706</v>
       </c>
       <c r="R38" t="n">
-        <v>7039596</v>
+        <v>7039810</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,14 +4742,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4804,22 +4774,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425754</v>
+        <v>122430719</v>
       </c>
       <c r="B39" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4832,16 +4802,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4852,7 +4822,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4861,13 +4831,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562652</v>
+        <v>562835</v>
       </c>
       <c r="R39" t="n">
-        <v>7039805</v>
+        <v>7039750</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4894,14 +4864,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4916,22 +4896,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122425405</v>
+        <v>122429005</v>
       </c>
       <c r="B40" t="n">
-        <v>74752</v>
+        <v>57379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4944,34 +4924,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562648</v>
+        <v>562522</v>
       </c>
       <c r="R40" t="n">
-        <v>7039865</v>
+        <v>7039596</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5004,6 +4989,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5030,10 +5020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122425331</v>
+        <v>122425754</v>
       </c>
       <c r="B41" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5046,34 +5036,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562650</v>
+        <v>562652</v>
       </c>
       <c r="R41" t="n">
-        <v>7039856</v>
+        <v>7039805</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5106,6 +5101,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6144,10 +6144,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122430816</v>
+        <v>122429819</v>
       </c>
       <c r="B51" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6160,42 +6160,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562845</v>
+        <v>562600</v>
       </c>
       <c r="R51" t="n">
-        <v>7039809</v>
+        <v>7039877</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6222,19 +6217,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6249,22 +6234,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122428711</v>
+        <v>122425310</v>
       </c>
       <c r="B52" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6277,39 +6262,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562889</v>
+        <v>562650</v>
       </c>
       <c r="R52" t="n">
-        <v>7039463</v>
+        <v>7039868</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6341,7 +6321,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6351,12 +6331,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6383,7 +6358,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122426422</v>
+        <v>122430816</v>
       </c>
       <c r="B53" t="n">
         <v>57379</v>
@@ -6419,7 +6394,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6428,10 +6403,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562642</v>
+        <v>562845</v>
       </c>
       <c r="R53" t="n">
-        <v>7039716</v>
+        <v>7039809</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6463,7 +6438,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6473,12 +6448,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6505,10 +6475,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122429819</v>
+        <v>122428711</v>
       </c>
       <c r="B54" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6521,37 +6491,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562600</v>
+        <v>562889</v>
       </c>
       <c r="R54" t="n">
-        <v>7039877</v>
+        <v>7039463</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6578,9 +6553,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6595,22 +6585,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122425310</v>
+        <v>122426422</v>
       </c>
       <c r="B55" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6623,34 +6613,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562650</v>
+        <v>562642</v>
       </c>
       <c r="R55" t="n">
-        <v>7039868</v>
+        <v>7039716</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6682,7 +6677,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6692,7 +6687,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430397</v>
+        <v>122430183</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1041,11 +1041,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1059,7 +1054,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562890</v>
+        <v>562911</v>
       </c>
       <c r="R5" t="n">
-        <v>7039728</v>
+        <v>7039598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1108,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122430062</v>
+        <v>122430816</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,37 +1156,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562624</v>
+        <v>562845</v>
       </c>
       <c r="R6" t="n">
-        <v>7039856</v>
+        <v>7039809</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,9 +1213,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1240,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425397</v>
+        <v>122427605</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1265,11 +1270,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562662</v>
+        <v>562687</v>
       </c>
       <c r="R7" t="n">
-        <v>7039854</v>
+        <v>7039594</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1357,22 +1357,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429000</v>
+        <v>122428692</v>
       </c>
       <c r="B8" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,37 +1385,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562984</v>
+        <v>562502</v>
       </c>
       <c r="R8" t="n">
-        <v>7039447</v>
+        <v>7039635</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,19 +1442,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:08</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1464,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122426079</v>
+        <v>122429596</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,21 +1492,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562676</v>
+        <v>562565</v>
       </c>
       <c r="R9" t="n">
-        <v>7039760</v>
+        <v>7039844</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1583,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122427824</v>
+        <v>122429240</v>
       </c>
       <c r="B10" t="n">
-        <v>79732</v>
+        <v>78388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,21 +1589,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,13 +1608,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562770</v>
+        <v>562497</v>
       </c>
       <c r="R10" t="n">
-        <v>7039566</v>
+        <v>7039642</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,19 +1641,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,22 +1658,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430036</v>
+        <v>122426079</v>
       </c>
       <c r="B11" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,21 +1686,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562621</v>
+        <v>562676</v>
       </c>
       <c r="R11" t="n">
-        <v>7039854</v>
+        <v>7039760</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1797,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429240</v>
+        <v>122425191</v>
       </c>
       <c r="B12" t="n">
-        <v>78387</v>
+        <v>79733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,34 +1783,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562497</v>
+        <v>562649</v>
       </c>
       <c r="R12" t="n">
-        <v>7039642</v>
+        <v>7039883</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1899,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122430183</v>
+        <v>122425536</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,39 +1880,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562911</v>
+        <v>562710</v>
       </c>
       <c r="R13" t="n">
-        <v>7039598</v>
+        <v>7039834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1934,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,12 +1944,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,22 +1959,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122427407</v>
+        <v>122429996</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,42 +1987,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562761</v>
+        <v>562622</v>
       </c>
       <c r="R14" t="n">
-        <v>7039655</v>
+        <v>7039843</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,24 +2039,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,22 +2056,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122427566</v>
+        <v>122427618</v>
       </c>
       <c r="B15" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,34 +2084,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562663</v>
+        <v>562674</v>
       </c>
       <c r="R15" t="n">
-        <v>7039574</v>
+        <v>7039582</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,6 +2144,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122427645</v>
+        <v>122429998</v>
       </c>
       <c r="B16" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,34 +2191,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562693</v>
+        <v>562999</v>
       </c>
       <c r="R16" t="n">
-        <v>7039587</v>
+        <v>7039523</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,7 +2250,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2260,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,22 +2280,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122425617</v>
+        <v>122426351</v>
       </c>
       <c r="B17" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,37 +2308,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562648</v>
+        <v>562771</v>
       </c>
       <c r="R17" t="n">
-        <v>7039837</v>
+        <v>7039744</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,9 +2365,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122425539</v>
+        <v>122425544</v>
       </c>
       <c r="B18" t="n">
-        <v>79732</v>
+        <v>78388</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2475,21 +2425,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,13 +2444,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562651</v>
+        <v>562672</v>
       </c>
       <c r="R18" t="n">
-        <v>7039827</v>
+        <v>7039840</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,9 +2477,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,22 +2504,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122428173</v>
+        <v>122426080</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2577,39 +2532,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562701</v>
+        <v>562743</v>
       </c>
       <c r="R19" t="n">
-        <v>7039441</v>
+        <v>7039807</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,7 +2586,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,12 +2596,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122427605</v>
+        <v>122429588</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,42 +2639,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562687</v>
+        <v>562549</v>
       </c>
       <c r="R20" t="n">
-        <v>7039594</v>
+        <v>7039854</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,24 +2691,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,22 +2708,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122428692</v>
+        <v>122425539</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,39 +2736,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562502</v>
+        <v>562651</v>
       </c>
       <c r="R21" t="n">
-        <v>7039635</v>
+        <v>7039827</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2886,11 +2791,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,10 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122425700</v>
+        <v>122425754</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,16 +2833,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2953,7 +2848,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2962,13 +2857,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562678</v>
+        <v>562652</v>
       </c>
       <c r="R22" t="n">
-        <v>7039813</v>
+        <v>7039805</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2995,24 +2890,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122427953</v>
+        <v>122428307</v>
       </c>
       <c r="B23" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3055,34 +2940,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562661</v>
+        <v>562557</v>
       </c>
       <c r="R23" t="n">
-        <v>7039580</v>
+        <v>7039552</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3115,6 +3000,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122425278</v>
+        <v>122425284</v>
       </c>
       <c r="B24" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,11 +3049,6 @@
       <c r="E24" t="n">
         <v>6458</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -3181,13 +3066,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562673</v>
+        <v>562657</v>
       </c>
       <c r="R24" t="n">
-        <v>7039869</v>
+        <v>7039870</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,19 +3099,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,22 +3116,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122427618</v>
+        <v>122427824</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,42 +3144,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562674</v>
+        <v>562770</v>
       </c>
       <c r="R25" t="n">
-        <v>7039582</v>
+        <v>7039566</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3331,14 +3196,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3353,19 +3223,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429998</v>
+        <v>122427743</v>
       </c>
       <c r="B26" t="n">
         <v>57379</v>
@@ -3383,11 +3253,6 @@
       <c r="E26" t="n">
         <v>100109</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3406,14 +3271,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562999</v>
+        <v>562670</v>
       </c>
       <c r="R26" t="n">
-        <v>7039523</v>
+        <v>7039613</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3445,7 +3310,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,12 +3320,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,22 +3340,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122425242</v>
+        <v>122428074</v>
       </c>
       <c r="B27" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3503,37 +3368,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562659</v>
+        <v>562763</v>
       </c>
       <c r="R27" t="n">
-        <v>7039871</v>
+        <v>7039478</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3560,9 +3425,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3577,22 +3457,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122426059</v>
+        <v>122428645</v>
       </c>
       <c r="B28" t="n">
-        <v>82438</v>
+        <v>78652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,21 +3485,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3629,10 +3504,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562673</v>
+        <v>562509</v>
       </c>
       <c r="R28" t="n">
-        <v>7039763</v>
+        <v>7039629</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3691,10 +3566,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122426080</v>
+        <v>122428173</v>
       </c>
       <c r="B29" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3707,34 +3582,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562743</v>
+        <v>562701</v>
       </c>
       <c r="R29" t="n">
-        <v>7039807</v>
+        <v>7039441</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,7 +3641,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3776,7 +3651,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3803,10 +3683,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122425284</v>
+        <v>122425516</v>
       </c>
       <c r="B30" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3819,37 +3699,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562657</v>
+        <v>562706</v>
       </c>
       <c r="R30" t="n">
-        <v>7039870</v>
+        <v>7039810</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3876,9 +3756,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3893,22 +3788,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425544</v>
+        <v>122426059</v>
       </c>
       <c r="B31" t="n">
-        <v>78387</v>
+        <v>82439</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3921,21 +3816,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>1312</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3945,13 +3835,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562672</v>
+        <v>562673</v>
       </c>
       <c r="R31" t="n">
-        <v>7039840</v>
+        <v>7039763</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3978,19 +3868,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4005,22 +3885,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122425703</v>
+        <v>122427459</v>
       </c>
       <c r="B32" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4029,31 +3909,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4062,13 +3946,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562654</v>
+        <v>562755</v>
       </c>
       <c r="R32" t="n">
-        <v>7039819</v>
+        <v>7039631</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4095,9 +3979,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,22 +4006,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122426351</v>
+        <v>122425331</v>
       </c>
       <c r="B33" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,42 +4034,32 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562771</v>
+        <v>562650</v>
       </c>
       <c r="R33" t="n">
-        <v>7039744</v>
+        <v>7039856</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4202,24 +4086,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,22 +4103,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122427401</v>
+        <v>122428711</v>
       </c>
       <c r="B34" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4262,37 +4131,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562674</v>
+        <v>562889</v>
       </c>
       <c r="R34" t="n">
-        <v>7039653</v>
+        <v>7039463</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,9 +4188,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4336,22 +4220,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122428148</v>
+        <v>122425700</v>
       </c>
       <c r="B35" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4364,34 +4248,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562707</v>
+        <v>562678</v>
       </c>
       <c r="R35" t="n">
-        <v>7039456</v>
+        <v>7039813</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4423,7 +4307,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4433,7 +4317,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4448,22 +4337,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122425405</v>
+        <v>122428796</v>
       </c>
       <c r="B36" t="n">
-        <v>74752</v>
+        <v>57379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4476,37 +4365,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562648</v>
+        <v>563001</v>
       </c>
       <c r="R36" t="n">
-        <v>7039865</v>
+        <v>7039421</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4533,9 +4422,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4550,22 +4454,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122425331</v>
+        <v>122429992</v>
       </c>
       <c r="B37" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4578,21 +4482,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4602,10 +4501,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562650</v>
+        <v>562620</v>
       </c>
       <c r="R37" t="n">
-        <v>7039856</v>
+        <v>7039839</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4664,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122425516</v>
+        <v>122429000</v>
       </c>
       <c r="B38" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4680,39 +4579,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562706</v>
+        <v>562984</v>
       </c>
       <c r="R38" t="n">
-        <v>7039810</v>
+        <v>7039447</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4744,7 +4633,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4754,12 +4643,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4774,22 +4658,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122430719</v>
+        <v>122425780</v>
       </c>
       <c r="B39" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,39 +4686,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562835</v>
+        <v>562725</v>
       </c>
       <c r="R39" t="n">
-        <v>7039750</v>
+        <v>7039812</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4866,7 +4740,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4876,12 +4750,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4896,19 +4770,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122429005</v>
+        <v>122427407</v>
       </c>
       <c r="B40" t="n">
         <v>57379</v>
@@ -4926,11 +4800,6 @@
       <c r="E40" t="n">
         <v>100109</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4944,7 +4813,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4953,13 +4822,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562522</v>
+        <v>562761</v>
       </c>
       <c r="R40" t="n">
-        <v>7039596</v>
+        <v>7039655</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4986,14 +4855,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,22 +4887,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122425754</v>
+        <v>122425242</v>
       </c>
       <c r="B41" t="n">
-        <v>57395</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5036,39 +4915,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562652</v>
+        <v>562659</v>
       </c>
       <c r="R41" t="n">
-        <v>7039805</v>
+        <v>7039871</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5101,11 +4970,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5132,7 +4996,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122427985</v>
+        <v>122429005</v>
       </c>
       <c r="B42" t="n">
         <v>57379</v>
@@ -5150,11 +5014,6 @@
       <c r="E42" t="n">
         <v>100109</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5168,7 +5027,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5177,13 +5036,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562695</v>
+        <v>562522</v>
       </c>
       <c r="R42" t="n">
-        <v>7039574</v>
+        <v>7039596</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5210,24 +5069,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5242,22 +5091,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122425536</v>
+        <v>122427985</v>
       </c>
       <c r="B43" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5270,34 +5119,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562710</v>
+        <v>562695</v>
       </c>
       <c r="R43" t="n">
-        <v>7039834</v>
+        <v>7039574</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5329,7 +5178,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5339,7 +5188,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5366,10 +5220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122429996</v>
+        <v>122427645</v>
       </c>
       <c r="B44" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5384,11 +5238,6 @@
       <c r="E44" t="n">
         <v>6458</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5406,13 +5255,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562622</v>
+        <v>562693</v>
       </c>
       <c r="R44" t="n">
-        <v>7039843</v>
+        <v>7039587</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5439,9 +5288,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,22 +5315,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122429588</v>
+        <v>122425328</v>
       </c>
       <c r="B45" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5486,11 +5345,6 @@
       <c r="E45" t="n">
         <v>6458</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5504,17 +5358,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562549</v>
+        <v>562678</v>
       </c>
       <c r="R45" t="n">
-        <v>7039854</v>
+        <v>7039868</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5541,9 +5395,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5558,22 +5422,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428645</v>
+        <v>122425617</v>
       </c>
       <c r="B46" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5586,21 +5450,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5610,10 +5469,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562509</v>
+        <v>562648</v>
       </c>
       <c r="R46" t="n">
-        <v>7039629</v>
+        <v>7039837</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5672,7 +5531,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122426220</v>
+        <v>122428693</v>
       </c>
       <c r="B47" t="n">
         <v>57379</v>
@@ -5690,11 +5549,6 @@
       <c r="E47" t="n">
         <v>100109</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5713,17 +5567,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562671</v>
+        <v>562933</v>
       </c>
       <c r="R47" t="n">
-        <v>7039729</v>
+        <v>7039394</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5750,14 +5604,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack, gammeltall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5772,22 +5636,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122427473</v>
+        <v>122428034</v>
       </c>
       <c r="B48" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5800,27 +5664,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5829,13 +5692,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562684</v>
+        <v>562674</v>
       </c>
       <c r="R48" t="n">
-        <v>7039617</v>
+        <v>7039543</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5862,14 +5725,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5884,22 +5752,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122429056</v>
+        <v>122427401</v>
       </c>
       <c r="B49" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5912,42 +5780,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562996</v>
+        <v>562674</v>
       </c>
       <c r="R49" t="n">
-        <v>7039422</v>
+        <v>7039653</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5974,24 +5832,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6006,22 +5849,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122427459</v>
+        <v>122427566</v>
       </c>
       <c r="B50" t="n">
-        <v>98202</v>
+        <v>79733</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6030,55 +5873,36 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562755</v>
+        <v>562663</v>
       </c>
       <c r="R50" t="n">
-        <v>7039631</v>
+        <v>7039574</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6105,19 +5929,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6132,22 +5946,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122429819</v>
+        <v>122427953</v>
       </c>
       <c r="B51" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6160,21 +5974,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6184,10 +5993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562600</v>
+        <v>562661</v>
       </c>
       <c r="R51" t="n">
-        <v>7039877</v>
+        <v>7039580</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6246,10 +6055,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122425310</v>
+        <v>122430780</v>
       </c>
       <c r="B52" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6262,34 +6071,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562650</v>
+        <v>562903</v>
       </c>
       <c r="R52" t="n">
-        <v>7039868</v>
+        <v>7039567</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6321,7 +6130,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6331,7 +6140,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6346,19 +6155,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122430816</v>
+        <v>122426422</v>
       </c>
       <c r="B53" t="n">
         <v>57379</v>
@@ -6376,11 +6185,6 @@
       <c r="E53" t="n">
         <v>100109</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -6394,7 +6198,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6403,10 +6207,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562845</v>
+        <v>562642</v>
       </c>
       <c r="R53" t="n">
-        <v>7039809</v>
+        <v>7039716</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6438,7 +6242,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6448,7 +6252,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6475,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428711</v>
+        <v>122429969</v>
       </c>
       <c r="B54" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6491,42 +6300,32 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562889</v>
+        <v>562604</v>
       </c>
       <c r="R54" t="n">
-        <v>7039463</v>
+        <v>7039850</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6553,24 +6352,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6585,22 +6369,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122426422</v>
+        <v>122427418</v>
       </c>
       <c r="B55" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6613,42 +6397,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562642</v>
+        <v>562680</v>
       </c>
       <c r="R55" t="n">
-        <v>7039716</v>
+        <v>7039626</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6675,24 +6449,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6707,22 +6466,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430780</v>
+        <v>122429855</v>
       </c>
       <c r="B56" t="n">
-        <v>57395</v>
+        <v>79733</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6735,42 +6494,32 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562903</v>
+        <v>562619</v>
       </c>
       <c r="R56" t="n">
-        <v>7039567</v>
+        <v>7039840</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6797,19 +6546,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6824,22 +6563,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427626</v>
+        <v>122429056</v>
       </c>
       <c r="B57" t="n">
-        <v>78387</v>
+        <v>57379</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6852,34 +6591,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562773</v>
+        <v>562996</v>
       </c>
       <c r="R57" t="n">
-        <v>7039605</v>
+        <v>7039422</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6911,7 +6650,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6921,7 +6660,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6948,10 +6692,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122427418</v>
+        <v>122427473</v>
       </c>
       <c r="B58" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6964,34 +6708,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562680</v>
+        <v>562684</v>
       </c>
       <c r="R58" t="n">
-        <v>7039626</v>
+        <v>7039617</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7024,6 +6768,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7050,10 +6799,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122429855</v>
+        <v>122430036</v>
       </c>
       <c r="B59" t="n">
-        <v>79732</v>
+        <v>79734</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7066,21 +6815,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7090,10 +6834,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562619</v>
+        <v>562621</v>
       </c>
       <c r="R59" t="n">
-        <v>7039840</v>
+        <v>7039854</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7152,10 +6896,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122429596</v>
+        <v>122430274</v>
       </c>
       <c r="B60" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7168,37 +6912,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562565</v>
+        <v>562903</v>
       </c>
       <c r="R60" t="n">
-        <v>7039844</v>
+        <v>7039649</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7225,9 +6969,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7242,22 +7001,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122430274</v>
+        <v>122428124</v>
       </c>
       <c r="B61" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7270,42 +7029,32 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562903</v>
+        <v>562630</v>
       </c>
       <c r="R61" t="n">
-        <v>7039649</v>
+        <v>7039565</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7332,24 +7081,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7364,19 +7098,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122425414</v>
+        <v>122426220</v>
       </c>
       <c r="B62" t="n">
         <v>57379</v>
@@ -7394,11 +7128,6 @@
       <c r="E62" t="n">
         <v>100109</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -7421,13 +7150,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562678</v>
+        <v>562671</v>
       </c>
       <c r="R62" t="n">
-        <v>7039855</v>
+        <v>7039729</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7454,24 +7183,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7486,19 +7205,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122428074</v>
+        <v>122425414</v>
       </c>
       <c r="B63" t="n">
         <v>57379</v>
@@ -7516,11 +7235,6 @@
       <c r="E63" t="n">
         <v>100109</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -7543,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562763</v>
+        <v>562678</v>
       </c>
       <c r="R63" t="n">
-        <v>7039478</v>
+        <v>7039855</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7578,7 +7292,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7588,7 +7302,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7608,22 +7322,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122429992</v>
+        <v>122427703</v>
       </c>
       <c r="B64" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7636,37 +7350,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562620</v>
+        <v>562784</v>
       </c>
       <c r="R64" t="n">
-        <v>7039839</v>
+        <v>7039590</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7693,9 +7407,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7710,22 +7439,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122430000</v>
+        <v>122429819</v>
       </c>
       <c r="B65" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7738,21 +7467,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7762,10 +7486,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562623</v>
+        <v>562600</v>
       </c>
       <c r="R65" t="n">
-        <v>7039843</v>
+        <v>7039877</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7824,10 +7548,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122425191</v>
+        <v>122425855</v>
       </c>
       <c r="B66" t="n">
-        <v>79732</v>
+        <v>90831</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7840,37 +7564,32 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562649</v>
+        <v>562731</v>
       </c>
       <c r="R66" t="n">
-        <v>7039883</v>
+        <v>7039827</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7897,9 +7616,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7914,22 +7643,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122428796</v>
+        <v>122430000</v>
       </c>
       <c r="B67" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7942,42 +7671,32 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563001</v>
+        <v>562623</v>
       </c>
       <c r="R67" t="n">
-        <v>7039421</v>
+        <v>7039843</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8004,24 +7723,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8036,22 +7740,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122426187</v>
+        <v>122427626</v>
       </c>
       <c r="B68" t="n">
-        <v>79732</v>
+        <v>78388</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8064,21 +7768,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8088,10 +7787,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562759</v>
+        <v>562773</v>
       </c>
       <c r="R68" t="n">
-        <v>7039787</v>
+        <v>7039605</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8123,7 +7822,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8133,7 +7832,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8148,22 +7847,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122425780</v>
+        <v>122425405</v>
       </c>
       <c r="B69" t="n">
-        <v>79732</v>
+        <v>74753</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8176,21 +7875,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8200,13 +7894,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562725</v>
+        <v>562648</v>
       </c>
       <c r="R69" t="n">
-        <v>7039812</v>
+        <v>7039865</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8233,24 +7927,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8265,22 +7944,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122425328</v>
+        <v>122428148</v>
       </c>
       <c r="B70" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8295,11 +7974,6 @@
       <c r="E70" t="n">
         <v>6458</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8313,14 +7987,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562678</v>
+        <v>562707</v>
       </c>
       <c r="R70" t="n">
-        <v>7039868</v>
+        <v>7039456</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8352,7 +8026,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8362,7 +8036,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8389,10 +8063,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122427703</v>
+        <v>122425703</v>
       </c>
       <c r="B71" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8405,16 +8079,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8425,7 +8094,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8434,13 +8103,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562784</v>
+        <v>562654</v>
       </c>
       <c r="R71" t="n">
-        <v>7039590</v>
+        <v>7039819</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8467,24 +8136,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8499,22 +8153,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122429969</v>
+        <v>122430397</v>
       </c>
       <c r="B72" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8527,37 +8181,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562604</v>
+        <v>562890</v>
       </c>
       <c r="R72" t="n">
-        <v>7039850</v>
+        <v>7039728</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8584,9 +8238,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8601,22 +8270,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122428124</v>
+        <v>122425310</v>
       </c>
       <c r="B73" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8629,21 +8298,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8653,13 +8317,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562630</v>
+        <v>562650</v>
       </c>
       <c r="R73" t="n">
-        <v>7039565</v>
+        <v>7039868</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8686,9 +8350,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8703,22 +8377,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122425855</v>
+        <v>122426187</v>
       </c>
       <c r="B74" t="n">
-        <v>90826</v>
+        <v>79733</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8731,21 +8405,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8755,10 +8424,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562731</v>
+        <v>562759</v>
       </c>
       <c r="R74" t="n">
-        <v>7039827</v>
+        <v>7039787</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8790,7 +8459,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8800,7 +8469,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8827,10 +8496,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122428307</v>
+        <v>122425278</v>
       </c>
       <c r="B75" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8843,42 +8512,32 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562557</v>
+        <v>562673</v>
       </c>
       <c r="R75" t="n">
-        <v>7039552</v>
+        <v>7039869</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8905,14 +8564,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8927,22 +8591,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122427743</v>
+        <v>122430062</v>
       </c>
       <c r="B76" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8955,42 +8619,32 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562670</v>
+        <v>562624</v>
       </c>
       <c r="R76" t="n">
-        <v>7039613</v>
+        <v>7039856</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9017,24 +8671,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9049,19 +8688,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122428693</v>
+        <v>122430719</v>
       </c>
       <c r="B77" t="n">
         <v>57379</v>
@@ -9079,11 +8718,6 @@
       <c r="E77" t="n">
         <v>100109</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -9102,14 +8736,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562933</v>
+        <v>562835</v>
       </c>
       <c r="R77" t="n">
-        <v>7039394</v>
+        <v>7039750</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9141,7 +8775,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9151,7 +8785,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -9171,22 +8805,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122428034</v>
+        <v>122425397</v>
       </c>
       <c r="B78" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9199,31 +8833,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9232,10 +8857,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562674</v>
+        <v>562662</v>
       </c>
       <c r="R78" t="n">
-        <v>7039543</v>
+        <v>7039854</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9267,7 +8892,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9277,7 +8902,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +8922,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -2292,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122426351</v>
+        <v>122426080</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2308,34 +2308,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562771</v>
+        <v>562743</v>
       </c>
       <c r="R17" t="n">
-        <v>7039744</v>
+        <v>7039807</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,7 +2362,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2377,12 +2372,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122426080</v>
+        <v>122426351</v>
       </c>
       <c r="B19" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,29 +2522,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562743</v>
+        <v>562771</v>
       </c>
       <c r="R19" t="n">
-        <v>7039807</v>
+        <v>7039744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2581,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2596,7 +2591,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122429588</v>
+        <v>122425754</v>
       </c>
       <c r="B20" t="n">
-        <v>79733</v>
+        <v>57395</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,29 +2639,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562549</v>
+        <v>562652</v>
       </c>
       <c r="R20" t="n">
-        <v>7039854</v>
+        <v>7039805</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2694,6 +2699,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122425754</v>
+        <v>122428307</v>
       </c>
       <c r="B22" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2833,11 +2843,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,7 +2858,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562652</v>
+        <v>562557</v>
       </c>
       <c r="R22" t="n">
-        <v>7039805</v>
+        <v>7039552</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2897,7 +2907,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122428307</v>
+        <v>122425284</v>
       </c>
       <c r="B23" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,34 +2950,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562557</v>
+        <v>562657</v>
       </c>
       <c r="R23" t="n">
-        <v>7039552</v>
+        <v>7039870</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3000,11 +3005,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,7 +3031,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122425284</v>
+        <v>122429588</v>
       </c>
       <c r="B24" t="n">
         <v>79733</v>
@@ -3062,14 +3062,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562657</v>
+        <v>562549</v>
       </c>
       <c r="R24" t="n">
-        <v>7039870</v>
+        <v>7039854</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122427743</v>
+        <v>122428074</v>
       </c>
       <c r="B26" t="n">
         <v>57379</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562670</v>
+        <v>562763</v>
       </c>
       <c r="R26" t="n">
-        <v>7039613</v>
+        <v>7039478</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,19 +3340,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122428074</v>
+        <v>122427743</v>
       </c>
       <c r="B27" t="n">
         <v>57379</v>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562763</v>
+        <v>562670</v>
       </c>
       <c r="R27" t="n">
-        <v>7039478</v>
+        <v>7039613</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,12 +3457,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4466,10 +4466,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122429992</v>
+        <v>122427407</v>
       </c>
       <c r="B37" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4482,32 +4482,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562620</v>
+        <v>562761</v>
       </c>
       <c r="R37" t="n">
-        <v>7039839</v>
+        <v>7039655</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,9 +4539,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4551,19 +4571,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429000</v>
+        <v>122429992</v>
       </c>
       <c r="B38" t="n">
         <v>79733</v>
@@ -4594,17 +4614,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562984</v>
+        <v>562620</v>
       </c>
       <c r="R38" t="n">
-        <v>7039447</v>
+        <v>7039839</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4631,19 +4651,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,19 +4668,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425780</v>
+        <v>122429000</v>
       </c>
       <c r="B39" t="n">
         <v>79733</v>
@@ -4701,14 +4711,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562725</v>
+        <v>562984</v>
       </c>
       <c r="R39" t="n">
-        <v>7039812</v>
+        <v>7039447</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4740,7 +4750,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4750,12 +4760,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,22 +4775,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122427407</v>
+        <v>122425780</v>
       </c>
       <c r="B40" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4798,34 +4803,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562761</v>
+        <v>562725</v>
       </c>
       <c r="R40" t="n">
-        <v>7039655</v>
+        <v>7039812</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -8282,10 +8282,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122425310</v>
+        <v>122426187</v>
       </c>
       <c r="B73" t="n">
-        <v>78652</v>
+        <v>79733</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8298,16 +8298,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562650</v>
+        <v>562759</v>
       </c>
       <c r="R73" t="n">
-        <v>7039868</v>
+        <v>7039787</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8377,19 +8377,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122426187</v>
+        <v>122425278</v>
       </c>
       <c r="B74" t="n">
         <v>79733</v>
@@ -8420,14 +8420,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562759</v>
+        <v>562673</v>
       </c>
       <c r="R74" t="n">
-        <v>7039787</v>
+        <v>7039869</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8496,10 +8496,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122425278</v>
+        <v>122425310</v>
       </c>
       <c r="B75" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8512,29 +8512,29 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562673</v>
+        <v>562650</v>
       </c>
       <c r="R75" t="n">
-        <v>7039869</v>
+        <v>7039868</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8591,12 +8591,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122427824</v>
+        <v>122427743</v>
       </c>
       <c r="B25" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,29 +3144,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562770</v>
+        <v>562670</v>
       </c>
       <c r="R25" t="n">
-        <v>7039566</v>
+        <v>7039613</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3203,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3213,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,12 +3233,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3352,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122427743</v>
+        <v>122427824</v>
       </c>
       <c r="B27" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3368,34 +3378,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562670</v>
+        <v>562770</v>
       </c>
       <c r="R27" t="n">
-        <v>7039613</v>
+        <v>7039566</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3432,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3437,12 +3442,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,12 +3457,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122425516</v>
+        <v>122426059</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>82439</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3699,37 +3699,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562706</v>
+        <v>562673</v>
       </c>
       <c r="R30" t="n">
-        <v>7039810</v>
+        <v>7039763</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3756,24 +3751,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3788,22 +3768,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122426059</v>
+        <v>122427459</v>
       </c>
       <c r="B31" t="n">
-        <v>82439</v>
+        <v>98211</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,36 +3792,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562673</v>
+        <v>562755</v>
       </c>
       <c r="R31" t="n">
-        <v>7039763</v>
+        <v>7039631</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3868,9 +3862,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,22 +3889,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122427459</v>
+        <v>122425331</v>
       </c>
       <c r="B32" t="n">
-        <v>98211</v>
+        <v>78652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3909,50 +3913,36 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562755</v>
+        <v>562650</v>
       </c>
       <c r="R32" t="n">
-        <v>7039631</v>
+        <v>7039856</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3979,19 +3969,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,22 +3986,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122425331</v>
+        <v>122425516</v>
       </c>
       <c r="B33" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4034,32 +4014,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562650</v>
+        <v>562706</v>
       </c>
       <c r="R33" t="n">
-        <v>7039856</v>
+        <v>7039810</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4086,9 +4071,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4103,12 +4103,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4466,10 +4466,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122427407</v>
+        <v>122429992</v>
       </c>
       <c r="B37" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4482,37 +4482,32 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562761</v>
+        <v>562620</v>
       </c>
       <c r="R37" t="n">
-        <v>7039655</v>
+        <v>7039839</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4539,24 +4534,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4571,19 +4551,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429992</v>
+        <v>122429000</v>
       </c>
       <c r="B38" t="n">
         <v>79733</v>
@@ -4614,17 +4594,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562620</v>
+        <v>562984</v>
       </c>
       <c r="R38" t="n">
-        <v>7039839</v>
+        <v>7039447</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4651,9 +4631,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4668,19 +4658,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122429000</v>
+        <v>122425780</v>
       </c>
       <c r="B39" t="n">
         <v>79733</v>
@@ -4711,14 +4701,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562984</v>
+        <v>562725</v>
       </c>
       <c r="R39" t="n">
-        <v>7039447</v>
+        <v>7039812</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4750,7 +4740,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4760,7 +4750,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4775,22 +4770,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122425780</v>
+        <v>122427407</v>
       </c>
       <c r="B40" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4803,29 +4798,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562725</v>
+        <v>562761</v>
       </c>
       <c r="R40" t="n">
-        <v>7039812</v>
+        <v>7039655</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Lunglav på rönn</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5434,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122425617</v>
+        <v>122428693</v>
       </c>
       <c r="B46" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5450,32 +5450,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562648</v>
+        <v>562933</v>
       </c>
       <c r="R46" t="n">
-        <v>7039837</v>
+        <v>7039394</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5502,9 +5507,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5519,22 +5539,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428693</v>
+        <v>122427401</v>
       </c>
       <c r="B47" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5547,37 +5567,32 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562933</v>
+        <v>562674</v>
       </c>
       <c r="R47" t="n">
-        <v>7039394</v>
+        <v>7039653</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5604,24 +5619,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5636,22 +5636,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122428034</v>
+        <v>122427566</v>
       </c>
       <c r="B48" t="n">
-        <v>57532</v>
+        <v>79733</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5664,41 +5664,32 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562674</v>
+        <v>562663</v>
       </c>
       <c r="R48" t="n">
-        <v>7039543</v>
+        <v>7039574</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5725,19 +5716,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5752,22 +5733,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122427401</v>
+        <v>122427953</v>
       </c>
       <c r="B49" t="n">
-        <v>78652</v>
+        <v>79733</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5780,16 +5761,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562674</v>
+        <v>562661</v>
       </c>
       <c r="R49" t="n">
-        <v>7039653</v>
+        <v>7039580</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5861,7 +5842,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122427566</v>
+        <v>122425617</v>
       </c>
       <c r="B50" t="n">
         <v>79733</v>
@@ -5896,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562663</v>
+        <v>562648</v>
       </c>
       <c r="R50" t="n">
-        <v>7039574</v>
+        <v>7039837</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5958,10 +5939,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122427953</v>
+        <v>122428034</v>
       </c>
       <c r="B51" t="n">
-        <v>79733</v>
+        <v>57532</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5974,32 +5955,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562661</v>
+        <v>562674</v>
       </c>
       <c r="R51" t="n">
-        <v>7039580</v>
+        <v>7039543</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6026,9 +6016,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6043,12 +6043,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430183</v>
+        <v>122430780</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,11 +1039,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562911</v>
+        <v>562903</v>
       </c>
       <c r="R5" t="n">
-        <v>7039598</v>
+        <v>7039567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122430816</v>
+        <v>122426220</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,6 +1158,11 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1180,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562845</v>
+        <v>562671</v>
       </c>
       <c r="R6" t="n">
-        <v>7039809</v>
+        <v>7039729</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,19 +1218,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:15</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1240,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427605</v>
+        <v>122425397</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,6 +1270,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562687</v>
+        <v>562662</v>
       </c>
       <c r="R7" t="n">
-        <v>7039594</v>
+        <v>7039854</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1342,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1357,22 +1362,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122428692</v>
+        <v>122427626</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>78392</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,37 +1390,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562502</v>
+        <v>562773</v>
       </c>
       <c r="R8" t="n">
-        <v>7039635</v>
+        <v>7039605</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,14 +1447,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,22 +1474,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429596</v>
+        <v>122425310</v>
       </c>
       <c r="B9" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,16 +1502,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,13 +1526,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562565</v>
+        <v>562650</v>
       </c>
       <c r="R9" t="n">
-        <v>7039844</v>
+        <v>7039868</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,9 +1559,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1586,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429240</v>
+        <v>122428645</v>
       </c>
       <c r="B10" t="n">
-        <v>78388</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,16 +1614,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562497</v>
+        <v>562509</v>
       </c>
       <c r="R10" t="n">
-        <v>7039642</v>
+        <v>7039629</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1670,10 +1700,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122426079</v>
+        <v>122425331</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,6 +1718,11 @@
       <c r="E11" t="n">
         <v>6425</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1705,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562676</v>
+        <v>562650</v>
       </c>
       <c r="R11" t="n">
-        <v>7039760</v>
+        <v>7039856</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1767,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122425191</v>
+        <v>122428173</v>
       </c>
       <c r="B12" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,32 +1818,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562649</v>
+        <v>562701</v>
       </c>
       <c r="R12" t="n">
-        <v>7039883</v>
+        <v>7039441</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,9 +1880,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,22 +1912,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122425536</v>
+        <v>122428711</v>
       </c>
       <c r="B13" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,29 +1940,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562710</v>
+        <v>562889</v>
       </c>
       <c r="R13" t="n">
-        <v>7039834</v>
+        <v>7039463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1944,7 +2014,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,22 +2034,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122429996</v>
+        <v>122426422</v>
       </c>
       <c r="B14" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,32 +2062,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562622</v>
+        <v>562642</v>
       </c>
       <c r="R14" t="n">
-        <v>7039843</v>
+        <v>7039716</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,9 +2124,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,22 +2156,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122427618</v>
+        <v>122425754</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,11 +2184,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2099,7 +2204,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2108,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562674</v>
+        <v>562652</v>
       </c>
       <c r="R15" t="n">
-        <v>7039582</v>
+        <v>7039805</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2148,7 +2253,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122429998</v>
+        <v>122427618</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,6 +2298,11 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2211,17 +2321,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562999</v>
+        <v>562674</v>
       </c>
       <c r="R16" t="n">
-        <v>7039523</v>
+        <v>7039582</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,24 +2358,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,22 +2380,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122426080</v>
+        <v>122430062</v>
       </c>
       <c r="B17" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,6 +2410,11 @@
       <c r="E17" t="n">
         <v>6458</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -2327,13 +2432,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562743</v>
+        <v>562624</v>
       </c>
       <c r="R17" t="n">
-        <v>7039807</v>
+        <v>7039856</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2360,19 +2465,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,22 +2482,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122425544</v>
+        <v>122426059</v>
       </c>
       <c r="B18" t="n">
-        <v>78388</v>
+        <v>82443</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,16 +2510,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2434,13 +2534,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562672</v>
+        <v>562673</v>
       </c>
       <c r="R18" t="n">
-        <v>7039840</v>
+        <v>7039763</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,19 +2567,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,22 +2584,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122426351</v>
+        <v>122425855</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2522,34 +2612,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562771</v>
+        <v>562731</v>
       </c>
       <c r="R19" t="n">
-        <v>7039744</v>
+        <v>7039827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2591,12 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2708,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122425754</v>
+        <v>122425242</v>
       </c>
       <c r="B20" t="n">
-        <v>57395</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,34 +2724,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562652</v>
+        <v>562659</v>
       </c>
       <c r="R20" t="n">
-        <v>7039805</v>
+        <v>7039871</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2699,11 +2784,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122425539</v>
+        <v>122427473</v>
       </c>
       <c r="B21" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,29 +2826,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562651</v>
+        <v>562684</v>
       </c>
       <c r="R21" t="n">
-        <v>7039827</v>
+        <v>7039617</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2801,6 +2891,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2827,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122428307</v>
+        <v>122429000</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,37 +2938,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562557</v>
+        <v>562984</v>
       </c>
       <c r="R22" t="n">
-        <v>7039552</v>
+        <v>7039447</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,14 +2995,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,22 +3022,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122425284</v>
+        <v>122427459</v>
       </c>
       <c r="B23" t="n">
-        <v>79733</v>
+        <v>98224</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2946,36 +3046,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562657</v>
+        <v>562755</v>
       </c>
       <c r="R23" t="n">
-        <v>7039870</v>
+        <v>7039631</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,9 +3121,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,22 +3148,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122429588</v>
+        <v>122427985</v>
       </c>
       <c r="B24" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3047,32 +3176,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562549</v>
+        <v>562695</v>
       </c>
       <c r="R24" t="n">
-        <v>7039854</v>
+        <v>7039574</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,9 +3238,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,22 +3270,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122427743</v>
+        <v>122427401</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,37 +3298,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562670</v>
+        <v>562674</v>
       </c>
       <c r="R25" t="n">
-        <v>7039613</v>
+        <v>7039653</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3201,24 +3355,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,22 +3372,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122428074</v>
+        <v>122429969</v>
       </c>
       <c r="B26" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,37 +3400,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562763</v>
+        <v>562604</v>
       </c>
       <c r="R26" t="n">
-        <v>7039478</v>
+        <v>7039850</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3318,24 +3457,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,22 +3474,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122427824</v>
+        <v>122427605</v>
       </c>
       <c r="B27" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3378,29 +3502,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562770</v>
+        <v>562687</v>
       </c>
       <c r="R27" t="n">
-        <v>7039566</v>
+        <v>7039594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3432,7 +3566,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3442,7 +3576,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,22 +3596,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122428645</v>
+        <v>122426351</v>
       </c>
       <c r="B28" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3485,32 +3624,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562509</v>
+        <v>562771</v>
       </c>
       <c r="R28" t="n">
-        <v>7039629</v>
+        <v>7039744</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3537,9 +3686,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,22 +3718,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122428173</v>
+        <v>122425405</v>
       </c>
       <c r="B29" t="n">
-        <v>57379</v>
+        <v>74757</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3582,37 +3746,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562701</v>
+        <v>562648</v>
       </c>
       <c r="R29" t="n">
-        <v>7039441</v>
+        <v>7039865</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,24 +3803,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,22 +3820,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122426059</v>
+        <v>122430000</v>
       </c>
       <c r="B30" t="n">
-        <v>82439</v>
+        <v>79737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3699,16 +3848,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3718,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562673</v>
+        <v>562623</v>
       </c>
       <c r="R30" t="n">
-        <v>7039763</v>
+        <v>7039843</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3780,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122427459</v>
+        <v>122429588</v>
       </c>
       <c r="B31" t="n">
-        <v>98211</v>
+        <v>79737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3792,50 +3946,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562755</v>
+        <v>562549</v>
       </c>
       <c r="R31" t="n">
-        <v>7039631</v>
+        <v>7039854</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3862,19 +4007,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,22 +4024,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122425331</v>
+        <v>122425703</v>
       </c>
       <c r="B32" t="n">
-        <v>78652</v>
+        <v>57399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3917,29 +4052,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562650</v>
+        <v>562654</v>
       </c>
       <c r="R32" t="n">
-        <v>7039856</v>
+        <v>7039819</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3998,10 +4143,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122425516</v>
+        <v>122429334</v>
       </c>
       <c r="B33" t="n">
-        <v>57379</v>
+        <v>78392</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4014,37 +4159,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562706</v>
+        <v>562497</v>
       </c>
       <c r="R33" t="n">
-        <v>7039810</v>
+        <v>7039642</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4071,24 +4216,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4103,22 +4233,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122428711</v>
+        <v>122428148</v>
       </c>
       <c r="B34" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4131,34 +4261,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562889</v>
+        <v>562707</v>
       </c>
       <c r="R34" t="n">
-        <v>7039463</v>
+        <v>7039456</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4320,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4200,12 +4330,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,22 +4345,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122425700</v>
+        <v>122428796</v>
       </c>
       <c r="B35" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4250,6 +4375,11 @@
       <c r="E35" t="n">
         <v>100109</v>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4268,14 +4398,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562678</v>
+        <v>563001</v>
       </c>
       <c r="R35" t="n">
-        <v>7039813</v>
+        <v>7039421</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4307,7 +4437,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4317,7 +4447,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4337,22 +4467,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122428796</v>
+        <v>122429596</v>
       </c>
       <c r="B36" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4365,37 +4495,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563001</v>
+        <v>562565</v>
       </c>
       <c r="R36" t="n">
-        <v>7039421</v>
+        <v>7039844</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4422,24 +4552,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4454,22 +4569,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122429992</v>
+        <v>122427645</v>
       </c>
       <c r="B37" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4484,6 +4599,11 @@
       <c r="E37" t="n">
         <v>6458</v>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -4501,13 +4621,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562620</v>
+        <v>562693</v>
       </c>
       <c r="R37" t="n">
-        <v>7039839</v>
+        <v>7039587</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4534,9 +4654,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4551,22 +4681,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429000</v>
+        <v>122425539</v>
       </c>
       <c r="B38" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4581,6 +4711,11 @@
       <c r="E38" t="n">
         <v>6458</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -4594,17 +4729,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562984</v>
+        <v>562651</v>
       </c>
       <c r="R38" t="n">
-        <v>7039447</v>
+        <v>7039827</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4631,19 +4766,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,22 +4783,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425780</v>
+        <v>122430274</v>
       </c>
       <c r="B39" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4686,29 +4811,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562725</v>
+        <v>562903</v>
       </c>
       <c r="R39" t="n">
-        <v>7039812</v>
+        <v>7039649</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4740,7 +4875,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4750,12 +4885,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Lunglav på rönn</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,22 +4905,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122427407</v>
+        <v>122429819</v>
       </c>
       <c r="B40" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4798,37 +4933,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562761</v>
+        <v>562600</v>
       </c>
       <c r="R40" t="n">
-        <v>7039655</v>
+        <v>7039877</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,24 +4990,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4887,22 +5007,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122425242</v>
+        <v>122428124</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4917,6 +5037,11 @@
       <c r="E41" t="n">
         <v>6458</v>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -4930,14 +5055,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562659</v>
+        <v>562630</v>
       </c>
       <c r="R41" t="n">
-        <v>7039871</v>
+        <v>7039565</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4996,10 +5121,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122429005</v>
+        <v>122425516</v>
       </c>
       <c r="B42" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5014,6 +5139,11 @@
       <c r="E42" t="n">
         <v>100109</v>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5027,7 +5157,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5036,13 +5166,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562522</v>
+        <v>562706</v>
       </c>
       <c r="R42" t="n">
-        <v>7039596</v>
+        <v>7039810</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5069,14 +5199,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5091,22 +5231,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427985</v>
+        <v>122427703</v>
       </c>
       <c r="B43" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5121,6 +5261,11 @@
       <c r="E43" t="n">
         <v>100109</v>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5143,10 +5288,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562695</v>
+        <v>562784</v>
       </c>
       <c r="R43" t="n">
-        <v>7039574</v>
+        <v>7039590</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5178,7 +5323,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5188,12 +5333,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5208,22 +5353,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122427645</v>
+        <v>122430397</v>
       </c>
       <c r="B44" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5236,29 +5381,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562693</v>
+        <v>562890</v>
       </c>
       <c r="R44" t="n">
-        <v>7039587</v>
+        <v>7039728</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,7 +5445,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5300,7 +5455,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5315,22 +5475,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122425328</v>
+        <v>122425278</v>
       </c>
       <c r="B45" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5345,6 +5505,11 @@
       <c r="E45" t="n">
         <v>6458</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5362,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562678</v>
+        <v>562673</v>
       </c>
       <c r="R45" t="n">
-        <v>7039868</v>
+        <v>7039869</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,7 +5562,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5407,7 +5572,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5434,10 +5599,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428693</v>
+        <v>122428074</v>
       </c>
       <c r="B46" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5452,6 +5617,11 @@
       <c r="E46" t="n">
         <v>100109</v>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -5470,14 +5640,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562933</v>
+        <v>562763</v>
       </c>
       <c r="R46" t="n">
-        <v>7039394</v>
+        <v>7039478</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5509,7 +5679,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5519,7 +5689,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5539,22 +5709,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122427401</v>
+        <v>122429992</v>
       </c>
       <c r="B47" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5567,16 +5737,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5586,10 +5761,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562674</v>
+        <v>562620</v>
       </c>
       <c r="R47" t="n">
-        <v>7039653</v>
+        <v>7039839</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5648,10 +5823,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122427566</v>
+        <v>122427953</v>
       </c>
       <c r="B48" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5666,6 +5841,11 @@
       <c r="E48" t="n">
         <v>6458</v>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5683,10 +5863,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562663</v>
+        <v>562661</v>
       </c>
       <c r="R48" t="n">
-        <v>7039574</v>
+        <v>7039580</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5745,10 +5925,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122427953</v>
+        <v>122425328</v>
       </c>
       <c r="B49" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5763,6 +5943,11 @@
       <c r="E49" t="n">
         <v>6458</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5776,17 +5961,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562661</v>
+        <v>562678</v>
       </c>
       <c r="R49" t="n">
-        <v>7039580</v>
+        <v>7039868</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5813,9 +5998,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5830,22 +6025,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122425617</v>
+        <v>122429005</v>
       </c>
       <c r="B50" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5858,29 +6053,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562648</v>
+        <v>562522</v>
       </c>
       <c r="R50" t="n">
-        <v>7039837</v>
+        <v>7039596</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5913,6 +6118,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5939,10 +6149,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122428034</v>
+        <v>122430816</v>
       </c>
       <c r="B51" t="n">
-        <v>57532</v>
+        <v>57383</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5955,26 +6165,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5983,10 +6194,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562674</v>
+        <v>562845</v>
       </c>
       <c r="R51" t="n">
-        <v>7039543</v>
+        <v>7039809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6018,7 +6229,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6028,7 +6239,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6043,22 +6254,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122430780</v>
+        <v>122429056</v>
       </c>
       <c r="B52" t="n">
-        <v>57395</v>
+        <v>57383</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6071,11 +6282,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6091,14 +6307,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562903</v>
+        <v>562996</v>
       </c>
       <c r="R52" t="n">
-        <v>7039567</v>
+        <v>7039422</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6130,7 +6346,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6140,7 +6356,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6155,22 +6376,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122426422</v>
+        <v>122427407</v>
       </c>
       <c r="B53" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6185,6 +6406,11 @@
       <c r="E53" t="n">
         <v>100109</v>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -6198,7 +6424,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6207,10 +6433,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562642</v>
+        <v>562761</v>
       </c>
       <c r="R53" t="n">
-        <v>7039716</v>
+        <v>7039655</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,7 +6468,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6252,12 +6478,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6272,22 +6498,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122429969</v>
+        <v>122430719</v>
       </c>
       <c r="B54" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6300,32 +6526,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562604</v>
+        <v>562835</v>
       </c>
       <c r="R54" t="n">
-        <v>7039850</v>
+        <v>7039750</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6352,9 +6588,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,22 +6620,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122427418</v>
+        <v>122425780</v>
       </c>
       <c r="B55" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6399,6 +6650,11 @@
       <c r="E55" t="n">
         <v>6458</v>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -6416,13 +6672,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562680</v>
+        <v>562725</v>
       </c>
       <c r="R55" t="n">
-        <v>7039626</v>
+        <v>7039812</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6449,9 +6705,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6466,22 +6737,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122429855</v>
+        <v>122426079</v>
       </c>
       <c r="B56" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6494,16 +6765,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6513,10 +6789,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562619</v>
+        <v>562676</v>
       </c>
       <c r="R56" t="n">
-        <v>7039840</v>
+        <v>7039760</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6575,10 +6851,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122429056</v>
+        <v>122425617</v>
       </c>
       <c r="B57" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6591,37 +6867,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562996</v>
+        <v>562648</v>
       </c>
       <c r="R57" t="n">
-        <v>7039422</v>
+        <v>7039837</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6648,24 +6924,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,22 +6941,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122427473</v>
+        <v>122429855</v>
       </c>
       <c r="B58" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6708,34 +6969,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562684</v>
+        <v>562619</v>
       </c>
       <c r="R58" t="n">
-        <v>7039617</v>
+        <v>7039840</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6768,11 +7029,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6799,10 +7055,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122430036</v>
+        <v>122425700</v>
       </c>
       <c r="B59" t="n">
-        <v>79734</v>
+        <v>57383</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6815,32 +7071,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562621</v>
+        <v>562678</v>
       </c>
       <c r="R59" t="n">
-        <v>7039854</v>
+        <v>7039813</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6867,9 +7133,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,22 +7165,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122430274</v>
+        <v>122427418</v>
       </c>
       <c r="B60" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6912,37 +7193,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562903</v>
+        <v>562680</v>
       </c>
       <c r="R60" t="n">
-        <v>7039649</v>
+        <v>7039626</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6969,24 +7250,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7001,22 +7267,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122428124</v>
+        <v>122425544</v>
       </c>
       <c r="B61" t="n">
-        <v>79733</v>
+        <v>78392</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7029,16 +7295,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6446</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7048,13 +7319,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562630</v>
+        <v>562672</v>
       </c>
       <c r="R61" t="n">
-        <v>7039565</v>
+        <v>7039840</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7081,9 +7352,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7098,22 +7379,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122426220</v>
+        <v>122428034</v>
       </c>
       <c r="B62" t="n">
-        <v>57379</v>
+        <v>57536</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7126,22 +7407,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>103021</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7150,13 +7440,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562671</v>
+        <v>562674</v>
       </c>
       <c r="R62" t="n">
-        <v>7039729</v>
+        <v>7039543</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7183,14 +7473,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7205,22 +7500,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122425414</v>
+        <v>122430036</v>
       </c>
       <c r="B63" t="n">
-        <v>57379</v>
+        <v>79738</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7233,37 +7528,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2081</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562678</v>
+        <v>562621</v>
       </c>
       <c r="R63" t="n">
-        <v>7039855</v>
+        <v>7039854</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7290,24 +7585,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7322,22 +7602,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427703</v>
+        <v>122425536</v>
       </c>
       <c r="B64" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7350,34 +7630,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562784</v>
+        <v>562710</v>
       </c>
       <c r="R64" t="n">
-        <v>7039590</v>
+        <v>7039834</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7409,7 +7689,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7419,12 +7699,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7439,22 +7714,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122429819</v>
+        <v>122428307</v>
       </c>
       <c r="B65" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7467,29 +7742,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562600</v>
+        <v>562557</v>
       </c>
       <c r="R65" t="n">
-        <v>7039877</v>
+        <v>7039552</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7522,6 +7807,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7548,10 +7838,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122425855</v>
+        <v>122428693</v>
       </c>
       <c r="B66" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7564,29 +7854,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562731</v>
+        <v>562933</v>
       </c>
       <c r="R66" t="n">
-        <v>7039827</v>
+        <v>7039394</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7618,7 +7918,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7628,7 +7928,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7655,10 +7960,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122430000</v>
+        <v>122427566</v>
       </c>
       <c r="B67" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7673,6 +7978,11 @@
       <c r="E67" t="n">
         <v>6458</v>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7690,10 +8000,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562623</v>
+        <v>562663</v>
       </c>
       <c r="R67" t="n">
-        <v>7039843</v>
+        <v>7039574</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7752,10 +8062,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122427626</v>
+        <v>122426080</v>
       </c>
       <c r="B68" t="n">
-        <v>78388</v>
+        <v>79737</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7768,16 +8078,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6458</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7787,10 +8102,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562773</v>
+        <v>562743</v>
       </c>
       <c r="R68" t="n">
-        <v>7039605</v>
+        <v>7039807</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7822,7 +8137,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7832,7 +8147,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7847,22 +8162,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122425405</v>
+        <v>122427824</v>
       </c>
       <c r="B69" t="n">
-        <v>74753</v>
+        <v>79737</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7875,16 +8190,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7894,13 +8214,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562648</v>
+        <v>562770</v>
       </c>
       <c r="R69" t="n">
-        <v>7039865</v>
+        <v>7039566</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7927,9 +8247,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7944,22 +8274,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122428148</v>
+        <v>122429998</v>
       </c>
       <c r="B70" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7972,29 +8302,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562707</v>
+        <v>562999</v>
       </c>
       <c r="R70" t="n">
-        <v>7039456</v>
+        <v>7039523</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8026,7 +8366,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8036,7 +8376,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8051,22 +8396,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425703</v>
+        <v>122425191</v>
       </c>
       <c r="B71" t="n">
-        <v>57395</v>
+        <v>79737</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8079,34 +8424,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562654</v>
+        <v>562649</v>
       </c>
       <c r="R71" t="n">
-        <v>7039819</v>
+        <v>7039883</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8165,10 +8510,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122430397</v>
+        <v>122429996</v>
       </c>
       <c r="B72" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8181,37 +8526,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562890</v>
+        <v>562622</v>
       </c>
       <c r="R72" t="n">
-        <v>7039728</v>
+        <v>7039843</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8238,24 +8583,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,22 +8600,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122426187</v>
+        <v>122428692</v>
       </c>
       <c r="B73" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8298,32 +8628,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562759</v>
+        <v>562502</v>
       </c>
       <c r="R73" t="n">
-        <v>7039787</v>
+        <v>7039635</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8350,19 +8690,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:19</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8377,22 +8712,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122425278</v>
+        <v>122426187</v>
       </c>
       <c r="B74" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8407,6 +8742,11 @@
       <c r="E74" t="n">
         <v>6458</v>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8420,14 +8760,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562673</v>
+        <v>562759</v>
       </c>
       <c r="R74" t="n">
-        <v>7039869</v>
+        <v>7039787</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8459,7 +8799,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8469,7 +8809,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8496,10 +8836,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122425310</v>
+        <v>122425284</v>
       </c>
       <c r="B75" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8512,32 +8852,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562650</v>
+        <v>562657</v>
       </c>
       <c r="R75" t="n">
-        <v>7039868</v>
+        <v>7039870</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8564,19 +8909,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8591,22 +8926,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122430062</v>
+        <v>122430183</v>
       </c>
       <c r="B76" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8619,32 +8954,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562624</v>
+        <v>562911</v>
       </c>
       <c r="R76" t="n">
-        <v>7039856</v>
+        <v>7039598</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8671,9 +9016,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8688,22 +9048,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122430719</v>
+        <v>122427743</v>
       </c>
       <c r="B77" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8718,6 +9078,11 @@
       <c r="E77" t="n">
         <v>100109</v>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -8740,10 +9105,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562835</v>
+        <v>562670</v>
       </c>
       <c r="R77" t="n">
-        <v>7039750</v>
+        <v>7039613</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8775,7 +9140,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8785,12 +9150,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8805,22 +9170,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122425397</v>
+        <v>122425414</v>
       </c>
       <c r="B78" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8835,6 +9200,11 @@
       <c r="E78" t="n">
         <v>100109</v>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -8857,10 +9227,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562662</v>
+        <v>562678</v>
       </c>
       <c r="R78" t="n">
-        <v>7039854</v>
+        <v>7039855</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8892,7 +9262,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8902,7 +9272,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -8922,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430780</v>
+        <v>122428692</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562903</v>
+        <v>562502</v>
       </c>
       <c r="R5" t="n">
-        <v>7039567</v>
+        <v>7039635</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,19 +1101,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:21</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,22 +1123,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122426220</v>
+        <v>122425703</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,16 +1151,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,7 +1171,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562671</v>
+        <v>562654</v>
       </c>
       <c r="R6" t="n">
-        <v>7039729</v>
+        <v>7039819</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1221,11 +1216,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425397</v>
+        <v>122430000</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,42 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562662</v>
+        <v>562623</v>
       </c>
       <c r="R7" t="n">
-        <v>7039854</v>
+        <v>7039843</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,24 +1315,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1486,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425310</v>
+        <v>122428693</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,34 +1472,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562650</v>
+        <v>562933</v>
       </c>
       <c r="R9" t="n">
-        <v>7039868</v>
+        <v>7039394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1566,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428645</v>
+        <v>122427407</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,37 +1594,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562509</v>
+        <v>562761</v>
       </c>
       <c r="R10" t="n">
-        <v>7039629</v>
+        <v>7039655</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,9 +1656,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,22 +1688,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425331</v>
+        <v>122426187</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562650</v>
+        <v>562759</v>
       </c>
       <c r="R11" t="n">
-        <v>7039856</v>
+        <v>7039787</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1773,9 +1773,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,22 +1800,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122428173</v>
+        <v>122427824</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,39 +1828,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562701</v>
+        <v>562770</v>
       </c>
       <c r="R12" t="n">
-        <v>7039441</v>
+        <v>7039566</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,12 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,19 +1912,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122428711</v>
+        <v>122430719</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562889</v>
+        <v>562835</v>
       </c>
       <c r="R13" t="n">
-        <v>7039463</v>
+        <v>7039750</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,7 +2046,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122426422</v>
+        <v>122425397</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2082,7 +2082,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562642</v>
+        <v>562662</v>
       </c>
       <c r="R14" t="n">
-        <v>7039716</v>
+        <v>7039854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122425754</v>
+        <v>122429992</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,39 +2184,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562652</v>
+        <v>562620</v>
       </c>
       <c r="R15" t="n">
-        <v>7039805</v>
+        <v>7039839</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2249,11 +2244,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122427618</v>
+        <v>122425617</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,39 +2286,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562674</v>
+        <v>562648</v>
       </c>
       <c r="R16" t="n">
-        <v>7039582</v>
+        <v>7039837</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2361,11 +2346,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122430062</v>
+        <v>122428173</v>
       </c>
       <c r="B17" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,37 +2388,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562624</v>
+        <v>562701</v>
       </c>
       <c r="R17" t="n">
-        <v>7039856</v>
+        <v>7039441</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2465,9 +2450,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,22 +2482,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122426059</v>
+        <v>122425310</v>
       </c>
       <c r="B18" t="n">
-        <v>82443</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,21 +2510,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,13 +2534,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562673</v>
+        <v>562650</v>
       </c>
       <c r="R18" t="n">
-        <v>7039763</v>
+        <v>7039868</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2567,9 +2567,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,22 +2594,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122425855</v>
+        <v>122429969</v>
       </c>
       <c r="B19" t="n">
-        <v>90844</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,21 +2622,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,13 +2646,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562731</v>
+        <v>562604</v>
       </c>
       <c r="R19" t="n">
-        <v>7039827</v>
+        <v>7039850</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2669,19 +2679,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122425242</v>
+        <v>122426422</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,37 +2724,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562659</v>
+        <v>562642</v>
       </c>
       <c r="R20" t="n">
-        <v>7039871</v>
+        <v>7039716</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2781,9 +2786,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,22 +2818,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122427473</v>
+        <v>122427401</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,39 +2846,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562684</v>
+        <v>562674</v>
       </c>
       <c r="R21" t="n">
-        <v>7039617</v>
+        <v>7039653</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2891,11 +2906,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122429000</v>
+        <v>122425405</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>74757</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,37 +2948,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562984</v>
+        <v>562648</v>
       </c>
       <c r="R22" t="n">
-        <v>7039447</v>
+        <v>7039865</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2995,19 +3005,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3022,22 +3022,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122427459</v>
+        <v>122425278</v>
       </c>
       <c r="B23" t="n">
-        <v>98224</v>
+        <v>79737</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,52 +3046,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562755</v>
+        <v>562673</v>
       </c>
       <c r="R23" t="n">
-        <v>7039631</v>
+        <v>7039869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3133,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,22 +3134,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122427985</v>
+        <v>122425855</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3176,39 +3162,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562695</v>
+        <v>562731</v>
       </c>
       <c r="R24" t="n">
-        <v>7039574</v>
+        <v>7039827</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3240,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3250,12 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,10 +3258,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122427401</v>
+        <v>122427459</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3294,41 +3270,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562674</v>
+        <v>562755</v>
       </c>
       <c r="R25" t="n">
-        <v>7039653</v>
+        <v>7039631</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3355,9 +3345,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,22 +3372,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429969</v>
+        <v>122425191</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,34 +3400,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562604</v>
+        <v>562649</v>
       </c>
       <c r="R26" t="n">
-        <v>7039850</v>
+        <v>7039883</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122427605</v>
+        <v>122427418</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,42 +3502,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562687</v>
+        <v>562680</v>
       </c>
       <c r="R27" t="n">
-        <v>7039594</v>
+        <v>7039626</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3564,24 +3559,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,22 +3576,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122426351</v>
+        <v>122428148</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3624,39 +3604,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562771</v>
+        <v>562707</v>
       </c>
       <c r="R28" t="n">
-        <v>7039744</v>
+        <v>7039456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3688,7 +3663,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3698,12 +3673,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3730,10 +3700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122425405</v>
+        <v>122430397</v>
       </c>
       <c r="B29" t="n">
-        <v>74757</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3746,37 +3716,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562648</v>
+        <v>562890</v>
       </c>
       <c r="R29" t="n">
-        <v>7039865</v>
+        <v>7039728</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3803,9 +3778,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3820,22 +3810,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122430000</v>
+        <v>122426079</v>
       </c>
       <c r="B30" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3848,21 +3838,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3872,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562623</v>
+        <v>562676</v>
       </c>
       <c r="R30" t="n">
-        <v>7039843</v>
+        <v>7039760</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3934,7 +3924,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122429588</v>
+        <v>122425284</v>
       </c>
       <c r="B31" t="n">
         <v>79737</v>
@@ -3970,14 +3960,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562549</v>
+        <v>562657</v>
       </c>
       <c r="R31" t="n">
-        <v>7039854</v>
+        <v>7039870</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4036,10 +4026,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122425703</v>
+        <v>122428124</v>
       </c>
       <c r="B32" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4052,39 +4042,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562654</v>
+        <v>562630</v>
       </c>
       <c r="R32" t="n">
-        <v>7039819</v>
+        <v>7039565</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4143,10 +4128,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122429334</v>
+        <v>122427703</v>
       </c>
       <c r="B33" t="n">
-        <v>78392</v>
+        <v>57383</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4159,37 +4144,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562497</v>
+        <v>562784</v>
       </c>
       <c r="R33" t="n">
-        <v>7039642</v>
+        <v>7039590</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4216,9 +4206,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4233,22 +4238,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122428148</v>
+        <v>122429998</v>
       </c>
       <c r="B34" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4261,34 +4266,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562707</v>
+        <v>562999</v>
       </c>
       <c r="R34" t="n">
-        <v>7039456</v>
+        <v>7039523</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4320,7 +4330,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4330,7 +4340,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,22 +4360,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122428796</v>
+        <v>122425536</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4373,39 +4388,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563001</v>
+        <v>562710</v>
       </c>
       <c r="R35" t="n">
-        <v>7039421</v>
+        <v>7039834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4437,7 +4447,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4447,12 +4457,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4479,10 +4484,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122429596</v>
+        <v>122427605</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4495,37 +4500,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562565</v>
+        <v>562687</v>
       </c>
       <c r="R36" t="n">
-        <v>7039844</v>
+        <v>7039594</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4552,9 +4562,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,22 +4594,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122427645</v>
+        <v>122430780</v>
       </c>
       <c r="B37" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4597,34 +4622,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562693</v>
+        <v>562903</v>
       </c>
       <c r="R37" t="n">
-        <v>7039587</v>
+        <v>7039567</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4656,7 +4686,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4666,7 +4696,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4693,7 +4723,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122425539</v>
+        <v>122429855</v>
       </c>
       <c r="B38" t="n">
         <v>79737</v>
@@ -4733,10 +4763,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562651</v>
+        <v>562619</v>
       </c>
       <c r="R38" t="n">
-        <v>7039827</v>
+        <v>7039840</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4795,10 +4825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122430274</v>
+        <v>122429588</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4811,42 +4841,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562903</v>
+        <v>562549</v>
       </c>
       <c r="R39" t="n">
-        <v>7039649</v>
+        <v>7039854</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4873,24 +4898,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4905,22 +4915,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122429819</v>
+        <v>122430062</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4933,21 +4943,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4957,10 +4967,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562600</v>
+        <v>562624</v>
       </c>
       <c r="R40" t="n">
-        <v>7039877</v>
+        <v>7039856</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5019,10 +5029,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122428124</v>
+        <v>122430816</v>
       </c>
       <c r="B41" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5035,37 +5045,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562630</v>
+        <v>562845</v>
       </c>
       <c r="R41" t="n">
-        <v>7039565</v>
+        <v>7039809</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5092,9 +5107,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5109,22 +5134,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122425516</v>
+        <v>122430036</v>
       </c>
       <c r="B42" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5137,42 +5162,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562706</v>
+        <v>562621</v>
       </c>
       <c r="R42" t="n">
-        <v>7039810</v>
+        <v>7039854</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5199,24 +5219,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5231,19 +5236,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427703</v>
+        <v>122430183</v>
       </c>
       <c r="B43" t="n">
         <v>57383</v>
@@ -5288,10 +5293,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562784</v>
+        <v>562911</v>
       </c>
       <c r="R43" t="n">
-        <v>7039590</v>
+        <v>7039598</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5323,7 +5328,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5333,7 +5338,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5365,7 +5370,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122430397</v>
+        <v>122427473</v>
       </c>
       <c r="B44" t="n">
         <v>57383</v>
@@ -5410,13 +5415,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562890</v>
+        <v>562684</v>
       </c>
       <c r="R44" t="n">
-        <v>7039728</v>
+        <v>7039617</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5443,24 +5448,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5475,22 +5470,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122425278</v>
+        <v>122426059</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>82443</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5503,37 +5498,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
         <v>562673</v>
       </c>
       <c r="R45" t="n">
-        <v>7039869</v>
+        <v>7039763</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5560,19 +5555,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5587,22 +5572,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428074</v>
+        <v>122427645</v>
       </c>
       <c r="B46" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5615,39 +5600,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562763</v>
+        <v>562693</v>
       </c>
       <c r="R46" t="n">
-        <v>7039478</v>
+        <v>7039587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5679,7 +5659,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5689,12 +5669,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5709,22 +5684,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122429992</v>
+        <v>122426351</v>
       </c>
       <c r="B47" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5737,37 +5712,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562620</v>
+        <v>562771</v>
       </c>
       <c r="R47" t="n">
-        <v>7039839</v>
+        <v>7039744</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5794,9 +5774,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5811,22 +5806,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122427953</v>
+        <v>122425700</v>
       </c>
       <c r="B48" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5839,37 +5834,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562661</v>
+        <v>562678</v>
       </c>
       <c r="R48" t="n">
-        <v>7039580</v>
+        <v>7039813</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5896,9 +5896,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,22 +5928,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122425328</v>
+        <v>122428645</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5941,37 +5956,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562678</v>
+        <v>562509</v>
       </c>
       <c r="R49" t="n">
-        <v>7039868</v>
+        <v>7039629</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5998,19 +6013,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,22 +6030,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122429005</v>
+        <v>122425544</v>
       </c>
       <c r="B50" t="n">
-        <v>57383</v>
+        <v>78392</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6053,42 +6058,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562522</v>
+        <v>562672</v>
       </c>
       <c r="R50" t="n">
-        <v>7039596</v>
+        <v>7039840</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6115,14 +6115,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6137,22 +6142,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122430816</v>
+        <v>122425331</v>
       </c>
       <c r="B51" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6165,42 +6170,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562845</v>
+        <v>562650</v>
       </c>
       <c r="R51" t="n">
-        <v>7039809</v>
+        <v>7039856</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6227,19 +6227,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,22 +6244,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122429056</v>
+        <v>122427953</v>
       </c>
       <c r="B52" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6282,42 +6272,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562996</v>
+        <v>562661</v>
       </c>
       <c r="R52" t="n">
-        <v>7039422</v>
+        <v>7039580</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6344,24 +6329,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,19 +6346,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122427407</v>
+        <v>122425516</v>
       </c>
       <c r="B53" t="n">
         <v>57383</v>
@@ -6433,10 +6403,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562761</v>
+        <v>562706</v>
       </c>
       <c r="R53" t="n">
-        <v>7039655</v>
+        <v>7039810</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6468,7 +6438,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6478,7 +6448,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6510,7 +6480,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122430719</v>
+        <v>122426220</v>
       </c>
       <c r="B54" t="n">
         <v>57383</v>
@@ -6555,13 +6525,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562835</v>
+        <v>562671</v>
       </c>
       <c r="R54" t="n">
-        <v>7039750</v>
+        <v>7039729</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6588,24 +6558,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6620,22 +6580,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122425780</v>
+        <v>122427985</v>
       </c>
       <c r="B55" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6648,34 +6608,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562725</v>
+        <v>562695</v>
       </c>
       <c r="R55" t="n">
-        <v>7039812</v>
+        <v>7039574</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6707,7 +6672,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6717,12 +6682,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Lunglav på rönn</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6749,10 +6714,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122426079</v>
+        <v>122430274</v>
       </c>
       <c r="B56" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6765,37 +6730,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562676</v>
+        <v>562903</v>
       </c>
       <c r="R56" t="n">
-        <v>7039760</v>
+        <v>7039649</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6822,9 +6792,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6839,22 +6824,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122425617</v>
+        <v>122429005</v>
       </c>
       <c r="B57" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6867,34 +6852,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562648</v>
+        <v>562522</v>
       </c>
       <c r="R57" t="n">
-        <v>7039837</v>
+        <v>7039596</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6927,6 +6917,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6953,10 +6948,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122429855</v>
+        <v>122428796</v>
       </c>
       <c r="B58" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6969,37 +6964,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562619</v>
+        <v>563001</v>
       </c>
       <c r="R58" t="n">
-        <v>7039840</v>
+        <v>7039421</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7026,9 +7026,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7043,22 +7058,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122425700</v>
+        <v>122428034</v>
       </c>
       <c r="B59" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7071,27 +7086,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7100,10 +7119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562678</v>
+        <v>562674</v>
       </c>
       <c r="R59" t="n">
-        <v>7039813</v>
+        <v>7039543</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7135,7 +7154,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7145,12 +7164,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7165,22 +7179,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427418</v>
+        <v>122425754</v>
       </c>
       <c r="B60" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7193,34 +7207,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562680</v>
+        <v>562652</v>
       </c>
       <c r="R60" t="n">
-        <v>7039626</v>
+        <v>7039805</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7253,6 +7272,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7279,10 +7303,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122425544</v>
+        <v>122425539</v>
       </c>
       <c r="B61" t="n">
-        <v>78392</v>
+        <v>79737</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7295,21 +7319,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7319,13 +7343,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562672</v>
+        <v>562651</v>
       </c>
       <c r="R61" t="n">
-        <v>7039840</v>
+        <v>7039827</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7352,19 +7376,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7379,22 +7393,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122428034</v>
+        <v>122429056</v>
       </c>
       <c r="B62" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7407,43 +7421,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562674</v>
+        <v>562996</v>
       </c>
       <c r="R62" t="n">
-        <v>7039543</v>
+        <v>7039422</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7475,7 +7485,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7485,7 +7495,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7500,22 +7515,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122430036</v>
+        <v>122426080</v>
       </c>
       <c r="B63" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7528,21 +7543,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7552,13 +7567,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562621</v>
+        <v>562743</v>
       </c>
       <c r="R63" t="n">
-        <v>7039854</v>
+        <v>7039807</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7585,9 +7600,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7602,22 +7627,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122425536</v>
+        <v>122429819</v>
       </c>
       <c r="B64" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7630,21 +7655,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7654,13 +7679,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562710</v>
+        <v>562600</v>
       </c>
       <c r="R64" t="n">
-        <v>7039834</v>
+        <v>7039877</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7687,19 +7712,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7714,19 +7729,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122428307</v>
+        <v>122425414</v>
       </c>
       <c r="B65" t="n">
         <v>57383</v>
@@ -7771,13 +7786,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562557</v>
+        <v>562678</v>
       </c>
       <c r="R65" t="n">
-        <v>7039552</v>
+        <v>7039855</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7804,14 +7819,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7826,22 +7851,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122428693</v>
+        <v>122427566</v>
       </c>
       <c r="B66" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7854,42 +7879,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562933</v>
+        <v>562663</v>
       </c>
       <c r="R66" t="n">
-        <v>7039394</v>
+        <v>7039574</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7916,24 +7936,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7948,19 +7953,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122427566</v>
+        <v>122429996</v>
       </c>
       <c r="B67" t="n">
         <v>79737</v>
@@ -8000,10 +8005,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562663</v>
+        <v>562622</v>
       </c>
       <c r="R67" t="n">
-        <v>7039574</v>
+        <v>7039843</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8062,7 +8067,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122426080</v>
+        <v>122425242</v>
       </c>
       <c r="B68" t="n">
         <v>79737</v>
@@ -8098,17 +8103,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562743</v>
+        <v>562659</v>
       </c>
       <c r="R68" t="n">
-        <v>7039807</v>
+        <v>7039871</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8135,19 +8140,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8162,22 +8157,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122427824</v>
+        <v>122428074</v>
       </c>
       <c r="B69" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8190,34 +8185,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562770</v>
+        <v>562763</v>
       </c>
       <c r="R69" t="n">
-        <v>7039566</v>
+        <v>7039478</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8259,7 +8259,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8286,7 +8291,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122429998</v>
+        <v>122427618</v>
       </c>
       <c r="B70" t="n">
         <v>57383</v>
@@ -8327,17 +8332,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562999</v>
+        <v>562674</v>
       </c>
       <c r="R70" t="n">
-        <v>7039523</v>
+        <v>7039582</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8364,24 +8369,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8396,19 +8391,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425191</v>
+        <v>122425780</v>
       </c>
       <c r="B71" t="n">
         <v>79737</v>
@@ -8444,17 +8439,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562649</v>
+        <v>562725</v>
       </c>
       <c r="R71" t="n">
-        <v>7039883</v>
+        <v>7039812</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8481,9 +8476,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8498,22 +8508,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122429996</v>
+        <v>122429240</v>
       </c>
       <c r="B72" t="n">
-        <v>79737</v>
+        <v>78392</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8526,21 +8536,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8550,10 +8560,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562622</v>
+        <v>562497</v>
       </c>
       <c r="R72" t="n">
-        <v>7039843</v>
+        <v>7039642</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8612,7 +8622,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122428692</v>
+        <v>122428307</v>
       </c>
       <c r="B73" t="n">
         <v>57383</v>
@@ -8648,7 +8658,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8657,10 +8667,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562502</v>
+        <v>562557</v>
       </c>
       <c r="R73" t="n">
-        <v>7039635</v>
+        <v>7039552</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8697,7 +8707,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8724,10 +8734,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122426187</v>
+        <v>122427743</v>
       </c>
       <c r="B74" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8740,34 +8750,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562759</v>
+        <v>562670</v>
       </c>
       <c r="R74" t="n">
-        <v>7039787</v>
+        <v>7039613</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8799,7 +8814,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8809,7 +8824,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8836,10 +8856,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122425284</v>
+        <v>122428711</v>
       </c>
       <c r="B75" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8852,37 +8872,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562657</v>
+        <v>562889</v>
       </c>
       <c r="R75" t="n">
-        <v>7039870</v>
+        <v>7039463</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8909,9 +8934,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8926,22 +8966,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122430183</v>
+        <v>122429000</v>
       </c>
       <c r="B76" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8954,39 +8994,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562911</v>
+        <v>562984</v>
       </c>
       <c r="R76" t="n">
-        <v>7039598</v>
+        <v>7039447</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9018,7 +9053,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9028,12 +9063,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9060,10 +9090,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122427743</v>
+        <v>122425328</v>
       </c>
       <c r="B77" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9076,39 +9106,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562670</v>
+        <v>562678</v>
       </c>
       <c r="R77" t="n">
-        <v>7039613</v>
+        <v>7039868</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9140,7 +9165,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9150,12 +9175,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9182,10 +9202,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122425414</v>
+        <v>122429596</v>
       </c>
       <c r="B78" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9198,42 +9218,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562678</v>
+        <v>562565</v>
       </c>
       <c r="R78" t="n">
-        <v>7039855</v>
+        <v>7039844</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9260,24 +9275,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -7527,10 +7527,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122426080</v>
+        <v>122425414</v>
       </c>
       <c r="B63" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7543,34 +7543,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562743</v>
+        <v>562678</v>
       </c>
       <c r="R63" t="n">
-        <v>7039807</v>
+        <v>7039855</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7602,7 +7607,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7612,7 +7617,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7639,10 +7649,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122429819</v>
+        <v>122426080</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7655,21 +7665,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7679,13 +7689,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562600</v>
+        <v>562743</v>
       </c>
       <c r="R64" t="n">
-        <v>7039877</v>
+        <v>7039807</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7712,9 +7722,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7729,22 +7749,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122425414</v>
+        <v>122429819</v>
       </c>
       <c r="B65" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7757,42 +7777,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562678</v>
+        <v>562600</v>
       </c>
       <c r="R65" t="n">
-        <v>7039855</v>
+        <v>7039877</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7819,24 +7834,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7851,12 +7851,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122429000</v>
+        <v>122429596</v>
       </c>
       <c r="B76" t="n">
         <v>79737</v>
@@ -9014,17 +9014,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562984</v>
+        <v>562565</v>
       </c>
       <c r="R76" t="n">
-        <v>7039447</v>
+        <v>7039844</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9051,19 +9051,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9078,19 +9068,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122425328</v>
+        <v>122429000</v>
       </c>
       <c r="B77" t="n">
         <v>79737</v>
@@ -9126,14 +9116,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562678</v>
+        <v>562984</v>
       </c>
       <c r="R77" t="n">
-        <v>7039868</v>
+        <v>7039447</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9165,7 +9155,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9175,7 +9165,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9190,19 +9180,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122429596</v>
+        <v>122425328</v>
       </c>
       <c r="B78" t="n">
         <v>79737</v>
@@ -9238,17 +9228,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562565</v>
+        <v>562678</v>
       </c>
       <c r="R78" t="n">
-        <v>7039844</v>
+        <v>7039868</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9275,9 +9265,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122428692</v>
+        <v>122425780</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,42 +1039,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562502</v>
+        <v>562725</v>
       </c>
       <c r="R5" t="n">
-        <v>7039635</v>
+        <v>7039812</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,14 +1096,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425703</v>
+        <v>122429969</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,39 +1156,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562654</v>
+        <v>562604</v>
       </c>
       <c r="R6" t="n">
-        <v>7039819</v>
+        <v>7039850</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430000</v>
+        <v>122428645</v>
       </c>
       <c r="B7" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1258,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562623</v>
+        <v>562509</v>
       </c>
       <c r="R7" t="n">
-        <v>7039843</v>
+        <v>7039629</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427626</v>
+        <v>122430036</v>
       </c>
       <c r="B8" t="n">
-        <v>78392</v>
+        <v>79738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,13 +1384,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562773</v>
+        <v>562621</v>
       </c>
       <c r="R8" t="n">
-        <v>7039605</v>
+        <v>7039854</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,19 +1417,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,19 +1434,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122428693</v>
+        <v>122428173</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1497,14 +1487,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562933</v>
+        <v>562701</v>
       </c>
       <c r="R9" t="n">
-        <v>7039394</v>
+        <v>7039441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1578,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122427407</v>
+        <v>122429056</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1619,14 +1609,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562761</v>
+        <v>562996</v>
       </c>
       <c r="R10" t="n">
-        <v>7039655</v>
+        <v>7039422</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,12 +1658,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,22 +1678,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122426187</v>
+        <v>122427743</v>
       </c>
       <c r="B11" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,34 +1706,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562759</v>
+        <v>562670</v>
       </c>
       <c r="R11" t="n">
-        <v>7039787</v>
+        <v>7039613</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,7 +1812,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122427824</v>
+        <v>122427566</v>
       </c>
       <c r="B12" t="n">
         <v>79737</v>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562770</v>
+        <v>562663</v>
       </c>
       <c r="R12" t="n">
-        <v>7039566</v>
+        <v>7039574</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,19 +1885,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,22 +1902,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122430719</v>
+        <v>122429996</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,42 +1930,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562835</v>
+        <v>562622</v>
       </c>
       <c r="R13" t="n">
-        <v>7039750</v>
+        <v>7039843</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2002,24 +1987,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,22 +2004,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122425397</v>
+        <v>122429855</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,42 +2032,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562662</v>
+        <v>562619</v>
       </c>
       <c r="R14" t="n">
-        <v>7039854</v>
+        <v>7039840</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,24 +2089,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,22 +2106,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122429992</v>
+        <v>122429005</v>
       </c>
       <c r="B15" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,34 +2134,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562620</v>
+        <v>562522</v>
       </c>
       <c r="R15" t="n">
-        <v>7039839</v>
+        <v>7039596</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2244,6 +2199,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122425617</v>
+        <v>122428034</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,37 +2246,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562648</v>
+        <v>562674</v>
       </c>
       <c r="R16" t="n">
-        <v>7039837</v>
+        <v>7039543</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2343,9 +2312,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,22 +2339,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122428173</v>
+        <v>122427626</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>78392</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,39 +2367,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562701</v>
+        <v>562773</v>
       </c>
       <c r="R17" t="n">
-        <v>7039441</v>
+        <v>7039605</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2426,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,12 +2436,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,22 +2451,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122425310</v>
+        <v>122425405</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562650</v>
+        <v>562648</v>
       </c>
       <c r="R18" t="n">
-        <v>7039868</v>
+        <v>7039865</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2567,19 +2536,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,22 +2553,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122429969</v>
+        <v>122425855</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562604</v>
+        <v>562731</v>
       </c>
       <c r="R19" t="n">
-        <v>7039850</v>
+        <v>7039827</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2679,9 +2638,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,22 +2665,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122426422</v>
+        <v>122426079</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,42 +2693,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562642</v>
+        <v>562676</v>
       </c>
       <c r="R20" t="n">
-        <v>7039716</v>
+        <v>7039760</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2786,24 +2750,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,22 +2767,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122427401</v>
+        <v>122429240</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2870,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562674</v>
+        <v>562497</v>
       </c>
       <c r="R21" t="n">
-        <v>7039653</v>
+        <v>7039642</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2932,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122425405</v>
+        <v>122430062</v>
       </c>
       <c r="B22" t="n">
-        <v>74757</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2948,21 +2897,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2921,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562648</v>
+        <v>562624</v>
       </c>
       <c r="R22" t="n">
-        <v>7039865</v>
+        <v>7039856</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3034,10 +2983,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122425278</v>
+        <v>122425703</v>
       </c>
       <c r="B23" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,37 +2999,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562673</v>
+        <v>562654</v>
       </c>
       <c r="R23" t="n">
-        <v>7039869</v>
+        <v>7039819</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3107,19 +3061,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,22 +3078,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122425855</v>
+        <v>122426220</v>
       </c>
       <c r="B24" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,37 +3106,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562731</v>
+        <v>562671</v>
       </c>
       <c r="R24" t="n">
-        <v>7039827</v>
+        <v>7039729</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3219,19 +3168,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:07</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,22 +3190,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122427459</v>
+        <v>122428307</v>
       </c>
       <c r="B25" t="n">
-        <v>98237</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3270,40 +3214,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3312,13 +3247,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562755</v>
+        <v>562557</v>
       </c>
       <c r="R25" t="n">
-        <v>7039631</v>
+        <v>7039552</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3345,19 +3280,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:05</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,22 +3302,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122425191</v>
+        <v>122429819</v>
       </c>
       <c r="B26" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,34 +3330,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562649</v>
+        <v>562600</v>
       </c>
       <c r="R26" t="n">
-        <v>7039883</v>
+        <v>7039877</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3486,7 +3416,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122427418</v>
+        <v>122430000</v>
       </c>
       <c r="B27" t="n">
         <v>79737</v>
@@ -3526,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562680</v>
+        <v>562623</v>
       </c>
       <c r="R27" t="n">
-        <v>7039626</v>
+        <v>7039843</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3588,7 +3518,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122428148</v>
+        <v>122425536</v>
       </c>
       <c r="B28" t="n">
         <v>79737</v>
@@ -3628,10 +3558,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562707</v>
+        <v>562710</v>
       </c>
       <c r="R28" t="n">
-        <v>7039456</v>
+        <v>7039834</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3663,7 +3593,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3673,7 +3603,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3700,10 +3630,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122430397</v>
+        <v>122426187</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,39 +3646,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562890</v>
+        <v>562759</v>
       </c>
       <c r="R29" t="n">
-        <v>7039728</v>
+        <v>7039787</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3780,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3790,12 +3715,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,22 +3730,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122426079</v>
+        <v>122428148</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3838,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3862,13 +3782,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562676</v>
+        <v>562707</v>
       </c>
       <c r="R30" t="n">
-        <v>7039760</v>
+        <v>7039456</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3895,9 +3815,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3912,22 +3842,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425284</v>
+        <v>122425414</v>
       </c>
       <c r="B31" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3940,37 +3870,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562657</v>
+        <v>562678</v>
       </c>
       <c r="R31" t="n">
-        <v>7039870</v>
+        <v>7039855</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3997,9 +3932,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,22 +3964,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122428124</v>
+        <v>122425700</v>
       </c>
       <c r="B32" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4042,37 +3992,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562630</v>
+        <v>562678</v>
       </c>
       <c r="R32" t="n">
-        <v>7039565</v>
+        <v>7039813</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4099,9 +4054,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4116,19 +4086,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122427703</v>
+        <v>122427985</v>
       </c>
       <c r="B33" t="n">
         <v>57383</v>
@@ -4173,10 +4143,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562784</v>
+        <v>562695</v>
       </c>
       <c r="R33" t="n">
-        <v>7039590</v>
+        <v>7039574</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4208,7 +4178,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4218,12 +4188,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,22 +4208,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122429998</v>
+        <v>122429000</v>
       </c>
       <c r="B34" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4266,39 +4236,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562999</v>
+        <v>562984</v>
       </c>
       <c r="R34" t="n">
-        <v>7039523</v>
+        <v>7039447</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4330,7 +4295,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4340,12 +4305,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,7 +4332,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122425536</v>
+        <v>122425242</v>
       </c>
       <c r="B35" t="n">
         <v>79737</v>
@@ -4408,17 +4368,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562710</v>
+        <v>562659</v>
       </c>
       <c r="R35" t="n">
-        <v>7039834</v>
+        <v>7039871</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4445,19 +4405,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,22 +4422,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122427605</v>
+        <v>122429588</v>
       </c>
       <c r="B36" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4500,42 +4450,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562687</v>
+        <v>562549</v>
       </c>
       <c r="R36" t="n">
-        <v>7039594</v>
+        <v>7039854</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4562,24 +4507,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4594,22 +4524,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122430780</v>
+        <v>122430274</v>
       </c>
       <c r="B37" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,16 +4552,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4642,7 +4572,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4654,7 +4584,7 @@
         <v>562903</v>
       </c>
       <c r="R37" t="n">
-        <v>7039567</v>
+        <v>7039649</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4686,7 +4616,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4696,7 +4626,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4711,22 +4646,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122429855</v>
+        <v>122430816</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4739,37 +4674,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562619</v>
+        <v>562845</v>
       </c>
       <c r="R38" t="n">
-        <v>7039840</v>
+        <v>7039809</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4796,9 +4736,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4813,22 +4763,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122429588</v>
+        <v>122429998</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4841,37 +4791,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562549</v>
+        <v>562999</v>
       </c>
       <c r="R39" t="n">
-        <v>7039854</v>
+        <v>7039523</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4898,9 +4853,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4915,22 +4885,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122430062</v>
+        <v>122427407</v>
       </c>
       <c r="B40" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4943,37 +4913,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562624</v>
+        <v>562761</v>
       </c>
       <c r="R40" t="n">
-        <v>7039856</v>
+        <v>7039655</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5000,9 +4975,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5017,22 +5007,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122430816</v>
+        <v>122425754</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5045,16 +5035,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5065,7 +5055,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5074,13 +5064,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562845</v>
+        <v>562652</v>
       </c>
       <c r="R41" t="n">
-        <v>7039809</v>
+        <v>7039805</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5107,19 +5097,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:15</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5134,22 +5119,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122430036</v>
+        <v>122430780</v>
       </c>
       <c r="B42" t="n">
-        <v>79738</v>
+        <v>57399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5162,37 +5147,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562621</v>
+        <v>562903</v>
       </c>
       <c r="R42" t="n">
-        <v>7039854</v>
+        <v>7039567</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5219,9 +5209,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5236,22 +5236,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122430183</v>
+        <v>122427953</v>
       </c>
       <c r="B43" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5264,42 +5264,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562911</v>
+        <v>562661</v>
       </c>
       <c r="R43" t="n">
-        <v>7039598</v>
+        <v>7039580</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,24 +5321,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5358,19 +5338,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122427473</v>
+        <v>122425397</v>
       </c>
       <c r="B44" t="n">
         <v>57383</v>
@@ -5406,7 +5386,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5415,13 +5395,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562684</v>
+        <v>562662</v>
       </c>
       <c r="R44" t="n">
-        <v>7039617</v>
+        <v>7039854</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5448,14 +5428,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5470,22 +5460,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122426059</v>
+        <v>122425191</v>
       </c>
       <c r="B45" t="n">
-        <v>82443</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5498,34 +5488,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562673</v>
+        <v>562649</v>
       </c>
       <c r="R45" t="n">
-        <v>7039763</v>
+        <v>7039883</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5584,7 +5574,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122427645</v>
+        <v>122427418</v>
       </c>
       <c r="B46" t="n">
         <v>79737</v>
@@ -5624,13 +5614,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562693</v>
+        <v>562680</v>
       </c>
       <c r="R46" t="n">
-        <v>7039587</v>
+        <v>7039626</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5657,19 +5647,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5684,19 +5664,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122426351</v>
+        <v>122428711</v>
       </c>
       <c r="B47" t="n">
         <v>57383</v>
@@ -5741,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562771</v>
+        <v>562889</v>
       </c>
       <c r="R47" t="n">
-        <v>7039744</v>
+        <v>7039463</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5776,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5806,19 +5786,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122425700</v>
+        <v>122425516</v>
       </c>
       <c r="B48" t="n">
         <v>57383</v>
@@ -5863,10 +5843,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562678</v>
+        <v>562706</v>
       </c>
       <c r="R48" t="n">
-        <v>7039813</v>
+        <v>7039810</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5898,7 +5878,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5908,7 +5888,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5928,22 +5908,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122428645</v>
+        <v>122425284</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5956,34 +5936,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562509</v>
+        <v>562657</v>
       </c>
       <c r="R49" t="n">
-        <v>7039629</v>
+        <v>7039870</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6042,10 +6022,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122425544</v>
+        <v>122425617</v>
       </c>
       <c r="B50" t="n">
-        <v>78392</v>
+        <v>79737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6058,21 +6038,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6082,13 +6062,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562672</v>
+        <v>562648</v>
       </c>
       <c r="R50" t="n">
-        <v>7039840</v>
+        <v>7039837</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6115,19 +6095,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,22 +6112,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122425331</v>
+        <v>122427645</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6170,21 +6140,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6194,13 +6164,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562650</v>
+        <v>562693</v>
       </c>
       <c r="R51" t="n">
-        <v>7039856</v>
+        <v>7039587</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6227,9 +6197,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6244,22 +6224,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122427953</v>
+        <v>122427605</v>
       </c>
       <c r="B52" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6272,37 +6252,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562661</v>
+        <v>562687</v>
       </c>
       <c r="R52" t="n">
-        <v>7039580</v>
+        <v>7039594</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6329,9 +6314,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6346,19 +6346,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122425516</v>
+        <v>122428693</v>
       </c>
       <c r="B53" t="n">
         <v>57383</v>
@@ -6399,14 +6399,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562706</v>
+        <v>562933</v>
       </c>
       <c r="R53" t="n">
-        <v>7039810</v>
+        <v>7039394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6480,7 +6480,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122426220</v>
+        <v>122427473</v>
       </c>
       <c r="B54" t="n">
         <v>57383</v>
@@ -6516,7 +6516,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562671</v>
+        <v>562684</v>
       </c>
       <c r="R54" t="n">
-        <v>7039729</v>
+        <v>7039617</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack, gammeltall</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6592,7 +6592,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122427985</v>
+        <v>122426351</v>
       </c>
       <c r="B55" t="n">
         <v>57383</v>
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562695</v>
+        <v>562771</v>
       </c>
       <c r="R55" t="n">
-        <v>7039574</v>
+        <v>7039744</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6714,7 +6714,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430274</v>
+        <v>122430397</v>
       </c>
       <c r="B56" t="n">
         <v>57383</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562903</v>
+        <v>562890</v>
       </c>
       <c r="R56" t="n">
-        <v>7039649</v>
+        <v>7039728</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6836,7 +6836,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122429005</v>
+        <v>122428692</v>
       </c>
       <c r="B57" t="n">
         <v>57383</v>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562522</v>
+        <v>562502</v>
       </c>
       <c r="R57" t="n">
-        <v>7039596</v>
+        <v>7039635</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6948,10 +6948,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122428796</v>
+        <v>122426059</v>
       </c>
       <c r="B58" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6964,42 +6964,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>563001</v>
+        <v>562673</v>
       </c>
       <c r="R58" t="n">
-        <v>7039421</v>
+        <v>7039763</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7026,24 +7021,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7058,22 +7038,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122428034</v>
+        <v>122425278</v>
       </c>
       <c r="B59" t="n">
-        <v>57536</v>
+        <v>79737</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7086,43 +7066,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562674</v>
+        <v>562673</v>
       </c>
       <c r="R59" t="n">
-        <v>7039543</v>
+        <v>7039869</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7154,7 +7125,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7164,7 +7135,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7191,10 +7162,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122425754</v>
+        <v>122427618</v>
       </c>
       <c r="B60" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7207,16 +7178,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7227,7 +7198,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7236,10 +7207,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562652</v>
+        <v>562674</v>
       </c>
       <c r="R60" t="n">
-        <v>7039805</v>
+        <v>7039582</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7276,7 +7247,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7303,10 +7274,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122425539</v>
+        <v>122426422</v>
       </c>
       <c r="B61" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7319,37 +7290,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562651</v>
+        <v>562642</v>
       </c>
       <c r="R61" t="n">
-        <v>7039827</v>
+        <v>7039716</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7376,9 +7352,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7393,19 +7384,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122429056</v>
+        <v>122427703</v>
       </c>
       <c r="B62" t="n">
         <v>57383</v>
@@ -7446,14 +7437,14 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562996</v>
+        <v>562784</v>
       </c>
       <c r="R62" t="n">
-        <v>7039422</v>
+        <v>7039590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7485,7 +7476,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7495,12 +7486,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7527,7 +7518,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122425414</v>
+        <v>122428796</v>
       </c>
       <c r="B63" t="n">
         <v>57383</v>
@@ -7568,14 +7559,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562678</v>
+        <v>563001</v>
       </c>
       <c r="R63" t="n">
-        <v>7039855</v>
+        <v>7039421</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7607,7 +7598,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7617,7 +7608,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7649,7 +7640,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122426080</v>
+        <v>122428124</v>
       </c>
       <c r="B64" t="n">
         <v>79737</v>
@@ -7689,13 +7680,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562743</v>
+        <v>562630</v>
       </c>
       <c r="R64" t="n">
-        <v>7039807</v>
+        <v>7039565</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7722,19 +7713,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7749,22 +7730,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122429819</v>
+        <v>122430719</v>
       </c>
       <c r="B65" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7777,37 +7758,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562600</v>
+        <v>562835</v>
       </c>
       <c r="R65" t="n">
-        <v>7039877</v>
+        <v>7039750</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7834,9 +7820,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7851,22 +7852,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122427566</v>
+        <v>122430183</v>
       </c>
       <c r="B66" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7879,37 +7880,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562663</v>
+        <v>562911</v>
       </c>
       <c r="R66" t="n">
-        <v>7039574</v>
+        <v>7039598</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7936,9 +7942,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7953,19 +7974,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429996</v>
+        <v>122425328</v>
       </c>
       <c r="B67" t="n">
         <v>79737</v>
@@ -8001,17 +8022,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562622</v>
+        <v>562678</v>
       </c>
       <c r="R67" t="n">
-        <v>7039843</v>
+        <v>7039868</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8038,9 +8059,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8055,19 +8086,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122425242</v>
+        <v>122429596</v>
       </c>
       <c r="B68" t="n">
         <v>79737</v>
@@ -8103,14 +8134,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562659</v>
+        <v>562565</v>
       </c>
       <c r="R68" t="n">
-        <v>7039871</v>
+        <v>7039844</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8169,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122428074</v>
+        <v>122427824</v>
       </c>
       <c r="B69" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8185,39 +8216,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562763</v>
+        <v>562770</v>
       </c>
       <c r="R69" t="n">
-        <v>7039478</v>
+        <v>7039566</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8249,7 +8275,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8259,12 +8285,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8291,10 +8312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122427618</v>
+        <v>122425310</v>
       </c>
       <c r="B70" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8307,42 +8328,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562674</v>
+        <v>562650</v>
       </c>
       <c r="R70" t="n">
-        <v>7039582</v>
+        <v>7039868</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8369,14 +8385,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8391,22 +8412,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425780</v>
+        <v>122425331</v>
       </c>
       <c r="B71" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8419,21 +8440,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8443,13 +8464,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562725</v>
+        <v>562650</v>
       </c>
       <c r="R71" t="n">
-        <v>7039812</v>
+        <v>7039856</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8476,24 +8497,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8508,22 +8514,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122429240</v>
+        <v>122426080</v>
       </c>
       <c r="B72" t="n">
-        <v>78392</v>
+        <v>79737</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8536,21 +8542,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8560,13 +8566,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562497</v>
+        <v>562743</v>
       </c>
       <c r="R72" t="n">
-        <v>7039642</v>
+        <v>7039807</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8593,9 +8599,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8610,22 +8626,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122428307</v>
+        <v>122427401</v>
       </c>
       <c r="B73" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8638,39 +8654,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562557</v>
+        <v>562674</v>
       </c>
       <c r="R73" t="n">
-        <v>7039552</v>
+        <v>7039653</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8703,11 +8714,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8734,10 +8740,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122427743</v>
+        <v>122425539</v>
       </c>
       <c r="B74" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8750,42 +8756,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562670</v>
+        <v>562651</v>
       </c>
       <c r="R74" t="n">
-        <v>7039613</v>
+        <v>7039827</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8812,24 +8813,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8844,22 +8830,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122428711</v>
+        <v>122427459</v>
       </c>
       <c r="B75" t="n">
-        <v>57383</v>
+        <v>98237</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8868,31 +8854,40 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8901,10 +8896,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562889</v>
+        <v>562755</v>
       </c>
       <c r="R75" t="n">
-        <v>7039463</v>
+        <v>7039631</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8936,7 +8931,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8946,12 +8941,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8978,7 +8968,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122429596</v>
+        <v>122429992</v>
       </c>
       <c r="B76" t="n">
         <v>79737</v>
@@ -9018,10 +9008,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562565</v>
+        <v>562620</v>
       </c>
       <c r="R76" t="n">
-        <v>7039844</v>
+        <v>7039839</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -9080,10 +9070,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122429000</v>
+        <v>122425544</v>
       </c>
       <c r="B77" t="n">
-        <v>79737</v>
+        <v>78392</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9096,34 +9086,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562984</v>
+        <v>562672</v>
       </c>
       <c r="R77" t="n">
-        <v>7039447</v>
+        <v>7039840</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9155,7 +9145,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9165,7 +9155,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9192,10 +9182,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122425328</v>
+        <v>122428074</v>
       </c>
       <c r="B78" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9208,34 +9198,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562678</v>
+        <v>562763</v>
       </c>
       <c r="R78" t="n">
-        <v>7039868</v>
+        <v>7039478</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9267,7 +9262,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9277,7 +9272,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -2677,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122426079</v>
+        <v>122425703</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2693,34 +2693,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562676</v>
+        <v>562654</v>
       </c>
       <c r="R20" t="n">
-        <v>7039760</v>
+        <v>7039819</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2779,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122429240</v>
+        <v>122426220</v>
       </c>
       <c r="B21" t="n">
-        <v>78392</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2795,34 +2800,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562497</v>
+        <v>562671</v>
       </c>
       <c r="R21" t="n">
-        <v>7039642</v>
+        <v>7039729</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2855,6 +2865,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2881,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122430062</v>
+        <v>122426079</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,21 +2912,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2921,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562624</v>
+        <v>562676</v>
       </c>
       <c r="R22" t="n">
-        <v>7039856</v>
+        <v>7039760</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2983,10 +2998,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122425703</v>
+        <v>122429240</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>78392</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,39 +3014,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562654</v>
+        <v>562497</v>
       </c>
       <c r="R23" t="n">
-        <v>7039819</v>
+        <v>7039642</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3090,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122426220</v>
+        <v>122430062</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3106,39 +3116,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562671</v>
+        <v>562624</v>
       </c>
       <c r="R24" t="n">
-        <v>7039729</v>
+        <v>7039856</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3171,11 +3176,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4897,10 +4897,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122427407</v>
+        <v>122425754</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4913,16 +4913,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4933,7 +4933,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4942,13 +4942,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562761</v>
+        <v>562652</v>
       </c>
       <c r="R40" t="n">
-        <v>7039655</v>
+        <v>7039805</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,24 +4975,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5007,22 +4997,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122425754</v>
+        <v>122427407</v>
       </c>
       <c r="B41" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5035,16 +5025,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5055,7 +5045,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5064,13 +5054,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562652</v>
+        <v>562761</v>
       </c>
       <c r="R41" t="n">
-        <v>7039805</v>
+        <v>7039655</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5097,14 +5087,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5119,12 +5119,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122425191</v>
+        <v>122428711</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5488,37 +5488,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562649</v>
+        <v>562889</v>
       </c>
       <c r="R45" t="n">
-        <v>7039883</v>
+        <v>7039463</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5545,9 +5550,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5562,19 +5582,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122427418</v>
+        <v>122425191</v>
       </c>
       <c r="B46" t="n">
         <v>79737</v>
@@ -5610,14 +5630,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562680</v>
+        <v>562649</v>
       </c>
       <c r="R46" t="n">
-        <v>7039626</v>
+        <v>7039883</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5676,10 +5696,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122428711</v>
+        <v>122427418</v>
       </c>
       <c r="B47" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5692,42 +5712,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562889</v>
+        <v>562680</v>
       </c>
       <c r="R47" t="n">
-        <v>7039463</v>
+        <v>7039626</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5754,24 +5769,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5786,22 +5786,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122425516</v>
+        <v>122425284</v>
       </c>
       <c r="B48" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5814,42 +5814,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562706</v>
+        <v>562657</v>
       </c>
       <c r="R48" t="n">
-        <v>7039810</v>
+        <v>7039870</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5876,24 +5871,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5908,19 +5888,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122425284</v>
+        <v>122425617</v>
       </c>
       <c r="B49" t="n">
         <v>79737</v>
@@ -5956,14 +5936,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562657</v>
+        <v>562648</v>
       </c>
       <c r="R49" t="n">
-        <v>7039870</v>
+        <v>7039837</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6022,10 +6002,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122425617</v>
+        <v>122425516</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6038,37 +6018,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562648</v>
+        <v>562706</v>
       </c>
       <c r="R50" t="n">
-        <v>7039837</v>
+        <v>7039810</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6095,9 +6080,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6112,12 +6112,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -8968,10 +8968,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122429992</v>
+        <v>122428074</v>
       </c>
       <c r="B76" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8984,37 +8984,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562620</v>
+        <v>562763</v>
       </c>
       <c r="R76" t="n">
-        <v>7039839</v>
+        <v>7039478</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9041,9 +9046,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9058,22 +9078,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122425544</v>
+        <v>122429992</v>
       </c>
       <c r="B77" t="n">
-        <v>78392</v>
+        <v>79737</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9086,21 +9106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9110,13 +9130,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562672</v>
+        <v>562620</v>
       </c>
       <c r="R77" t="n">
-        <v>7039840</v>
+        <v>7039839</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9143,19 +9163,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9170,22 +9180,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122428074</v>
+        <v>122425544</v>
       </c>
       <c r="B78" t="n">
-        <v>57383</v>
+        <v>78392</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9198,39 +9208,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562763</v>
+        <v>562672</v>
       </c>
       <c r="R78" t="n">
-        <v>7039478</v>
+        <v>7039840</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9262,7 +9267,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9272,12 +9277,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425780</v>
+        <v>122430183</v>
       </c>
       <c r="B5" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,34 +1039,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562725</v>
+        <v>562911</v>
       </c>
       <c r="R5" t="n">
-        <v>7039812</v>
+        <v>7039598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1113,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lunglav på rönn</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,22 +1133,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429969</v>
+        <v>122429005</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,34 +1161,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562604</v>
+        <v>562522</v>
       </c>
       <c r="R6" t="n">
-        <v>7039850</v>
+        <v>7039596</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1216,6 +1226,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122428645</v>
+        <v>122428711</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,37 +1273,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562509</v>
+        <v>562889</v>
       </c>
       <c r="R7" t="n">
-        <v>7039629</v>
+        <v>7039463</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,9 +1335,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1367,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430036</v>
+        <v>122430397</v>
       </c>
       <c r="B8" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,37 +1395,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562621</v>
+        <v>562890</v>
       </c>
       <c r="R8" t="n">
-        <v>7039854</v>
+        <v>7039728</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,9 +1457,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,19 +1489,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122428173</v>
+        <v>122429056</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1487,14 +1542,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562701</v>
+        <v>562996</v>
       </c>
       <c r="R9" t="n">
-        <v>7039441</v>
+        <v>7039422</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1581,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,12 +1591,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,22 +1611,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429056</v>
+        <v>122425405</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>74757</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,42 +1639,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562996</v>
+        <v>562648</v>
       </c>
       <c r="R10" t="n">
-        <v>7039422</v>
+        <v>7039865</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,24 +1696,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,22 +1713,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122427743</v>
+        <v>122429819</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,42 +1741,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562670</v>
+        <v>562600</v>
       </c>
       <c r="R11" t="n">
-        <v>7039613</v>
+        <v>7039877</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,24 +1798,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122427566</v>
+        <v>122430780</v>
       </c>
       <c r="B12" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,37 +1843,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562663</v>
+        <v>562903</v>
       </c>
       <c r="R12" t="n">
-        <v>7039574</v>
+        <v>7039567</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,9 +1905,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,19 +1932,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122429996</v>
+        <v>122425191</v>
       </c>
       <c r="B13" t="n">
         <v>79737</v>
@@ -1950,14 +1980,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562622</v>
+        <v>562649</v>
       </c>
       <c r="R13" t="n">
-        <v>7039843</v>
+        <v>7039883</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2016,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122429855</v>
+        <v>122427985</v>
       </c>
       <c r="B14" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,37 +2062,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562619</v>
+        <v>562695</v>
       </c>
       <c r="R14" t="n">
-        <v>7039840</v>
+        <v>7039574</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,9 +2124,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,22 +2156,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122429005</v>
+        <v>122425544</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78392</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,42 +2184,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562522</v>
+        <v>562672</v>
       </c>
       <c r="R15" t="n">
-        <v>7039596</v>
+        <v>7039840</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,14 +2241,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,22 +2268,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122428034</v>
+        <v>122429969</v>
       </c>
       <c r="B16" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,46 +2296,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562674</v>
+        <v>562604</v>
       </c>
       <c r="R16" t="n">
-        <v>7039543</v>
+        <v>7039850</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,19 +2353,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,22 +2370,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122427626</v>
+        <v>122425780</v>
       </c>
       <c r="B17" t="n">
-        <v>78392</v>
+        <v>79737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,21 +2398,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2391,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562773</v>
+        <v>562725</v>
       </c>
       <c r="R17" t="n">
-        <v>7039605</v>
+        <v>7039812</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,7 +2457,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2436,7 +2467,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,22 +2487,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122425405</v>
+        <v>122430036</v>
       </c>
       <c r="B18" t="n">
-        <v>74757</v>
+        <v>79738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2515,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562648</v>
+        <v>562621</v>
       </c>
       <c r="R18" t="n">
-        <v>7039865</v>
+        <v>7039854</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2565,10 +2601,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122425855</v>
+        <v>122426080</v>
       </c>
       <c r="B19" t="n">
-        <v>90857</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2617,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562731</v>
+        <v>562743</v>
       </c>
       <c r="R19" t="n">
-        <v>7039827</v>
+        <v>7039807</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,10 +2713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122425703</v>
+        <v>122429992</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2693,39 +2729,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562654</v>
+        <v>562620</v>
       </c>
       <c r="R20" t="n">
-        <v>7039819</v>
+        <v>7039839</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2784,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122426220</v>
+        <v>122425855</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,42 +2831,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562671</v>
+        <v>562731</v>
       </c>
       <c r="R21" t="n">
-        <v>7039729</v>
+        <v>7039827</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2862,14 +2888,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2884,22 +2915,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122426079</v>
+        <v>122426351</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,37 +2943,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562676</v>
+        <v>562771</v>
       </c>
       <c r="R22" t="n">
-        <v>7039760</v>
+        <v>7039744</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,9 +3005,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2986,22 +3037,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122429240</v>
+        <v>122426422</v>
       </c>
       <c r="B23" t="n">
-        <v>78392</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3014,37 +3065,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562497</v>
+        <v>562642</v>
       </c>
       <c r="R23" t="n">
-        <v>7039642</v>
+        <v>7039716</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3071,9 +3127,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,22 +3159,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122430062</v>
+        <v>122425516</v>
       </c>
       <c r="B24" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,37 +3187,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562624</v>
+        <v>562706</v>
       </c>
       <c r="R24" t="n">
-        <v>7039856</v>
+        <v>7039810</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,9 +3249,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3190,22 +3281,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122428307</v>
+        <v>122425242</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3218,39 +3309,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562557</v>
+        <v>562659</v>
       </c>
       <c r="R25" t="n">
-        <v>7039552</v>
+        <v>7039871</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3283,11 +3369,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3314,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429819</v>
+        <v>122428034</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3330,37 +3411,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562600</v>
+        <v>562674</v>
       </c>
       <c r="R26" t="n">
-        <v>7039877</v>
+        <v>7039543</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3387,9 +3477,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,22 +3504,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122430000</v>
+        <v>122425397</v>
       </c>
       <c r="B27" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3432,37 +3532,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562623</v>
+        <v>562662</v>
       </c>
       <c r="R27" t="n">
-        <v>7039843</v>
+        <v>7039854</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3489,9 +3594,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3506,22 +3626,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122425536</v>
+        <v>122429998</v>
       </c>
       <c r="B28" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3534,34 +3654,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562710</v>
+        <v>562999</v>
       </c>
       <c r="R28" t="n">
-        <v>7039834</v>
+        <v>7039523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3593,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3603,7 +3728,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,19 +3748,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122426187</v>
+        <v>122430000</v>
       </c>
       <c r="B29" t="n">
         <v>79737</v>
@@ -3670,13 +3800,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562759</v>
+        <v>562623</v>
       </c>
       <c r="R29" t="n">
-        <v>7039787</v>
+        <v>7039843</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3703,19 +3833,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3730,19 +3850,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122428148</v>
+        <v>122428124</v>
       </c>
       <c r="B30" t="n">
         <v>79737</v>
@@ -3782,13 +3902,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562707</v>
+        <v>562630</v>
       </c>
       <c r="R30" t="n">
-        <v>7039456</v>
+        <v>7039565</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,19 +3935,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,22 +3952,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425414</v>
+        <v>122425278</v>
       </c>
       <c r="B31" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3870,39 +3980,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562678</v>
+        <v>562673</v>
       </c>
       <c r="R31" t="n">
-        <v>7039855</v>
+        <v>7039869</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,7 +4039,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3944,12 +4049,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,7 +4076,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122425700</v>
+        <v>122427605</v>
       </c>
       <c r="B32" t="n">
         <v>57383</v>
@@ -4021,10 +4121,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562678</v>
+        <v>562687</v>
       </c>
       <c r="R32" t="n">
-        <v>7039813</v>
+        <v>7039594</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4156,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4066,7 +4166,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4086,22 +4186,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122427985</v>
+        <v>122427626</v>
       </c>
       <c r="B33" t="n">
-        <v>57383</v>
+        <v>78392</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4114,39 +4214,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562695</v>
+        <v>562773</v>
       </c>
       <c r="R33" t="n">
-        <v>7039574</v>
+        <v>7039605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4178,7 +4273,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4188,12 +4283,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4208,19 +4298,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122429000</v>
+        <v>122427953</v>
       </c>
       <c r="B34" t="n">
         <v>79737</v>
@@ -4256,17 +4346,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562984</v>
+        <v>562661</v>
       </c>
       <c r="R34" t="n">
-        <v>7039447</v>
+        <v>7039580</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4293,19 +4383,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4320,19 +4400,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122425242</v>
+        <v>122425536</v>
       </c>
       <c r="B35" t="n">
         <v>79737</v>
@@ -4368,17 +4448,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562659</v>
+        <v>562710</v>
       </c>
       <c r="R35" t="n">
-        <v>7039871</v>
+        <v>7039834</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4405,9 +4485,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4422,19 +4512,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122429588</v>
+        <v>122425539</v>
       </c>
       <c r="B36" t="n">
         <v>79737</v>
@@ -4474,10 +4564,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562549</v>
+        <v>562651</v>
       </c>
       <c r="R36" t="n">
-        <v>7039854</v>
+        <v>7039827</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4536,10 +4626,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122430274</v>
+        <v>122427566</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4552,42 +4642,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562903</v>
+        <v>562663</v>
       </c>
       <c r="R37" t="n">
-        <v>7039649</v>
+        <v>7039574</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4614,24 +4699,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4646,22 +4716,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122430816</v>
+        <v>122427824</v>
       </c>
       <c r="B38" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4674,39 +4744,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562845</v>
+        <v>562770</v>
       </c>
       <c r="R38" t="n">
-        <v>7039809</v>
+        <v>7039566</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4738,7 +4803,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4748,7 +4813,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4840,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122429998</v>
+        <v>122427645</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4791,39 +4856,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562999</v>
+        <v>562693</v>
       </c>
       <c r="R39" t="n">
-        <v>7039523</v>
+        <v>7039587</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4855,7 +4915,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4865,12 +4925,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4885,22 +4940,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122425754</v>
+        <v>122427407</v>
       </c>
       <c r="B40" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4913,16 +4968,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4933,7 +4988,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4942,13 +4997,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562652</v>
+        <v>562761</v>
       </c>
       <c r="R40" t="n">
-        <v>7039805</v>
+        <v>7039655</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,14 +5030,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4997,22 +5062,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122427407</v>
+        <v>122425331</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5025,42 +5090,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562761</v>
+        <v>562650</v>
       </c>
       <c r="R41" t="n">
-        <v>7039655</v>
+        <v>7039856</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5087,24 +5147,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5119,19 +5164,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122430780</v>
+        <v>122425754</v>
       </c>
       <c r="B42" t="n">
         <v>57399</v>
@@ -5167,7 +5212,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5176,13 +5221,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562903</v>
+        <v>562652</v>
       </c>
       <c r="R42" t="n">
-        <v>7039567</v>
+        <v>7039805</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5209,19 +5254,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:21</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5236,19 +5276,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427953</v>
+        <v>122427418</v>
       </c>
       <c r="B43" t="n">
         <v>79737</v>
@@ -5288,10 +5328,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562661</v>
+        <v>562680</v>
       </c>
       <c r="R43" t="n">
-        <v>7039580</v>
+        <v>7039626</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5350,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122425397</v>
+        <v>122430062</v>
       </c>
       <c r="B44" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5366,42 +5406,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562662</v>
+        <v>562624</v>
       </c>
       <c r="R44" t="n">
-        <v>7039854</v>
+        <v>7039856</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5428,24 +5463,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5460,22 +5480,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122428711</v>
+        <v>122425284</v>
       </c>
       <c r="B45" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5488,42 +5508,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562889</v>
+        <v>562657</v>
       </c>
       <c r="R45" t="n">
-        <v>7039463</v>
+        <v>7039870</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5550,24 +5565,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5582,22 +5582,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122425191</v>
+        <v>122428074</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5610,37 +5610,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562649</v>
+        <v>562763</v>
       </c>
       <c r="R46" t="n">
-        <v>7039883</v>
+        <v>7039478</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5667,9 +5672,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5684,22 +5704,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122427418</v>
+        <v>122427459</v>
       </c>
       <c r="B47" t="n">
-        <v>79737</v>
+        <v>98240</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5708,41 +5728,55 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562680</v>
+        <v>562755</v>
       </c>
       <c r="R47" t="n">
-        <v>7039626</v>
+        <v>7039631</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5769,9 +5803,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5786,22 +5830,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122425284</v>
+        <v>122426079</v>
       </c>
       <c r="B48" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5814,34 +5858,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562657</v>
+        <v>562676</v>
       </c>
       <c r="R48" t="n">
-        <v>7039870</v>
+        <v>7039760</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5900,7 +5944,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122425617</v>
+        <v>122429000</v>
       </c>
       <c r="B49" t="n">
         <v>79737</v>
@@ -5936,17 +5980,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562648</v>
+        <v>562984</v>
       </c>
       <c r="R49" t="n">
-        <v>7039837</v>
+        <v>7039447</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5973,9 +6017,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5990,19 +6044,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122425516</v>
+        <v>122426220</v>
       </c>
       <c r="B50" t="n">
         <v>57383</v>
@@ -6047,13 +6101,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562706</v>
+        <v>562671</v>
       </c>
       <c r="R50" t="n">
-        <v>7039810</v>
+        <v>7039729</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6080,24 +6134,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6112,22 +6156,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122427645</v>
+        <v>122428796</v>
       </c>
       <c r="B51" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6140,34 +6184,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562693</v>
+        <v>563001</v>
       </c>
       <c r="R51" t="n">
-        <v>7039587</v>
+        <v>7039421</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,7 +6248,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6209,7 +6258,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6236,10 +6290,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122427605</v>
+        <v>122427401</v>
       </c>
       <c r="B52" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6252,42 +6306,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562687</v>
+        <v>562674</v>
       </c>
       <c r="R52" t="n">
-        <v>7039594</v>
+        <v>7039653</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6314,24 +6363,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6346,19 +6380,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122428693</v>
+        <v>122430719</v>
       </c>
       <c r="B53" t="n">
         <v>57383</v>
@@ -6399,14 +6433,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562933</v>
+        <v>562835</v>
       </c>
       <c r="R53" t="n">
-        <v>7039394</v>
+        <v>7039750</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6438,7 +6472,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6448,7 +6482,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6468,19 +6502,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122427473</v>
+        <v>122428173</v>
       </c>
       <c r="B54" t="n">
         <v>57383</v>
@@ -6516,7 +6550,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6525,13 +6559,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562684</v>
+        <v>562701</v>
       </c>
       <c r="R54" t="n">
-        <v>7039617</v>
+        <v>7039441</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6558,14 +6592,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6580,19 +6624,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122426351</v>
+        <v>122427703</v>
       </c>
       <c r="B55" t="n">
         <v>57383</v>
@@ -6637,10 +6681,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562771</v>
+        <v>562784</v>
       </c>
       <c r="R55" t="n">
-        <v>7039744</v>
+        <v>7039590</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6672,7 +6716,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6682,12 +6726,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6702,22 +6746,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430397</v>
+        <v>122425617</v>
       </c>
       <c r="B56" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6730,42 +6774,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562890</v>
+        <v>562648</v>
       </c>
       <c r="R56" t="n">
-        <v>7039728</v>
+        <v>7039837</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6792,24 +6831,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6824,22 +6848,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122428692</v>
+        <v>122428148</v>
       </c>
       <c r="B57" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6852,42 +6876,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562502</v>
+        <v>562707</v>
       </c>
       <c r="R57" t="n">
-        <v>7039635</v>
+        <v>7039456</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6914,14 +6933,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6936,22 +6960,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122426059</v>
+        <v>122427473</v>
       </c>
       <c r="B58" t="n">
-        <v>82443</v>
+        <v>57383</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6964,34 +6988,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562673</v>
+        <v>562684</v>
       </c>
       <c r="R58" t="n">
-        <v>7039763</v>
+        <v>7039617</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7024,6 +7053,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7050,10 +7084,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122425278</v>
+        <v>122428307</v>
       </c>
       <c r="B59" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7066,37 +7100,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562673</v>
+        <v>562557</v>
       </c>
       <c r="R59" t="n">
-        <v>7039869</v>
+        <v>7039552</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7123,19 +7162,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7150,19 +7184,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122427618</v>
+        <v>122430274</v>
       </c>
       <c r="B60" t="n">
         <v>57383</v>
@@ -7198,7 +7232,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7207,13 +7241,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562674</v>
+        <v>562903</v>
       </c>
       <c r="R60" t="n">
-        <v>7039582</v>
+        <v>7039649</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7240,14 +7274,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7262,19 +7306,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122426422</v>
+        <v>122425414</v>
       </c>
       <c r="B61" t="n">
         <v>57383</v>
@@ -7310,7 +7354,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7319,10 +7363,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562642</v>
+        <v>562678</v>
       </c>
       <c r="R61" t="n">
-        <v>7039716</v>
+        <v>7039855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7354,7 +7398,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7364,12 +7408,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7384,22 +7428,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427703</v>
+        <v>122429240</v>
       </c>
       <c r="B62" t="n">
-        <v>57383</v>
+        <v>78392</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7412,42 +7456,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562784</v>
+        <v>562497</v>
       </c>
       <c r="R62" t="n">
-        <v>7039590</v>
+        <v>7039642</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7474,24 +7513,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7506,22 +7530,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122428796</v>
+        <v>122429588</v>
       </c>
       <c r="B63" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7534,42 +7558,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563001</v>
+        <v>562549</v>
       </c>
       <c r="R63" t="n">
-        <v>7039421</v>
+        <v>7039854</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7596,24 +7615,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7628,22 +7632,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122428124</v>
+        <v>122427743</v>
       </c>
       <c r="B64" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7656,37 +7660,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562630</v>
+        <v>562670</v>
       </c>
       <c r="R64" t="n">
-        <v>7039565</v>
+        <v>7039613</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7713,9 +7722,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7730,19 +7754,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122430719</v>
+        <v>122427618</v>
       </c>
       <c r="B65" t="n">
         <v>57383</v>
@@ -7787,13 +7811,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562835</v>
+        <v>562674</v>
       </c>
       <c r="R65" t="n">
-        <v>7039750</v>
+        <v>7039582</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7820,24 +7844,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7852,22 +7866,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122430183</v>
+        <v>122429596</v>
       </c>
       <c r="B66" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7880,42 +7894,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562911</v>
+        <v>562565</v>
       </c>
       <c r="R66" t="n">
-        <v>7039598</v>
+        <v>7039844</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7942,24 +7951,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7974,19 +7968,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122425328</v>
+        <v>122429855</v>
       </c>
       <c r="B67" t="n">
         <v>79737</v>
@@ -8022,17 +8016,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562678</v>
+        <v>562619</v>
       </c>
       <c r="R67" t="n">
-        <v>7039868</v>
+        <v>7039840</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8059,19 +8053,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8086,22 +8070,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122429596</v>
+        <v>122428693</v>
       </c>
       <c r="B68" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8114,37 +8098,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562565</v>
+        <v>562933</v>
       </c>
       <c r="R68" t="n">
-        <v>7039844</v>
+        <v>7039394</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8171,9 +8160,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8188,22 +8192,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122427824</v>
+        <v>122428692</v>
       </c>
       <c r="B69" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8216,37 +8220,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562770</v>
+        <v>562502</v>
       </c>
       <c r="R69" t="n">
-        <v>7039566</v>
+        <v>7039635</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8273,19 +8282,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:18</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8300,22 +8304,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122425310</v>
+        <v>122429996</v>
       </c>
       <c r="B70" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8328,21 +8332,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8352,13 +8356,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562650</v>
+        <v>562622</v>
       </c>
       <c r="R70" t="n">
-        <v>7039868</v>
+        <v>7039843</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8385,19 +8389,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8412,22 +8406,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425331</v>
+        <v>122425703</v>
       </c>
       <c r="B71" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8440,34 +8434,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562650</v>
+        <v>562654</v>
       </c>
       <c r="R71" t="n">
-        <v>7039856</v>
+        <v>7039819</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8526,10 +8525,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122426080</v>
+        <v>122428645</v>
       </c>
       <c r="B72" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8542,21 +8541,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8566,13 +8565,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562743</v>
+        <v>562509</v>
       </c>
       <c r="R72" t="n">
-        <v>7039807</v>
+        <v>7039629</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8599,19 +8598,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8626,22 +8615,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122427401</v>
+        <v>122426187</v>
       </c>
       <c r="B73" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8654,21 +8643,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8678,13 +8667,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562674</v>
+        <v>562759</v>
       </c>
       <c r="R73" t="n">
-        <v>7039653</v>
+        <v>7039787</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8711,9 +8700,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8728,22 +8727,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122425539</v>
+        <v>122425310</v>
       </c>
       <c r="B74" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8756,21 +8755,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8780,13 +8779,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562651</v>
+        <v>562650</v>
       </c>
       <c r="R74" t="n">
-        <v>7039827</v>
+        <v>7039868</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8813,9 +8812,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8830,22 +8839,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122427459</v>
+        <v>122425328</v>
       </c>
       <c r="B75" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8854,52 +8863,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562755</v>
+        <v>562678</v>
       </c>
       <c r="R75" t="n">
-        <v>7039631</v>
+        <v>7039868</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8931,7 +8926,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8941,7 +8936,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8956,22 +8951,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122428074</v>
+        <v>122426059</v>
       </c>
       <c r="B76" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8984,42 +8979,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562763</v>
+        <v>562673</v>
       </c>
       <c r="R76" t="n">
-        <v>7039478</v>
+        <v>7039763</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9046,24 +9036,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9078,22 +9053,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122429992</v>
+        <v>122430816</v>
       </c>
       <c r="B77" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9106,37 +9081,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562620</v>
+        <v>562845</v>
       </c>
       <c r="R77" t="n">
-        <v>7039839</v>
+        <v>7039809</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9163,9 +9143,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9180,22 +9170,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122425544</v>
+        <v>122425700</v>
       </c>
       <c r="B78" t="n">
-        <v>78392</v>
+        <v>57383</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9208,34 +9198,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562672</v>
+        <v>562678</v>
       </c>
       <c r="R78" t="n">
-        <v>7039840</v>
+        <v>7039813</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9267,7 +9262,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9277,7 +9272,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430183</v>
+        <v>122425855</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,39 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562911</v>
+        <v>562731</v>
       </c>
       <c r="R5" t="n">
-        <v>7039598</v>
+        <v>7039827</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,22 +1123,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429005</v>
+        <v>122427566</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,39 +1151,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562522</v>
+        <v>562663</v>
       </c>
       <c r="R6" t="n">
-        <v>7039596</v>
+        <v>7039574</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1226,11 +1211,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122428711</v>
+        <v>122429000</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,39 +1253,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562889</v>
+        <v>562984</v>
       </c>
       <c r="R7" t="n">
-        <v>7039463</v>
+        <v>7039447</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,12 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430397</v>
+        <v>122429596</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,42 +1365,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562890</v>
+        <v>562565</v>
       </c>
       <c r="R8" t="n">
-        <v>7039728</v>
+        <v>7039844</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,24 +1422,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,19 +1439,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429056</v>
+        <v>122430397</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1537,19 +1487,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562996</v>
+        <v>562890</v>
       </c>
       <c r="R9" t="n">
-        <v>7039422</v>
+        <v>7039728</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,12 +1541,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425405</v>
+        <v>122427985</v>
       </c>
       <c r="B10" t="n">
-        <v>74757</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,37 +1589,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562648</v>
+        <v>562695</v>
       </c>
       <c r="R10" t="n">
-        <v>7039865</v>
+        <v>7039574</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,9 +1651,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,22 +1683,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429819</v>
+        <v>122425284</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,34 +1711,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562600</v>
+        <v>562657</v>
       </c>
       <c r="R11" t="n">
-        <v>7039877</v>
+        <v>7039870</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1827,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122430780</v>
+        <v>122428796</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,16 +1813,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1868,14 +1838,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562903</v>
+        <v>563001</v>
       </c>
       <c r="R12" t="n">
-        <v>7039567</v>
+        <v>7039421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122425191</v>
+        <v>122429056</v>
       </c>
       <c r="B13" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,37 +1935,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562649</v>
+        <v>562996</v>
       </c>
       <c r="R13" t="n">
-        <v>7039883</v>
+        <v>7039422</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,9 +1997,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,19 +2029,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122427985</v>
+        <v>122429005</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2082,7 +2077,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2091,13 +2086,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562695</v>
+        <v>562522</v>
       </c>
       <c r="R14" t="n">
-        <v>7039574</v>
+        <v>7039596</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,24 +2119,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122425544</v>
+        <v>122427618</v>
       </c>
       <c r="B15" t="n">
-        <v>78392</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,37 +2169,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562672</v>
+        <v>562674</v>
       </c>
       <c r="R15" t="n">
-        <v>7039840</v>
+        <v>7039582</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2241,19 +2231,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:54</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,22 +2253,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122429969</v>
+        <v>122426422</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,37 +2281,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562604</v>
+        <v>562642</v>
       </c>
       <c r="R16" t="n">
-        <v>7039850</v>
+        <v>7039716</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2353,9 +2343,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,19 +2375,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122425780</v>
+        <v>122427953</v>
       </c>
       <c r="B17" t="n">
         <v>79737</v>
@@ -2422,13 +2427,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562725</v>
+        <v>562661</v>
       </c>
       <c r="R17" t="n">
-        <v>7039812</v>
+        <v>7039580</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,24 +2460,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,22 +2477,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122430036</v>
+        <v>122429240</v>
       </c>
       <c r="B18" t="n">
-        <v>79738</v>
+        <v>78392</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,21 +2505,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2539,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562621</v>
+        <v>562497</v>
       </c>
       <c r="R18" t="n">
-        <v>7039854</v>
+        <v>7039642</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2601,7 +2591,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122426080</v>
+        <v>122428124</v>
       </c>
       <c r="B19" t="n">
         <v>79737</v>
@@ -2641,13 +2631,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562743</v>
+        <v>562630</v>
       </c>
       <c r="R19" t="n">
-        <v>7039807</v>
+        <v>7039565</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2674,19 +2664,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,22 +2681,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122429992</v>
+        <v>122425414</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,37 +2709,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562620</v>
+        <v>562678</v>
       </c>
       <c r="R20" t="n">
-        <v>7039839</v>
+        <v>7039855</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2786,9 +2771,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,22 +2803,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122425855</v>
+        <v>122430062</v>
       </c>
       <c r="B21" t="n">
-        <v>90851</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2855,13 +2855,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562731</v>
+        <v>562624</v>
       </c>
       <c r="R21" t="n">
-        <v>7039827</v>
+        <v>7039856</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2888,19 +2888,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,19 +2905,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122426351</v>
+        <v>122427703</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2972,10 +2962,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562771</v>
+        <v>562784</v>
       </c>
       <c r="R22" t="n">
-        <v>7039744</v>
+        <v>7039590</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3007,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,12 +3007,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,19 +3027,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122426422</v>
+        <v>122430816</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -3085,7 +3075,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3094,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562642</v>
+        <v>562845</v>
       </c>
       <c r="R23" t="n">
-        <v>7039716</v>
+        <v>7039809</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,7 +3119,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3139,12 +3129,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3171,10 +3156,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122425516</v>
+        <v>122428148</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3187,39 +3172,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562706</v>
+        <v>562707</v>
       </c>
       <c r="R24" t="n">
-        <v>7039810</v>
+        <v>7039456</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,7 +3231,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3261,12 +3241,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,10 +3268,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122425242</v>
+        <v>122428034</v>
       </c>
       <c r="B25" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3309,37 +3284,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562659</v>
+        <v>562674</v>
       </c>
       <c r="R25" t="n">
-        <v>7039871</v>
+        <v>7039543</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3366,9 +3350,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,22 +3377,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122428034</v>
+        <v>122428307</v>
       </c>
       <c r="B26" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,31 +3405,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3444,13 +3434,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562674</v>
+        <v>562557</v>
       </c>
       <c r="R26" t="n">
-        <v>7039543</v>
+        <v>7039552</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3477,19 +3467,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3504,22 +3489,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122425397</v>
+        <v>122425242</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3532,42 +3517,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562662</v>
+        <v>562659</v>
       </c>
       <c r="R27" t="n">
-        <v>7039854</v>
+        <v>7039871</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,24 +3574,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,19 +3591,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122429998</v>
+        <v>122430274</v>
       </c>
       <c r="B28" t="n">
         <v>57383</v>
@@ -3674,19 +3639,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562999</v>
+        <v>562903</v>
       </c>
       <c r="R28" t="n">
-        <v>7039523</v>
+        <v>7039649</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3683,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3693,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3760,10 +3725,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122430000</v>
+        <v>122426220</v>
       </c>
       <c r="B29" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3776,34 +3741,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562623</v>
+        <v>562671</v>
       </c>
       <c r="R29" t="n">
-        <v>7039843</v>
+        <v>7039729</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3836,6 +3806,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3862,10 +3837,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122428124</v>
+        <v>122428074</v>
       </c>
       <c r="B30" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3878,37 +3853,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562630</v>
+        <v>562763</v>
       </c>
       <c r="R30" t="n">
-        <v>7039565</v>
+        <v>7039478</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3935,9 +3915,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,22 +3947,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425278</v>
+        <v>122430036</v>
       </c>
       <c r="B31" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3980,37 +3975,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562673</v>
+        <v>562621</v>
       </c>
       <c r="R31" t="n">
-        <v>7039869</v>
+        <v>7039854</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4037,19 +4032,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,22 +4049,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122427605</v>
+        <v>122425536</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4092,39 +4077,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562687</v>
+        <v>562710</v>
       </c>
       <c r="R32" t="n">
-        <v>7039594</v>
+        <v>7039834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4166,12 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4198,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122427626</v>
+        <v>122429996</v>
       </c>
       <c r="B33" t="n">
-        <v>78392</v>
+        <v>79737</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4214,21 +4189,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4238,13 +4213,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562773</v>
+        <v>562622</v>
       </c>
       <c r="R33" t="n">
-        <v>7039605</v>
+        <v>7039843</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4271,19 +4246,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4298,19 +4263,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122427953</v>
+        <v>122425780</v>
       </c>
       <c r="B34" t="n">
         <v>79737</v>
@@ -4350,13 +4315,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562661</v>
+        <v>562725</v>
       </c>
       <c r="R34" t="n">
-        <v>7039580</v>
+        <v>7039812</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4383,9 +4348,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4400,22 +4380,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122425536</v>
+        <v>122426059</v>
       </c>
       <c r="B35" t="n">
-        <v>79737</v>
+        <v>82443</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4428,21 +4408,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4452,13 +4432,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562710</v>
+        <v>562673</v>
       </c>
       <c r="R35" t="n">
-        <v>7039834</v>
+        <v>7039763</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4485,19 +4465,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,22 +4482,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122425539</v>
+        <v>122426079</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4540,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4564,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562651</v>
+        <v>562676</v>
       </c>
       <c r="R36" t="n">
-        <v>7039827</v>
+        <v>7039760</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4626,7 +4596,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122427566</v>
+        <v>122425617</v>
       </c>
       <c r="B37" t="n">
         <v>79737</v>
@@ -4666,10 +4636,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562663</v>
+        <v>562648</v>
       </c>
       <c r="R37" t="n">
-        <v>7039574</v>
+        <v>7039837</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4728,10 +4698,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122427824</v>
+        <v>122428645</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4744,21 +4714,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4768,13 +4738,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562770</v>
+        <v>562509</v>
       </c>
       <c r="R38" t="n">
-        <v>7039566</v>
+        <v>7039629</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4801,19 +4771,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,22 +4788,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122427645</v>
+        <v>122425331</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4856,21 +4816,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4880,13 +4840,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562693</v>
+        <v>562650</v>
       </c>
       <c r="R39" t="n">
-        <v>7039587</v>
+        <v>7039856</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4913,19 +4873,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4940,22 +4890,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122427407</v>
+        <v>122429992</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4968,42 +4918,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562761</v>
+        <v>562620</v>
       </c>
       <c r="R40" t="n">
-        <v>7039655</v>
+        <v>7039839</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5030,24 +4975,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5062,22 +4992,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122425331</v>
+        <v>122425405</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,21 +5020,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5114,10 +5044,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562650</v>
+        <v>562648</v>
       </c>
       <c r="R41" t="n">
-        <v>7039856</v>
+        <v>7039865</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5176,10 +5106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122425754</v>
+        <v>122426080</v>
       </c>
       <c r="B42" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5192,42 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562652</v>
+        <v>562743</v>
       </c>
       <c r="R42" t="n">
-        <v>7039805</v>
+        <v>7039807</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5254,14 +5179,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Stor bohål i aso</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,19 +5206,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427418</v>
+        <v>122429855</v>
       </c>
       <c r="B43" t="n">
         <v>79737</v>
@@ -5328,10 +5258,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562680</v>
+        <v>562619</v>
       </c>
       <c r="R43" t="n">
-        <v>7039626</v>
+        <v>7039840</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5390,7 +5320,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122430062</v>
+        <v>122427645</v>
       </c>
       <c r="B44" t="n">
         <v>79737</v>
@@ -5430,13 +5360,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562624</v>
+        <v>562693</v>
       </c>
       <c r="R44" t="n">
-        <v>7039856</v>
+        <v>7039587</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5463,9 +5393,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5480,22 +5420,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122425284</v>
+        <v>122428173</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5508,37 +5448,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562657</v>
+        <v>562701</v>
       </c>
       <c r="R45" t="n">
-        <v>7039870</v>
+        <v>7039441</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5565,9 +5510,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5582,22 +5542,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122428074</v>
+        <v>122425191</v>
       </c>
       <c r="B46" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5610,42 +5570,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562763</v>
+        <v>562649</v>
       </c>
       <c r="R46" t="n">
-        <v>7039478</v>
+        <v>7039883</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5672,24 +5627,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5704,22 +5644,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122427459</v>
+        <v>122427401</v>
       </c>
       <c r="B47" t="n">
-        <v>98240</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5728,55 +5668,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562755</v>
+        <v>562674</v>
       </c>
       <c r="R47" t="n">
-        <v>7039631</v>
+        <v>7039653</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5803,19 +5729,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,22 +5746,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122426079</v>
+        <v>122425516</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5858,37 +5774,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562676</v>
+        <v>562706</v>
       </c>
       <c r="R48" t="n">
-        <v>7039760</v>
+        <v>7039810</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5915,9 +5836,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5932,22 +5868,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122429000</v>
+        <v>122427626</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>78392</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5960,34 +5896,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562984</v>
+        <v>562773</v>
       </c>
       <c r="R49" t="n">
-        <v>7039447</v>
+        <v>7039605</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6019,7 +5955,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6029,7 +5965,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6056,10 +5992,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122426220</v>
+        <v>122430000</v>
       </c>
       <c r="B50" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6072,39 +6008,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562671</v>
+        <v>562623</v>
       </c>
       <c r="R50" t="n">
-        <v>7039729</v>
+        <v>7039843</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6137,11 +6068,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6168,10 +6094,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122428796</v>
+        <v>122425278</v>
       </c>
       <c r="B51" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6184,39 +6110,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563001</v>
+        <v>562673</v>
       </c>
       <c r="R51" t="n">
-        <v>7039421</v>
+        <v>7039869</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6248,7 +6169,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6258,12 +6179,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6290,7 +6206,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122427401</v>
+        <v>122429969</v>
       </c>
       <c r="B52" t="n">
         <v>78656</v>
@@ -6330,10 +6246,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562674</v>
+        <v>562604</v>
       </c>
       <c r="R52" t="n">
-        <v>7039653</v>
+        <v>7039850</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6392,10 +6308,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122430719</v>
+        <v>122425544</v>
       </c>
       <c r="B53" t="n">
-        <v>57383</v>
+        <v>78392</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6408,39 +6324,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562835</v>
+        <v>562672</v>
       </c>
       <c r="R53" t="n">
-        <v>7039750</v>
+        <v>7039840</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6472,7 +6383,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6482,12 +6393,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6514,10 +6420,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428173</v>
+        <v>122429588</v>
       </c>
       <c r="B54" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6530,42 +6436,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562701</v>
+        <v>562549</v>
       </c>
       <c r="R54" t="n">
-        <v>7039441</v>
+        <v>7039854</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6592,24 +6493,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6624,22 +6510,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122427703</v>
+        <v>122430780</v>
       </c>
       <c r="B55" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6652,16 +6538,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6681,10 +6567,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562784</v>
+        <v>562903</v>
       </c>
       <c r="R55" t="n">
-        <v>7039590</v>
+        <v>7039567</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6716,7 +6602,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6726,12 +6612,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6746,22 +6627,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122425617</v>
+        <v>122430719</v>
       </c>
       <c r="B56" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6774,37 +6655,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562648</v>
+        <v>562835</v>
       </c>
       <c r="R56" t="n">
-        <v>7039837</v>
+        <v>7039750</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6831,9 +6717,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6848,22 +6749,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122428148</v>
+        <v>122427473</v>
       </c>
       <c r="B57" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6876,37 +6777,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562707</v>
+        <v>562684</v>
       </c>
       <c r="R57" t="n">
-        <v>7039456</v>
+        <v>7039617</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6933,19 +6839,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:35</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6960,22 +6861,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122427473</v>
+        <v>122425539</v>
       </c>
       <c r="B58" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6988,39 +6889,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562684</v>
+        <v>562651</v>
       </c>
       <c r="R58" t="n">
-        <v>7039617</v>
+        <v>7039827</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7053,11 +6949,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7084,7 +6975,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122428307</v>
+        <v>122430183</v>
       </c>
       <c r="B59" t="n">
         <v>57383</v>
@@ -7129,13 +7020,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562557</v>
+        <v>562911</v>
       </c>
       <c r="R59" t="n">
-        <v>7039552</v>
+        <v>7039598</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7162,14 +7053,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7184,19 +7085,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122430274</v>
+        <v>122428693</v>
       </c>
       <c r="B60" t="n">
         <v>57383</v>
@@ -7232,19 +7133,19 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562903</v>
+        <v>562933</v>
       </c>
       <c r="R60" t="n">
-        <v>7039649</v>
+        <v>7039394</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7276,7 +7177,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7286,7 +7187,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7306,19 +7207,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122425414</v>
+        <v>122428692</v>
       </c>
       <c r="B61" t="n">
         <v>57383</v>
@@ -7354,7 +7255,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7363,13 +7264,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562678</v>
+        <v>562502</v>
       </c>
       <c r="R61" t="n">
-        <v>7039855</v>
+        <v>7039635</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7396,24 +7297,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7428,22 +7319,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122429240</v>
+        <v>122427743</v>
       </c>
       <c r="B62" t="n">
-        <v>78392</v>
+        <v>57383</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7456,37 +7347,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562497</v>
+        <v>562670</v>
       </c>
       <c r="R62" t="n">
-        <v>7039642</v>
+        <v>7039613</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7513,9 +7409,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7530,22 +7441,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122429588</v>
+        <v>122426351</v>
       </c>
       <c r="B63" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7558,37 +7469,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562549</v>
+        <v>562771</v>
       </c>
       <c r="R63" t="n">
-        <v>7039854</v>
+        <v>7039744</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7615,9 +7531,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7632,22 +7563,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427743</v>
+        <v>122425703</v>
       </c>
       <c r="B64" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7660,16 +7591,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7680,7 +7611,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7689,13 +7620,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562670</v>
+        <v>562654</v>
       </c>
       <c r="R64" t="n">
-        <v>7039613</v>
+        <v>7039819</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7722,24 +7653,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7754,22 +7670,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427618</v>
+        <v>122427459</v>
       </c>
       <c r="B65" t="n">
-        <v>57383</v>
+        <v>98240</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7778,31 +7694,40 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7811,13 +7736,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562674</v>
+        <v>562755</v>
       </c>
       <c r="R65" t="n">
-        <v>7039582</v>
+        <v>7039631</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7844,14 +7769,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7866,22 +7796,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122429596</v>
+        <v>122429819</v>
       </c>
       <c r="B66" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7894,21 +7824,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7918,10 +7848,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562565</v>
+        <v>562600</v>
       </c>
       <c r="R66" t="n">
-        <v>7039844</v>
+        <v>7039877</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7980,7 +7910,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122429855</v>
+        <v>122426187</v>
       </c>
       <c r="B67" t="n">
         <v>79737</v>
@@ -8020,13 +7950,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562619</v>
+        <v>562759</v>
       </c>
       <c r="R67" t="n">
-        <v>7039840</v>
+        <v>7039787</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8053,9 +7983,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8070,22 +8010,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122428693</v>
+        <v>122425310</v>
       </c>
       <c r="B68" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8098,39 +8038,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562933</v>
+        <v>562650</v>
       </c>
       <c r="R68" t="n">
-        <v>7039394</v>
+        <v>7039868</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8162,7 +8097,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8172,12 +8107,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8192,19 +8122,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122428692</v>
+        <v>122427605</v>
       </c>
       <c r="B69" t="n">
         <v>57383</v>
@@ -8240,7 +8170,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8249,13 +8179,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562502</v>
+        <v>562687</v>
       </c>
       <c r="R69" t="n">
-        <v>7039635</v>
+        <v>7039594</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8282,14 +8212,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8304,22 +8244,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122429996</v>
+        <v>122427407</v>
       </c>
       <c r="B70" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8332,37 +8272,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562622</v>
+        <v>562761</v>
       </c>
       <c r="R70" t="n">
-        <v>7039843</v>
+        <v>7039655</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8389,9 +8334,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8406,22 +8366,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425703</v>
+        <v>122427418</v>
       </c>
       <c r="B71" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8434,39 +8394,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562654</v>
+        <v>562680</v>
       </c>
       <c r="R71" t="n">
-        <v>7039819</v>
+        <v>7039626</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8525,10 +8480,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122428645</v>
+        <v>122425397</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8541,37 +8496,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562509</v>
+        <v>562662</v>
       </c>
       <c r="R72" t="n">
-        <v>7039629</v>
+        <v>7039854</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8598,9 +8558,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8615,22 +8590,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122426187</v>
+        <v>122425700</v>
       </c>
       <c r="B73" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8643,34 +8618,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562759</v>
+        <v>562678</v>
       </c>
       <c r="R73" t="n">
-        <v>7039787</v>
+        <v>7039813</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8702,7 +8682,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8712,7 +8692,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8727,22 +8712,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122425310</v>
+        <v>122429998</v>
       </c>
       <c r="B74" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8755,34 +8740,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562650</v>
+        <v>562999</v>
       </c>
       <c r="R74" t="n">
-        <v>7039868</v>
+        <v>7039523</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8814,7 +8804,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8824,7 +8814,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8851,10 +8846,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122425328</v>
+        <v>122425754</v>
       </c>
       <c r="B75" t="n">
-        <v>79737</v>
+        <v>57399</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8867,37 +8862,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562678</v>
+        <v>562652</v>
       </c>
       <c r="R75" t="n">
-        <v>7039868</v>
+        <v>7039805</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8924,19 +8924,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8951,22 +8946,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122426059</v>
+        <v>122427824</v>
       </c>
       <c r="B76" t="n">
-        <v>82443</v>
+        <v>79737</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8979,21 +8974,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9003,13 +8998,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562673</v>
+        <v>562770</v>
       </c>
       <c r="R76" t="n">
-        <v>7039763</v>
+        <v>7039566</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9036,9 +9031,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9053,22 +9058,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122430816</v>
+        <v>122425328</v>
       </c>
       <c r="B77" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9081,39 +9086,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562845</v>
+        <v>562678</v>
       </c>
       <c r="R77" t="n">
-        <v>7039809</v>
+        <v>7039868</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9170,19 +9170,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122425700</v>
+        <v>122428711</v>
       </c>
       <c r="B78" t="n">
         <v>57383</v>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562678</v>
+        <v>562889</v>
       </c>
       <c r="R78" t="n">
-        <v>7039813</v>
+        <v>7039463</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425855</v>
+        <v>122427401</v>
       </c>
       <c r="B5" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562731</v>
+        <v>562674</v>
       </c>
       <c r="R5" t="n">
-        <v>7039827</v>
+        <v>7039653</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1096,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1113,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427566</v>
+        <v>122425780</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562663</v>
+        <v>562725</v>
       </c>
       <c r="R6" t="n">
-        <v>7039574</v>
+        <v>7039812</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,9 +1198,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1230,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429000</v>
+        <v>122427418</v>
       </c>
       <c r="B7" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,17 +1278,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562984</v>
+        <v>562680</v>
       </c>
       <c r="R7" t="n">
-        <v>7039447</v>
+        <v>7039626</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,19 +1315,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,22 +1332,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429596</v>
+        <v>122430183</v>
       </c>
       <c r="B8" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,37 +1360,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562565</v>
+        <v>562911</v>
       </c>
       <c r="R8" t="n">
-        <v>7039844</v>
+        <v>7039598</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,9 +1422,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,22 +1454,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430397</v>
+        <v>122428173</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,7 +1502,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562890</v>
+        <v>562701</v>
       </c>
       <c r="R9" t="n">
-        <v>7039728</v>
+        <v>7039441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,12 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1576,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122427985</v>
+        <v>122430397</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,7 +1624,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1618,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562695</v>
+        <v>562890</v>
       </c>
       <c r="R10" t="n">
-        <v>7039574</v>
+        <v>7039728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425284</v>
+        <v>122430816</v>
       </c>
       <c r="B11" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,37 +1726,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562657</v>
+        <v>562845</v>
       </c>
       <c r="R11" t="n">
-        <v>7039870</v>
+        <v>7039809</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,9 +1788,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122428796</v>
+        <v>122428645</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,42 +1843,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563001</v>
+        <v>562509</v>
       </c>
       <c r="R12" t="n">
-        <v>7039421</v>
+        <v>7039629</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,24 +1900,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122429056</v>
+        <v>122425191</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,42 +1945,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562996</v>
+        <v>562649</v>
       </c>
       <c r="R13" t="n">
-        <v>7039422</v>
+        <v>7039883</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,24 +2002,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,22 +2019,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122429005</v>
+        <v>122428148</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,42 +2047,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562522</v>
+        <v>562707</v>
       </c>
       <c r="R14" t="n">
-        <v>7039596</v>
+        <v>7039456</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,14 +2104,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2131,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122427618</v>
+        <v>122425284</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,39 +2159,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562674</v>
+        <v>562657</v>
       </c>
       <c r="R15" t="n">
-        <v>7039582</v>
+        <v>7039870</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2234,11 +2219,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122426422</v>
+        <v>122429596</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,42 +2261,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562642</v>
+        <v>562565</v>
       </c>
       <c r="R16" t="n">
-        <v>7039716</v>
+        <v>7039844</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2343,24 +2318,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,22 +2335,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122427953</v>
+        <v>122430274</v>
       </c>
       <c r="B17" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,37 +2363,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562661</v>
+        <v>562903</v>
       </c>
       <c r="R17" t="n">
-        <v>7039580</v>
+        <v>7039649</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,9 +2425,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,22 +2457,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122429240</v>
+        <v>122428711</v>
       </c>
       <c r="B18" t="n">
-        <v>78392</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,37 +2485,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562497</v>
+        <v>562889</v>
       </c>
       <c r="R18" t="n">
-        <v>7039642</v>
+        <v>7039463</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2562,9 +2547,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,22 +2579,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122428124</v>
+        <v>122425544</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>78393</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562630</v>
+        <v>562672</v>
       </c>
       <c r="R19" t="n">
-        <v>7039565</v>
+        <v>7039840</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2664,9 +2664,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,22 +2691,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122425414</v>
+        <v>122425855</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,39 +2719,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562678</v>
+        <v>562731</v>
       </c>
       <c r="R20" t="n">
-        <v>7039855</v>
+        <v>7039827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,12 +2788,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122430062</v>
+        <v>122427953</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562624</v>
+        <v>562661</v>
       </c>
       <c r="R21" t="n">
-        <v>7039856</v>
+        <v>7039580</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427703</v>
+        <v>122429588</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,42 +2933,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562784</v>
+        <v>562549</v>
       </c>
       <c r="R22" t="n">
-        <v>7039590</v>
+        <v>7039854</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2995,24 +2990,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,22 +3007,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122430816</v>
+        <v>122427703</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3084,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562845</v>
+        <v>562784</v>
       </c>
       <c r="R23" t="n">
-        <v>7039809</v>
+        <v>7039590</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3119,7 +3099,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3109,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,10 +3141,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122428148</v>
+        <v>122425331</v>
       </c>
       <c r="B24" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3172,21 +3157,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3196,13 +3181,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562707</v>
+        <v>562650</v>
       </c>
       <c r="R24" t="n">
-        <v>7039456</v>
+        <v>7039856</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3229,19 +3214,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,22 +3231,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122428034</v>
+        <v>122430062</v>
       </c>
       <c r="B25" t="n">
-        <v>57536</v>
+        <v>79738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3284,46 +3259,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562674</v>
+        <v>562624</v>
       </c>
       <c r="R25" t="n">
-        <v>7039543</v>
+        <v>7039856</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3350,19 +3316,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,22 +3333,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122428307</v>
+        <v>122425700</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3434,13 +3390,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562557</v>
+        <v>562678</v>
       </c>
       <c r="R26" t="n">
-        <v>7039552</v>
+        <v>7039813</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3467,14 +3423,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,22 +3455,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122425242</v>
+        <v>122430719</v>
       </c>
       <c r="B27" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3517,37 +3483,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562659</v>
+        <v>562835</v>
       </c>
       <c r="R27" t="n">
-        <v>7039871</v>
+        <v>7039750</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3574,9 +3545,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,22 +3577,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122430274</v>
+        <v>122428796</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3639,19 +3625,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562903</v>
+        <v>563001</v>
       </c>
       <c r="R28" t="n">
-        <v>7039649</v>
+        <v>7039421</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3683,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3693,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3713,22 +3699,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122426220</v>
+        <v>122427459</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>98241</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,31 +3723,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3770,13 +3765,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562671</v>
+        <v>562755</v>
       </c>
       <c r="R29" t="n">
-        <v>7039729</v>
+        <v>7039631</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3803,14 +3798,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,22 +3825,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122428074</v>
+        <v>122429992</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3853,42 +3853,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562763</v>
+        <v>562620</v>
       </c>
       <c r="R30" t="n">
-        <v>7039478</v>
+        <v>7039839</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3915,24 +3910,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3947,22 +3927,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122430036</v>
+        <v>122428693</v>
       </c>
       <c r="B31" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3975,37 +3955,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562621</v>
+        <v>562933</v>
       </c>
       <c r="R31" t="n">
-        <v>7039854</v>
+        <v>7039394</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4032,9 +4017,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,22 +4049,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122425536</v>
+        <v>122425310</v>
       </c>
       <c r="B32" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4077,21 +4077,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562710</v>
+        <v>562650</v>
       </c>
       <c r="R32" t="n">
-        <v>7039834</v>
+        <v>7039868</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4161,22 +4161,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122429996</v>
+        <v>122428307</v>
       </c>
       <c r="B33" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4189,34 +4189,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562622</v>
+        <v>562557</v>
       </c>
       <c r="R33" t="n">
-        <v>7039843</v>
+        <v>7039552</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4249,6 +4254,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4275,10 +4285,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122425780</v>
+        <v>122429996</v>
       </c>
       <c r="B34" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4315,13 +4325,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562725</v>
+        <v>562622</v>
       </c>
       <c r="R34" t="n">
-        <v>7039812</v>
+        <v>7039843</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4348,24 +4358,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,22 +4375,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122426059</v>
+        <v>122427824</v>
       </c>
       <c r="B35" t="n">
-        <v>82443</v>
+        <v>79738</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4408,21 +4403,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4432,13 +4427,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562673</v>
+        <v>562770</v>
       </c>
       <c r="R35" t="n">
-        <v>7039763</v>
+        <v>7039566</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4465,9 +4460,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4482,22 +4487,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122426079</v>
+        <v>122425278</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4510,37 +4515,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562676</v>
+        <v>562673</v>
       </c>
       <c r="R36" t="n">
-        <v>7039760</v>
+        <v>7039869</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4567,9 +4572,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4584,22 +4599,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122425617</v>
+        <v>122426059</v>
       </c>
       <c r="B37" t="n">
-        <v>79737</v>
+        <v>82444</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4612,21 +4627,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4636,10 +4651,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562648</v>
+        <v>562673</v>
       </c>
       <c r="R37" t="n">
-        <v>7039837</v>
+        <v>7039763</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4698,10 +4713,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122428645</v>
+        <v>122427985</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4714,37 +4729,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562509</v>
+        <v>562695</v>
       </c>
       <c r="R38" t="n">
-        <v>7039629</v>
+        <v>7039574</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4771,9 +4791,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4788,22 +4823,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425331</v>
+        <v>122427407</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4816,37 +4851,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562650</v>
+        <v>562761</v>
       </c>
       <c r="R39" t="n">
-        <v>7039856</v>
+        <v>7039655</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4873,9 +4913,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,22 +4945,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122429992</v>
+        <v>122425397</v>
       </c>
       <c r="B40" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4918,37 +4973,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562620</v>
+        <v>562662</v>
       </c>
       <c r="R40" t="n">
-        <v>7039839</v>
+        <v>7039854</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,9 +5035,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4992,22 +5067,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122425405</v>
+        <v>122426187</v>
       </c>
       <c r="B41" t="n">
-        <v>74757</v>
+        <v>79738</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5020,21 +5095,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5044,13 +5119,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562648</v>
+        <v>562759</v>
       </c>
       <c r="R41" t="n">
-        <v>7039865</v>
+        <v>7039787</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5077,9 +5152,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5094,22 +5179,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122426080</v>
+        <v>122425405</v>
       </c>
       <c r="B42" t="n">
-        <v>79737</v>
+        <v>74758</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5122,21 +5207,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5146,13 +5231,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562743</v>
+        <v>562648</v>
       </c>
       <c r="R42" t="n">
-        <v>7039807</v>
+        <v>7039865</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5179,19 +5264,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5206,22 +5281,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122429855</v>
+        <v>122427473</v>
       </c>
       <c r="B43" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5234,34 +5309,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562619</v>
+        <v>562684</v>
       </c>
       <c r="R43" t="n">
-        <v>7039840</v>
+        <v>7039617</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5294,6 +5374,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5320,10 +5405,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122427645</v>
+        <v>122427743</v>
       </c>
       <c r="B44" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5336,34 +5421,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562693</v>
+        <v>562670</v>
       </c>
       <c r="R44" t="n">
-        <v>7039587</v>
+        <v>7039613</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5395,7 +5485,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5405,7 +5495,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5432,10 +5527,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122428173</v>
+        <v>122429969</v>
       </c>
       <c r="B45" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5448,42 +5543,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562701</v>
+        <v>562604</v>
       </c>
       <c r="R45" t="n">
-        <v>7039441</v>
+        <v>7039850</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5510,24 +5600,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5542,22 +5617,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122425191</v>
+        <v>122425242</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5594,10 +5669,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562649</v>
+        <v>562659</v>
       </c>
       <c r="R46" t="n">
-        <v>7039883</v>
+        <v>7039871</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5656,10 +5731,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122427401</v>
+        <v>122429855</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5672,21 +5747,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5696,10 +5771,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562674</v>
+        <v>562619</v>
       </c>
       <c r="R47" t="n">
-        <v>7039653</v>
+        <v>7039840</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5758,10 +5833,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122425516</v>
+        <v>122429240</v>
       </c>
       <c r="B48" t="n">
-        <v>57383</v>
+        <v>78393</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5774,42 +5849,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562706</v>
+        <v>562497</v>
       </c>
       <c r="R48" t="n">
-        <v>7039810</v>
+        <v>7039642</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5836,24 +5906,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5868,22 +5923,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122427626</v>
+        <v>122430036</v>
       </c>
       <c r="B49" t="n">
-        <v>78392</v>
+        <v>79739</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5896,21 +5951,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5920,13 +5975,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562773</v>
+        <v>562621</v>
       </c>
       <c r="R49" t="n">
-        <v>7039605</v>
+        <v>7039854</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5953,19 +6008,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5980,22 +6025,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122430000</v>
+        <v>122430780</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
+        <v>57400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6008,37 +6053,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562623</v>
+        <v>562903</v>
       </c>
       <c r="R50" t="n">
-        <v>7039843</v>
+        <v>7039567</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6065,9 +6115,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6082,22 +6142,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122425278</v>
+        <v>122425516</v>
       </c>
       <c r="B51" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6110,34 +6170,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562673</v>
+        <v>562706</v>
       </c>
       <c r="R51" t="n">
-        <v>7039869</v>
+        <v>7039810</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6169,7 +6234,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6179,7 +6244,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6206,10 +6276,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122429969</v>
+        <v>122428074</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6222,37 +6292,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562604</v>
+        <v>562763</v>
       </c>
       <c r="R52" t="n">
-        <v>7039850</v>
+        <v>7039478</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6279,9 +6354,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,22 +6386,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122425544</v>
+        <v>122427645</v>
       </c>
       <c r="B53" t="n">
-        <v>78392</v>
+        <v>79738</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6324,21 +6414,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6348,10 +6438,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562672</v>
+        <v>562693</v>
       </c>
       <c r="R53" t="n">
-        <v>7039840</v>
+        <v>7039587</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6383,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6393,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6408,22 +6498,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122429588</v>
+        <v>122429056</v>
       </c>
       <c r="B54" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6436,37 +6526,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562549</v>
+        <v>562996</v>
       </c>
       <c r="R54" t="n">
-        <v>7039854</v>
+        <v>7039422</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6493,9 +6588,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6510,22 +6620,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122430780</v>
+        <v>122427566</v>
       </c>
       <c r="B55" t="n">
-        <v>57399</v>
+        <v>79738</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6538,42 +6648,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562903</v>
+        <v>562663</v>
       </c>
       <c r="R55" t="n">
-        <v>7039567</v>
+        <v>7039574</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6600,19 +6705,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6627,22 +6722,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430719</v>
+        <v>122430000</v>
       </c>
       <c r="B56" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6655,42 +6750,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562835</v>
+        <v>562623</v>
       </c>
       <c r="R56" t="n">
-        <v>7039750</v>
+        <v>7039843</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6717,24 +6807,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,22 +6824,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427473</v>
+        <v>122427618</v>
       </c>
       <c r="B57" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6797,7 +6872,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6806,10 +6881,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562684</v>
+        <v>562674</v>
       </c>
       <c r="R57" t="n">
-        <v>7039617</v>
+        <v>7039582</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6846,7 +6921,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6873,10 +6948,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122425539</v>
+        <v>122428034</v>
       </c>
       <c r="B58" t="n">
-        <v>79737</v>
+        <v>57537</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6889,37 +6964,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562651</v>
+        <v>562674</v>
       </c>
       <c r="R58" t="n">
-        <v>7039827</v>
+        <v>7039543</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6946,9 +7030,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6963,22 +7057,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122430183</v>
+        <v>122426220</v>
       </c>
       <c r="B59" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7020,13 +7114,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562911</v>
+        <v>562671</v>
       </c>
       <c r="R59" t="n">
-        <v>7039598</v>
+        <v>7039729</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7053,24 +7147,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7085,22 +7169,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122428693</v>
+        <v>122428692</v>
       </c>
       <c r="B60" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7133,22 +7217,22 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562933</v>
+        <v>562502</v>
       </c>
       <c r="R60" t="n">
-        <v>7039394</v>
+        <v>7039635</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7175,24 +7259,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7207,22 +7281,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122428692</v>
+        <v>122425414</v>
       </c>
       <c r="B61" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7255,7 +7329,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7264,13 +7338,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562502</v>
+        <v>562678</v>
       </c>
       <c r="R61" t="n">
-        <v>7039635</v>
+        <v>7039855</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7297,14 +7371,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7319,22 +7403,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427743</v>
+        <v>122429819</v>
       </c>
       <c r="B62" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7347,42 +7431,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562670</v>
+        <v>562600</v>
       </c>
       <c r="R62" t="n">
-        <v>7039613</v>
+        <v>7039877</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7409,24 +7488,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7441,22 +7505,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122426351</v>
+        <v>122426079</v>
       </c>
       <c r="B63" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7469,42 +7533,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562771</v>
+        <v>562676</v>
       </c>
       <c r="R63" t="n">
-        <v>7039744</v>
+        <v>7039760</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7531,24 +7590,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7563,22 +7607,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122425703</v>
+        <v>122426351</v>
       </c>
       <c r="B64" t="n">
-        <v>57399</v>
+        <v>57384</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7591,16 +7635,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7611,7 +7655,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7620,13 +7664,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562654</v>
+        <v>562771</v>
       </c>
       <c r="R64" t="n">
-        <v>7039819</v>
+        <v>7039744</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7653,9 +7697,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7670,22 +7729,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122427459</v>
+        <v>122429000</v>
       </c>
       <c r="B65" t="n">
-        <v>98240</v>
+        <v>79738</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7694,52 +7753,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562755</v>
+        <v>562984</v>
       </c>
       <c r="R65" t="n">
-        <v>7039631</v>
+        <v>7039447</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7771,7 +7816,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7781,7 +7826,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7808,10 +7853,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122429819</v>
+        <v>122425536</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7824,21 +7869,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7848,13 +7893,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562600</v>
+        <v>562710</v>
       </c>
       <c r="R66" t="n">
-        <v>7039877</v>
+        <v>7039834</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7881,9 +7926,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7898,22 +7953,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122426187</v>
+        <v>122426080</v>
       </c>
       <c r="B67" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7950,10 +8005,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562759</v>
+        <v>562743</v>
       </c>
       <c r="R67" t="n">
-        <v>7039787</v>
+        <v>7039807</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7985,7 +8040,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7995,7 +8050,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8022,10 +8077,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122425310</v>
+        <v>122425539</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8038,21 +8093,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8062,13 +8117,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562650</v>
+        <v>562651</v>
       </c>
       <c r="R68" t="n">
-        <v>7039868</v>
+        <v>7039827</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8095,19 +8150,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8122,22 +8167,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122427605</v>
+        <v>122426422</v>
       </c>
       <c r="B69" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8170,7 +8215,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8179,10 +8224,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562687</v>
+        <v>562642</v>
       </c>
       <c r="R69" t="n">
-        <v>7039594</v>
+        <v>7039716</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8214,7 +8259,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8224,12 +8269,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8244,22 +8289,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122427407</v>
+        <v>122425754</v>
       </c>
       <c r="B70" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8272,16 +8317,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8292,7 +8337,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8301,13 +8346,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562761</v>
+        <v>562652</v>
       </c>
       <c r="R70" t="n">
-        <v>7039655</v>
+        <v>7039805</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8334,24 +8379,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8366,22 +8401,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122427418</v>
+        <v>122429005</v>
       </c>
       <c r="B71" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8394,34 +8429,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562680</v>
+        <v>562522</v>
       </c>
       <c r="R71" t="n">
-        <v>7039626</v>
+        <v>7039596</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8454,6 +8494,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8480,10 +8525,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122425397</v>
+        <v>122427626</v>
       </c>
       <c r="B72" t="n">
-        <v>57383</v>
+        <v>78393</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8496,39 +8541,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562662</v>
+        <v>562773</v>
       </c>
       <c r="R72" t="n">
-        <v>7039854</v>
+        <v>7039605</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8560,7 +8600,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8570,12 +8610,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8602,10 +8637,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122425700</v>
+        <v>122425328</v>
       </c>
       <c r="B73" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8618,39 +8653,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>562678</v>
       </c>
       <c r="R73" t="n">
-        <v>7039813</v>
+        <v>7039868</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8682,7 +8712,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8692,12 +8722,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8712,22 +8737,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122429998</v>
+        <v>122425617</v>
       </c>
       <c r="B74" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8740,42 +8765,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562999</v>
+        <v>562648</v>
       </c>
       <c r="R74" t="n">
-        <v>7039523</v>
+        <v>7039837</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8802,24 +8822,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8834,22 +8839,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122425754</v>
+        <v>122428124</v>
       </c>
       <c r="B75" t="n">
-        <v>57399</v>
+        <v>79738</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8862,39 +8867,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562652</v>
+        <v>562630</v>
       </c>
       <c r="R75" t="n">
-        <v>7039805</v>
+        <v>7039565</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8927,11 +8927,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8958,10 +8953,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122427824</v>
+        <v>122425703</v>
       </c>
       <c r="B76" t="n">
-        <v>79737</v>
+        <v>57400</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8974,37 +8969,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562770</v>
+        <v>562654</v>
       </c>
       <c r="R76" t="n">
-        <v>7039566</v>
+        <v>7039819</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9031,19 +9031,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9058,22 +9048,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122425328</v>
+        <v>122427605</v>
       </c>
       <c r="B77" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9086,34 +9076,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562678</v>
+        <v>562687</v>
       </c>
       <c r="R77" t="n">
-        <v>7039868</v>
+        <v>7039594</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9145,7 +9140,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9155,7 +9150,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9182,10 +9182,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122428711</v>
+        <v>122429998</v>
       </c>
       <c r="B78" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9223,14 +9223,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562889</v>
+        <v>562999</v>
       </c>
       <c r="R78" t="n">
-        <v>7039463</v>
+        <v>7039523</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -3243,10 +3243,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122430062</v>
+        <v>122425700</v>
       </c>
       <c r="B25" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3259,37 +3259,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562624</v>
+        <v>562678</v>
       </c>
       <c r="R25" t="n">
-        <v>7039856</v>
+        <v>7039813</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3316,9 +3321,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,22 +3353,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122425700</v>
+        <v>122430062</v>
       </c>
       <c r="B26" t="n">
-        <v>57384</v>
+        <v>79738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3361,42 +3381,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562678</v>
+        <v>562624</v>
       </c>
       <c r="R26" t="n">
-        <v>7039813</v>
+        <v>7039856</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3423,24 +3438,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,12 +3455,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122428307</v>
+        <v>122429996</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
+        <v>79738</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4189,39 +4189,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562557</v>
+        <v>562622</v>
       </c>
       <c r="R33" t="n">
-        <v>7039552</v>
+        <v>7039843</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4254,11 +4249,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4285,7 +4275,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122429996</v>
+        <v>122427824</v>
       </c>
       <c r="B34" t="n">
         <v>79738</v>
@@ -4325,13 +4315,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562622</v>
+        <v>562770</v>
       </c>
       <c r="R34" t="n">
-        <v>7039843</v>
+        <v>7039566</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4358,9 +4348,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,19 +4375,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122427824</v>
+        <v>122425278</v>
       </c>
       <c r="B35" t="n">
         <v>79738</v>
@@ -4423,14 +4423,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562770</v>
+        <v>562673</v>
       </c>
       <c r="R35" t="n">
-        <v>7039566</v>
+        <v>7039869</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4487,22 +4487,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122425278</v>
+        <v>122428307</v>
       </c>
       <c r="B36" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4515,37 +4515,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562673</v>
+        <v>562557</v>
       </c>
       <c r="R36" t="n">
-        <v>7039869</v>
+        <v>7039552</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4572,19 +4577,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4599,22 +4599,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122426059</v>
+        <v>122427985</v>
       </c>
       <c r="B37" t="n">
-        <v>82444</v>
+        <v>57384</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4627,37 +4627,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562673</v>
+        <v>562695</v>
       </c>
       <c r="R37" t="n">
-        <v>7039763</v>
+        <v>7039574</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4684,9 +4689,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4701,19 +4721,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122427985</v>
+        <v>122427407</v>
       </c>
       <c r="B38" t="n">
         <v>57384</v>
@@ -4758,10 +4778,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562695</v>
+        <v>562761</v>
       </c>
       <c r="R38" t="n">
-        <v>7039574</v>
+        <v>7039655</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4793,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,12 +4823,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,10 +4855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122427407</v>
+        <v>122426059</v>
       </c>
       <c r="B39" t="n">
-        <v>57384</v>
+        <v>82444</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4851,42 +4871,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562761</v>
+        <v>562673</v>
       </c>
       <c r="R39" t="n">
-        <v>7039655</v>
+        <v>7039763</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4913,24 +4928,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4945,12 +4945,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122428074</v>
+        <v>122427645</v>
       </c>
       <c r="B52" t="n">
-        <v>57384</v>
+        <v>79738</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6292,39 +6292,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562763</v>
+        <v>562693</v>
       </c>
       <c r="R52" t="n">
-        <v>7039478</v>
+        <v>7039587</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,7 +6351,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6366,12 +6361,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6386,22 +6376,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122427645</v>
+        <v>122429056</v>
       </c>
       <c r="B53" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6414,34 +6404,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562693</v>
+        <v>562996</v>
       </c>
       <c r="R53" t="n">
-        <v>7039587</v>
+        <v>7039422</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6473,7 +6468,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6478,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6498,19 +6498,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122429056</v>
+        <v>122428074</v>
       </c>
       <c r="B54" t="n">
         <v>57384</v>
@@ -6551,14 +6551,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562996</v>
+        <v>562763</v>
       </c>
       <c r="R54" t="n">
-        <v>7039422</v>
+        <v>7039478</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7293,10 +7293,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122425414</v>
+        <v>122429819</v>
       </c>
       <c r="B61" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7309,42 +7309,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562678</v>
+        <v>562600</v>
       </c>
       <c r="R61" t="n">
-        <v>7039855</v>
+        <v>7039877</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7371,24 +7366,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7403,22 +7383,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122429819</v>
+        <v>122425414</v>
       </c>
       <c r="B62" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,37 +7411,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562600</v>
+        <v>562678</v>
       </c>
       <c r="R62" t="n">
-        <v>7039877</v>
+        <v>7039855</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7488,9 +7473,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7505,12 +7505,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427401</v>
+        <v>122425617</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>79741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562674</v>
+        <v>562648</v>
       </c>
       <c r="R5" t="n">
-        <v>7039653</v>
+        <v>7039837</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425780</v>
+        <v>122427824</v>
       </c>
       <c r="B6" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562725</v>
+        <v>562770</v>
       </c>
       <c r="R6" t="n">
-        <v>7039812</v>
+        <v>7039566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lunglav på rönn</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427418</v>
+        <v>122429056</v>
       </c>
       <c r="B7" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,37 +1253,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562680</v>
+        <v>562996</v>
       </c>
       <c r="R7" t="n">
-        <v>7039626</v>
+        <v>7039422</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,9 +1315,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,19 +1347,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430183</v>
+        <v>122427985</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1389,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562911</v>
+        <v>562695</v>
       </c>
       <c r="R8" t="n">
-        <v>7039598</v>
+        <v>7039574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122428173</v>
+        <v>122426187</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,39 +1497,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562701</v>
+        <v>562759</v>
       </c>
       <c r="R9" t="n">
-        <v>7039441</v>
+        <v>7039787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122430397</v>
+        <v>122428148</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,39 +1609,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562890</v>
+        <v>562707</v>
       </c>
       <c r="R10" t="n">
-        <v>7039728</v>
+        <v>7039456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430816</v>
+        <v>122429596</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,42 +1721,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562845</v>
+        <v>562565</v>
       </c>
       <c r="R11" t="n">
-        <v>7039809</v>
+        <v>7039844</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,19 +1778,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1795,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122428645</v>
+        <v>122425397</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,37 +1823,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562509</v>
+        <v>562662</v>
       </c>
       <c r="R12" t="n">
-        <v>7039629</v>
+        <v>7039854</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,9 +1885,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122425191</v>
+        <v>122429334</v>
       </c>
       <c r="B13" t="n">
-        <v>79738</v>
+        <v>78396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,34 +1945,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562649</v>
+        <v>562497</v>
       </c>
       <c r="R13" t="n">
-        <v>7039883</v>
+        <v>7039642</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122428148</v>
+        <v>122425284</v>
       </c>
       <c r="B14" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,17 +2067,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562707</v>
+        <v>562657</v>
       </c>
       <c r="R14" t="n">
-        <v>7039456</v>
+        <v>7039870</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,19 +2104,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,22 +2121,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122425284</v>
+        <v>122425703</v>
       </c>
       <c r="B15" t="n">
-        <v>79738</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,34 +2149,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562657</v>
+        <v>562654</v>
       </c>
       <c r="R15" t="n">
-        <v>7039870</v>
+        <v>7039819</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2245,10 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122429596</v>
+        <v>122426422</v>
       </c>
       <c r="B16" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,37 +2256,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562565</v>
+        <v>562642</v>
       </c>
       <c r="R16" t="n">
-        <v>7039844</v>
+        <v>7039716</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,9 +2318,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,19 +2350,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122430274</v>
+        <v>122428692</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2392,13 +2407,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562903</v>
+        <v>562502</v>
       </c>
       <c r="R17" t="n">
-        <v>7039649</v>
+        <v>7039635</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,24 +2440,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,22 +2462,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122428711</v>
+        <v>122429855</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,42 +2490,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562889</v>
+        <v>562619</v>
       </c>
       <c r="R18" t="n">
-        <v>7039463</v>
+        <v>7039840</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2547,24 +2547,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,22 +2564,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122425544</v>
+        <v>122425331</v>
       </c>
       <c r="B19" t="n">
-        <v>78393</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,13 +2616,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562672</v>
+        <v>562650</v>
       </c>
       <c r="R19" t="n">
-        <v>7039840</v>
+        <v>7039856</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2664,19 +2649,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,22 +2666,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122425855</v>
+        <v>122428307</v>
       </c>
       <c r="B20" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2719,37 +2694,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562731</v>
+        <v>562557</v>
       </c>
       <c r="R20" t="n">
-        <v>7039827</v>
+        <v>7039552</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2776,19 +2756,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:07</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122427953</v>
+        <v>122426220</v>
       </c>
       <c r="B21" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2831,34 +2806,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562661</v>
+        <v>562671</v>
       </c>
       <c r="R21" t="n">
-        <v>7039580</v>
+        <v>7039729</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2891,6 +2871,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122429588</v>
+        <v>122427473</v>
       </c>
       <c r="B22" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,34 +2918,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562549</v>
+        <v>562684</v>
       </c>
       <c r="R22" t="n">
-        <v>7039854</v>
+        <v>7039617</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2993,6 +2983,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,10 +3014,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122427703</v>
+        <v>122425405</v>
       </c>
       <c r="B23" t="n">
-        <v>57384</v>
+        <v>74761</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3035,42 +3030,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562784</v>
+        <v>562648</v>
       </c>
       <c r="R23" t="n">
-        <v>7039590</v>
+        <v>7039865</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3097,24 +3087,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,22 +3104,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122425331</v>
+        <v>122427626</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3157,21 +3132,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3181,13 +3156,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562650</v>
+        <v>562773</v>
       </c>
       <c r="R24" t="n">
-        <v>7039856</v>
+        <v>7039605</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,9 +3189,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,22 +3216,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122425700</v>
+        <v>122428645</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3259,42 +3244,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562678</v>
+        <v>562509</v>
       </c>
       <c r="R25" t="n">
-        <v>7039813</v>
+        <v>7039629</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3321,24 +3301,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3353,22 +3318,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122430062</v>
+        <v>122429588</v>
       </c>
       <c r="B26" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3405,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562624</v>
+        <v>562549</v>
       </c>
       <c r="R26" t="n">
-        <v>7039856</v>
+        <v>7039854</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3467,7 +3432,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122430719</v>
+        <v>122428173</v>
       </c>
       <c r="B27" t="n">
         <v>57384</v>
@@ -3512,10 +3477,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562835</v>
+        <v>562701</v>
       </c>
       <c r="R27" t="n">
-        <v>7039750</v>
+        <v>7039441</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3547,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3557,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3577,19 +3542,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122428796</v>
+        <v>122428693</v>
       </c>
       <c r="B28" t="n">
         <v>57384</v>
@@ -3634,10 +3599,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563001</v>
+        <v>562933</v>
       </c>
       <c r="R28" t="n">
-        <v>7039421</v>
+        <v>7039394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3634,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3644,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3711,10 +3676,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122427459</v>
+        <v>122426080</v>
       </c>
       <c r="B29" t="n">
-        <v>98241</v>
+        <v>79741</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3723,52 +3688,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562755</v>
+        <v>562743</v>
       </c>
       <c r="R29" t="n">
-        <v>7039631</v>
+        <v>7039807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,7 +3751,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3810,7 +3761,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,22 +3776,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122429992</v>
+        <v>122425242</v>
       </c>
       <c r="B30" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3873,14 +3824,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562620</v>
+        <v>562659</v>
       </c>
       <c r="R30" t="n">
-        <v>7039839</v>
+        <v>7039871</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3939,7 +3890,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122428693</v>
+        <v>122425414</v>
       </c>
       <c r="B31" t="n">
         <v>57384</v>
@@ -3980,14 +3931,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562933</v>
+        <v>562678</v>
       </c>
       <c r="R31" t="n">
-        <v>7039394</v>
+        <v>7039855</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4019,7 +3970,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4029,7 +3980,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4061,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122425310</v>
+        <v>122427703</v>
       </c>
       <c r="B32" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4077,34 +4028,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562650</v>
+        <v>562784</v>
       </c>
       <c r="R32" t="n">
-        <v>7039868</v>
+        <v>7039590</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,7 +4092,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4146,7 +4102,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,10 +4134,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122429996</v>
+        <v>122425516</v>
       </c>
       <c r="B33" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4189,37 +4150,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562622</v>
+        <v>562706</v>
       </c>
       <c r="R33" t="n">
-        <v>7039843</v>
+        <v>7039810</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4246,9 +4212,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,22 +4244,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122427824</v>
+        <v>122425544</v>
       </c>
       <c r="B34" t="n">
-        <v>79738</v>
+        <v>78396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4291,21 +4272,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4315,10 +4296,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562770</v>
+        <v>562672</v>
       </c>
       <c r="R34" t="n">
-        <v>7039566</v>
+        <v>7039840</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4350,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,7 +4341,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4387,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122425278</v>
+        <v>122430183</v>
       </c>
       <c r="B35" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4403,34 +4384,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562673</v>
+        <v>562911</v>
       </c>
       <c r="R35" t="n">
-        <v>7039869</v>
+        <v>7039598</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4462,7 +4448,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4472,7 +4458,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4487,22 +4478,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122428307</v>
+        <v>122427459</v>
       </c>
       <c r="B36" t="n">
-        <v>57384</v>
+        <v>98244</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,31 +4502,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562557</v>
+        <v>562755</v>
       </c>
       <c r="R36" t="n">
-        <v>7039552</v>
+        <v>7039631</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4577,14 +4577,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4599,22 +4604,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122427985</v>
+        <v>122427418</v>
       </c>
       <c r="B37" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4627,42 +4632,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562695</v>
+        <v>562680</v>
       </c>
       <c r="R37" t="n">
-        <v>7039574</v>
+        <v>7039626</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4689,24 +4689,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4721,22 +4706,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122427407</v>
+        <v>122426059</v>
       </c>
       <c r="B38" t="n">
-        <v>57384</v>
+        <v>82447</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4749,42 +4734,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562761</v>
+        <v>562673</v>
       </c>
       <c r="R38" t="n">
-        <v>7039655</v>
+        <v>7039763</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4811,24 +4791,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4843,22 +4808,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122426059</v>
+        <v>122425754</v>
       </c>
       <c r="B39" t="n">
-        <v>82444</v>
+        <v>57400</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4871,34 +4836,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562673</v>
+        <v>562652</v>
       </c>
       <c r="R39" t="n">
-        <v>7039763</v>
+        <v>7039805</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4931,6 +4901,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4957,10 +4932,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122425397</v>
+        <v>122427566</v>
       </c>
       <c r="B40" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4973,42 +4948,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562662</v>
+        <v>562663</v>
       </c>
       <c r="R40" t="n">
-        <v>7039854</v>
+        <v>7039574</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5035,24 +5005,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5067,22 +5022,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122426187</v>
+        <v>122428796</v>
       </c>
       <c r="B41" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5095,34 +5050,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562759</v>
+        <v>563001</v>
       </c>
       <c r="R41" t="n">
-        <v>7039787</v>
+        <v>7039421</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5154,7 +5114,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5164,7 +5124,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5191,10 +5156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122425405</v>
+        <v>122430397</v>
       </c>
       <c r="B42" t="n">
-        <v>74758</v>
+        <v>57384</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5207,37 +5172,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562648</v>
+        <v>562890</v>
       </c>
       <c r="R42" t="n">
-        <v>7039865</v>
+        <v>7039728</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5264,9 +5234,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5281,22 +5266,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122427473</v>
+        <v>122425539</v>
       </c>
       <c r="B43" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5309,39 +5294,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562684</v>
+        <v>562651</v>
       </c>
       <c r="R43" t="n">
-        <v>7039617</v>
+        <v>7039827</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5374,11 +5354,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5405,10 +5380,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122427743</v>
+        <v>122425310</v>
       </c>
       <c r="B44" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5421,39 +5396,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562670</v>
+        <v>562650</v>
       </c>
       <c r="R44" t="n">
-        <v>7039613</v>
+        <v>7039868</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5485,7 +5455,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5495,12 +5465,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5515,12 +5480,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5530,7 +5495,7 @@
         <v>122429969</v>
       </c>
       <c r="B45" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5629,10 +5594,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122425242</v>
+        <v>122429819</v>
       </c>
       <c r="B46" t="n">
-        <v>79738</v>
+        <v>78660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5645,34 +5610,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562659</v>
+        <v>562600</v>
       </c>
       <c r="R46" t="n">
-        <v>7039871</v>
+        <v>7039877</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5731,10 +5696,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122429855</v>
+        <v>122425536</v>
       </c>
       <c r="B47" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5771,13 +5736,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562619</v>
+        <v>562710</v>
       </c>
       <c r="R47" t="n">
-        <v>7039840</v>
+        <v>7039834</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5804,9 +5769,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,22 +5796,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122429240</v>
+        <v>122427618</v>
       </c>
       <c r="B48" t="n">
-        <v>78393</v>
+        <v>57384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5849,34 +5824,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562497</v>
+        <v>562674</v>
       </c>
       <c r="R48" t="n">
-        <v>7039642</v>
+        <v>7039582</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5909,6 +5889,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5935,10 +5920,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122430036</v>
+        <v>122428034</v>
       </c>
       <c r="B49" t="n">
-        <v>79739</v>
+        <v>57537</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5951,37 +5936,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562621</v>
+        <v>562674</v>
       </c>
       <c r="R49" t="n">
-        <v>7039854</v>
+        <v>7039543</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6008,9 +6002,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,22 +6029,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122430780</v>
+        <v>122429005</v>
       </c>
       <c r="B50" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6053,16 +6057,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6073,7 +6077,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6082,13 +6086,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562903</v>
+        <v>562522</v>
       </c>
       <c r="R50" t="n">
-        <v>7039567</v>
+        <v>7039596</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6115,19 +6119,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:21</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,22 +6141,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122425516</v>
+        <v>122429000</v>
       </c>
       <c r="B51" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6170,39 +6169,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562706</v>
+        <v>562984</v>
       </c>
       <c r="R51" t="n">
-        <v>7039810</v>
+        <v>7039447</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6234,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6244,12 +6238,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6264,22 +6253,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122427645</v>
+        <v>122430062</v>
       </c>
       <c r="B52" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6316,13 +6305,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562693</v>
+        <v>562624</v>
       </c>
       <c r="R52" t="n">
-        <v>7039587</v>
+        <v>7039856</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6349,19 +6338,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,19 +6355,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122429056</v>
+        <v>122430719</v>
       </c>
       <c r="B53" t="n">
         <v>57384</v>
@@ -6429,14 +6408,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562996</v>
+        <v>562835</v>
       </c>
       <c r="R53" t="n">
-        <v>7039422</v>
+        <v>7039750</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6468,7 +6447,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6478,12 +6457,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,7 +6489,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428074</v>
+        <v>122427743</v>
       </c>
       <c r="B54" t="n">
         <v>57384</v>
@@ -6555,10 +6534,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562763</v>
+        <v>562670</v>
       </c>
       <c r="R54" t="n">
-        <v>7039478</v>
+        <v>7039613</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6590,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6600,12 +6579,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6620,22 +6599,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122427566</v>
+        <v>122430816</v>
       </c>
       <c r="B55" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6648,37 +6627,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562663</v>
+        <v>562845</v>
       </c>
       <c r="R55" t="n">
-        <v>7039574</v>
+        <v>7039809</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6705,9 +6689,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6722,22 +6716,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122430000</v>
+        <v>122428074</v>
       </c>
       <c r="B56" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6750,37 +6744,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562623</v>
+        <v>562763</v>
       </c>
       <c r="R56" t="n">
-        <v>7039843</v>
+        <v>7039478</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6807,9 +6806,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6824,22 +6838,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427618</v>
+        <v>122427401</v>
       </c>
       <c r="B57" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6852,29 +6866,24 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
@@ -6884,7 +6893,7 @@
         <v>562674</v>
       </c>
       <c r="R57" t="n">
-        <v>7039582</v>
+        <v>7039653</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6917,11 +6926,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6948,10 +6952,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122428034</v>
+        <v>122429998</v>
       </c>
       <c r="B58" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6964,43 +6968,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562674</v>
+        <v>562999</v>
       </c>
       <c r="R58" t="n">
-        <v>7039543</v>
+        <v>7039523</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7042,7 +7042,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7057,22 +7062,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122426220</v>
+        <v>122429996</v>
       </c>
       <c r="B59" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7085,39 +7090,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562671</v>
+        <v>562622</v>
       </c>
       <c r="R59" t="n">
-        <v>7039729</v>
+        <v>7039843</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7150,11 +7150,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7181,10 +7176,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122428692</v>
+        <v>122430000</v>
       </c>
       <c r="B60" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7197,39 +7192,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562502</v>
+        <v>562623</v>
       </c>
       <c r="R60" t="n">
-        <v>7039635</v>
+        <v>7039843</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7262,11 +7252,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7293,10 +7278,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122429819</v>
+        <v>122430036</v>
       </c>
       <c r="B61" t="n">
-        <v>78657</v>
+        <v>79742</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7309,21 +7294,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7333,10 +7318,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562600</v>
+        <v>562621</v>
       </c>
       <c r="R61" t="n">
-        <v>7039877</v>
+        <v>7039854</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7395,7 +7380,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122425414</v>
+        <v>122427407</v>
       </c>
       <c r="B62" t="n">
         <v>57384</v>
@@ -7440,10 +7425,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562678</v>
+        <v>562761</v>
       </c>
       <c r="R62" t="n">
-        <v>7039855</v>
+        <v>7039655</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7475,7 +7460,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7485,7 +7470,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7520,7 +7505,7 @@
         <v>122426079</v>
       </c>
       <c r="B63" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7619,10 +7604,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122426351</v>
+        <v>122428124</v>
       </c>
       <c r="B64" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7635,42 +7620,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562771</v>
+        <v>562630</v>
       </c>
       <c r="R64" t="n">
-        <v>7039744</v>
+        <v>7039565</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7697,24 +7677,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7729,22 +7694,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122429000</v>
+        <v>122429992</v>
       </c>
       <c r="B65" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7777,17 +7742,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562984</v>
+        <v>562620</v>
       </c>
       <c r="R65" t="n">
-        <v>7039447</v>
+        <v>7039839</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7814,19 +7779,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7841,22 +7796,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122425536</v>
+        <v>122426351</v>
       </c>
       <c r="B66" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7869,34 +7824,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562710</v>
+        <v>562771</v>
       </c>
       <c r="R66" t="n">
-        <v>7039834</v>
+        <v>7039744</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7928,7 +7888,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7938,7 +7898,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7965,10 +7930,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122426080</v>
+        <v>122425700</v>
       </c>
       <c r="B67" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7981,34 +7946,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562743</v>
+        <v>562678</v>
       </c>
       <c r="R67" t="n">
-        <v>7039807</v>
+        <v>7039813</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8040,7 +8010,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8050,7 +8020,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8065,22 +8040,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122425539</v>
+        <v>122430780</v>
       </c>
       <c r="B68" t="n">
-        <v>79738</v>
+        <v>57400</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8093,37 +8068,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562651</v>
+        <v>562903</v>
       </c>
       <c r="R68" t="n">
-        <v>7039827</v>
+        <v>7039567</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8150,9 +8130,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8167,19 +8157,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122426422</v>
+        <v>122430274</v>
       </c>
       <c r="B69" t="n">
         <v>57384</v>
@@ -8224,10 +8214,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562642</v>
+        <v>562903</v>
       </c>
       <c r="R69" t="n">
-        <v>7039716</v>
+        <v>7039649</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8259,7 +8249,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8269,12 +8259,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8301,10 +8291,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122425754</v>
+        <v>122425191</v>
       </c>
       <c r="B70" t="n">
-        <v>57400</v>
+        <v>79741</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8317,39 +8307,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562652</v>
+        <v>562649</v>
       </c>
       <c r="R70" t="n">
-        <v>7039805</v>
+        <v>7039883</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8382,11 +8367,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8413,10 +8393,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122429005</v>
+        <v>122427953</v>
       </c>
       <c r="B71" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8429,39 +8409,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562522</v>
+        <v>562661</v>
       </c>
       <c r="R71" t="n">
-        <v>7039596</v>
+        <v>7039580</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8494,11 +8469,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8525,10 +8495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122427626</v>
+        <v>122425278</v>
       </c>
       <c r="B72" t="n">
-        <v>78393</v>
+        <v>79741</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8541,34 +8511,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562773</v>
+        <v>562673</v>
       </c>
       <c r="R72" t="n">
-        <v>7039605</v>
+        <v>7039869</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8600,7 +8570,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8610,7 +8580,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8625,22 +8595,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122425328</v>
+        <v>122428711</v>
       </c>
       <c r="B73" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8653,34 +8623,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562678</v>
+        <v>562889</v>
       </c>
       <c r="R73" t="n">
-        <v>7039868</v>
+        <v>7039463</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8712,7 +8687,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8722,7 +8697,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8737,22 +8717,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122425617</v>
+        <v>122425780</v>
       </c>
       <c r="B74" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8789,13 +8769,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562648</v>
+        <v>562725</v>
       </c>
       <c r="R74" t="n">
-        <v>7039837</v>
+        <v>7039812</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8822,9 +8802,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8839,22 +8834,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122428124</v>
+        <v>122427645</v>
       </c>
       <c r="B75" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8891,13 +8886,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562630</v>
+        <v>562693</v>
       </c>
       <c r="R75" t="n">
-        <v>7039565</v>
+        <v>7039587</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8924,9 +8919,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8941,22 +8946,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122425703</v>
+        <v>122425328</v>
       </c>
       <c r="B76" t="n">
-        <v>57400</v>
+        <v>79741</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8969,42 +8974,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562654</v>
+        <v>562678</v>
       </c>
       <c r="R76" t="n">
-        <v>7039819</v>
+        <v>7039868</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9031,9 +9031,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9048,22 +9058,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122427605</v>
+        <v>122425855</v>
       </c>
       <c r="B77" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9076,39 +9086,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562687</v>
+        <v>562731</v>
       </c>
       <c r="R77" t="n">
-        <v>7039594</v>
+        <v>7039827</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9140,7 +9145,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9150,12 +9155,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9182,7 +9182,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122429998</v>
+        <v>122427605</v>
       </c>
       <c r="B78" t="n">
         <v>57384</v>
@@ -9223,14 +9223,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562999</v>
+        <v>562687</v>
       </c>
       <c r="R78" t="n">
-        <v>7039523</v>
+        <v>7039594</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425617</v>
+        <v>122425191</v>
       </c>
       <c r="B5" t="n">
         <v>79741</v>
@@ -1059,14 +1059,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562648</v>
+        <v>562649</v>
       </c>
       <c r="R5" t="n">
-        <v>7039837</v>
+        <v>7039883</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427824</v>
+        <v>122427626</v>
       </c>
       <c r="B6" t="n">
-        <v>79741</v>
+        <v>78396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562770</v>
+        <v>562773</v>
       </c>
       <c r="R6" t="n">
-        <v>7039566</v>
+        <v>7039605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429056</v>
+        <v>122430000</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,42 +1253,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562996</v>
+        <v>562623</v>
       </c>
       <c r="R7" t="n">
-        <v>7039422</v>
+        <v>7039843</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,24 +1310,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1327,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427985</v>
+        <v>122425539</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,42 +1355,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562695</v>
+        <v>562651</v>
       </c>
       <c r="R8" t="n">
-        <v>7039574</v>
+        <v>7039827</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,24 +1412,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1429,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122426187</v>
+        <v>122428173</v>
       </c>
       <c r="B9" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,34 +1457,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562759</v>
+        <v>562701</v>
       </c>
       <c r="R9" t="n">
-        <v>7039787</v>
+        <v>7039441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1531,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428148</v>
+        <v>122427459</v>
       </c>
       <c r="B10" t="n">
-        <v>79741</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,38 +1575,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562707</v>
+        <v>562755</v>
       </c>
       <c r="R10" t="n">
-        <v>7039456</v>
+        <v>7039631</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1677,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429596</v>
+        <v>122426059</v>
       </c>
       <c r="B11" t="n">
-        <v>79741</v>
+        <v>82447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1745,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562565</v>
+        <v>562673</v>
       </c>
       <c r="R11" t="n">
-        <v>7039844</v>
+        <v>7039763</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1807,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122425397</v>
+        <v>122429969</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,42 +1807,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562662</v>
+        <v>562604</v>
       </c>
       <c r="R12" t="n">
-        <v>7039854</v>
+        <v>7039850</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,24 +1864,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,12 +1881,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2031,7 +1995,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122425284</v>
+        <v>122430062</v>
       </c>
       <c r="B14" t="n">
         <v>79741</v>
@@ -2067,14 +2031,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562657</v>
+        <v>562624</v>
       </c>
       <c r="R14" t="n">
-        <v>7039870</v>
+        <v>7039856</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2133,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122425703</v>
+        <v>122425617</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>79741</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,39 +2113,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562654</v>
+        <v>562648</v>
       </c>
       <c r="R15" t="n">
-        <v>7039819</v>
+        <v>7039837</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2240,7 +2199,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122426422</v>
+        <v>122430719</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2276,7 +2235,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2285,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562642</v>
+        <v>562835</v>
       </c>
       <c r="R16" t="n">
-        <v>7039716</v>
+        <v>7039750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,7 +2279,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,12 +2289,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2321,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122428692</v>
+        <v>122430816</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2398,7 +2357,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2407,13 +2366,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562502</v>
+        <v>562845</v>
       </c>
       <c r="R17" t="n">
-        <v>7039635</v>
+        <v>7039809</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,14 +2399,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,22 +2426,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122429855</v>
+        <v>122426351</v>
       </c>
       <c r="B18" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,37 +2454,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562619</v>
+        <v>562771</v>
       </c>
       <c r="R18" t="n">
-        <v>7039840</v>
+        <v>7039744</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2547,9 +2516,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,22 +2548,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122425331</v>
+        <v>122425700</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,37 +2576,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562650</v>
+        <v>562678</v>
       </c>
       <c r="R19" t="n">
-        <v>7039856</v>
+        <v>7039813</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,9 +2638,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,22 +2670,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122428307</v>
+        <v>122425328</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2694,42 +2698,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562557</v>
+        <v>562678</v>
       </c>
       <c r="R20" t="n">
-        <v>7039552</v>
+        <v>7039868</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2756,14 +2755,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,22 +2782,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122426220</v>
+        <v>122429000</v>
       </c>
       <c r="B21" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,42 +2810,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562671</v>
+        <v>562984</v>
       </c>
       <c r="R21" t="n">
-        <v>7039729</v>
+        <v>7039447</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2868,14 +2867,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,22 +2894,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427473</v>
+        <v>122430036</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
+        <v>79742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2918,39 +2922,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562684</v>
+        <v>562621</v>
       </c>
       <c r="R22" t="n">
-        <v>7039617</v>
+        <v>7039854</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2983,11 +2982,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3014,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122425405</v>
+        <v>122427703</v>
       </c>
       <c r="B23" t="n">
-        <v>74761</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3030,37 +3024,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562648</v>
+        <v>562784</v>
       </c>
       <c r="R23" t="n">
-        <v>7039865</v>
+        <v>7039590</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3087,9 +3086,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,22 +3118,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122427626</v>
+        <v>122425414</v>
       </c>
       <c r="B24" t="n">
-        <v>78396</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3132,34 +3146,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562773</v>
+        <v>562678</v>
       </c>
       <c r="R24" t="n">
-        <v>7039605</v>
+        <v>7039855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3191,7 +3210,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3201,7 +3220,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,22 +3240,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122428645</v>
+        <v>122429998</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3244,37 +3268,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562509</v>
+        <v>562999</v>
       </c>
       <c r="R25" t="n">
-        <v>7039629</v>
+        <v>7039523</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3301,9 +3330,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,19 +3362,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122429588</v>
+        <v>122429996</v>
       </c>
       <c r="B26" t="n">
         <v>79741</v>
@@ -3370,10 +3414,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562549</v>
+        <v>562622</v>
       </c>
       <c r="R26" t="n">
-        <v>7039854</v>
+        <v>7039843</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3432,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122428173</v>
+        <v>122426079</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3448,42 +3492,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562701</v>
+        <v>562676</v>
       </c>
       <c r="R27" t="n">
-        <v>7039441</v>
+        <v>7039760</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3510,24 +3549,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,22 +3566,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122428693</v>
+        <v>122425278</v>
       </c>
       <c r="B28" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3570,39 +3594,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562933</v>
+        <v>562673</v>
       </c>
       <c r="R28" t="n">
-        <v>7039394</v>
+        <v>7039869</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3634,7 +3653,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3644,12 +3663,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3676,10 +3690,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122426080</v>
+        <v>122425405</v>
       </c>
       <c r="B29" t="n">
-        <v>79741</v>
+        <v>74761</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3692,21 +3706,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3716,13 +3730,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562743</v>
+        <v>562648</v>
       </c>
       <c r="R29" t="n">
-        <v>7039807</v>
+        <v>7039865</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3749,19 +3763,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3776,19 +3780,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122425242</v>
+        <v>122427645</v>
       </c>
       <c r="B30" t="n">
         <v>79741</v>
@@ -3824,17 +3828,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562659</v>
+        <v>562693</v>
       </c>
       <c r="R30" t="n">
-        <v>7039871</v>
+        <v>7039587</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3861,9 +3865,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,19 +3892,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122425414</v>
+        <v>122430274</v>
       </c>
       <c r="B31" t="n">
         <v>57384</v>
@@ -3926,7 +3940,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3935,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562678</v>
+        <v>562903</v>
       </c>
       <c r="R31" t="n">
-        <v>7039855</v>
+        <v>7039649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3970,7 +3984,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3980,7 +3994,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4000,22 +4014,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122427703</v>
+        <v>122425703</v>
       </c>
       <c r="B32" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4028,16 +4042,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4048,7 +4062,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4057,13 +4071,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562784</v>
+        <v>562654</v>
       </c>
       <c r="R32" t="n">
-        <v>7039590</v>
+        <v>7039819</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4090,24 +4104,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,22 +4121,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122425516</v>
+        <v>122429992</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4150,42 +4149,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562706</v>
+        <v>562620</v>
       </c>
       <c r="R33" t="n">
-        <v>7039810</v>
+        <v>7039839</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4212,24 +4206,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4244,22 +4223,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122425544</v>
+        <v>122429855</v>
       </c>
       <c r="B34" t="n">
-        <v>78396</v>
+        <v>79741</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,21 +4251,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4296,13 +4275,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562672</v>
+        <v>562619</v>
       </c>
       <c r="R34" t="n">
         <v>7039840</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4329,19 +4308,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,22 +4325,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122430183</v>
+        <v>122427824</v>
       </c>
       <c r="B35" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4384,39 +4353,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562911</v>
+        <v>562770</v>
       </c>
       <c r="R35" t="n">
-        <v>7039598</v>
+        <v>7039566</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4448,7 +4412,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4458,12 +4422,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4449,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122427459</v>
+        <v>122429588</v>
       </c>
       <c r="B36" t="n">
-        <v>98244</v>
+        <v>79741</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4502,55 +4461,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562755</v>
+        <v>562549</v>
       </c>
       <c r="R36" t="n">
-        <v>7039631</v>
+        <v>7039854</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4577,19 +4522,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,22 +4539,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122427418</v>
+        <v>122426422</v>
       </c>
       <c r="B37" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4632,37 +4567,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562680</v>
+        <v>562642</v>
       </c>
       <c r="R37" t="n">
-        <v>7039626</v>
+        <v>7039716</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4689,9 +4629,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, ca 3m ovanför ett bohål</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4706,22 +4661,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122426059</v>
+        <v>122430780</v>
       </c>
       <c r="B38" t="n">
-        <v>82447</v>
+        <v>57400</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4734,37 +4689,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562673</v>
+        <v>562903</v>
       </c>
       <c r="R38" t="n">
-        <v>7039763</v>
+        <v>7039567</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4791,9 +4751,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4808,22 +4778,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425754</v>
+        <v>122425516</v>
       </c>
       <c r="B39" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4836,16 +4806,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4856,7 +4826,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4865,13 +4835,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562652</v>
+        <v>562706</v>
       </c>
       <c r="R39" t="n">
-        <v>7039805</v>
+        <v>7039810</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4898,14 +4868,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4920,22 +4900,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122427566</v>
+        <v>122428796</v>
       </c>
       <c r="B40" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4948,37 +4928,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562663</v>
+        <v>563001</v>
       </c>
       <c r="R40" t="n">
-        <v>7039574</v>
+        <v>7039421</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5005,9 +4990,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5022,22 +5022,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122428796</v>
+        <v>122428645</v>
       </c>
       <c r="B41" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5050,42 +5050,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563001</v>
+        <v>562509</v>
       </c>
       <c r="R41" t="n">
-        <v>7039421</v>
+        <v>7039629</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5112,24 +5107,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5144,22 +5124,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122430397</v>
+        <v>122429596</v>
       </c>
       <c r="B42" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,42 +5152,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562890</v>
+        <v>562565</v>
       </c>
       <c r="R42" t="n">
-        <v>7039728</v>
+        <v>7039844</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5234,24 +5209,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5266,19 +5226,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122425539</v>
+        <v>122428124</v>
       </c>
       <c r="B43" t="n">
         <v>79741</v>
@@ -5318,10 +5278,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562651</v>
+        <v>562630</v>
       </c>
       <c r="R43" t="n">
-        <v>7039827</v>
+        <v>7039565</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5380,10 +5340,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122425310</v>
+        <v>122429056</v>
       </c>
       <c r="B44" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5396,34 +5356,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562650</v>
+        <v>562996</v>
       </c>
       <c r="R44" t="n">
-        <v>7039868</v>
+        <v>7039422</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,7 +5420,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5465,7 +5430,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,10 +5462,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122429969</v>
+        <v>122425780</v>
       </c>
       <c r="B45" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5508,21 +5478,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5532,13 +5502,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562604</v>
+        <v>562725</v>
       </c>
       <c r="R45" t="n">
-        <v>7039850</v>
+        <v>7039812</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5565,9 +5535,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lunglav på rönn</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5582,22 +5567,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122429819</v>
+        <v>122425284</v>
       </c>
       <c r="B46" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5610,34 +5595,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562600</v>
+        <v>562657</v>
       </c>
       <c r="R46" t="n">
-        <v>7039877</v>
+        <v>7039870</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5696,10 +5681,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122425536</v>
+        <v>122425754</v>
       </c>
       <c r="B47" t="n">
-        <v>79741</v>
+        <v>57400</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5712,37 +5697,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562710</v>
+        <v>562652</v>
       </c>
       <c r="R47" t="n">
-        <v>7039834</v>
+        <v>7039805</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5769,19 +5759,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:56</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5796,19 +5781,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122427618</v>
+        <v>122425397</v>
       </c>
       <c r="B48" t="n">
         <v>57384</v>
@@ -5853,13 +5838,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562674</v>
+        <v>562662</v>
       </c>
       <c r="R48" t="n">
-        <v>7039582</v>
+        <v>7039854</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5886,14 +5871,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5908,22 +5903,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122428034</v>
+        <v>122428692</v>
       </c>
       <c r="B49" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5936,31 +5931,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5969,13 +5960,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562674</v>
+        <v>562502</v>
       </c>
       <c r="R49" t="n">
-        <v>7039543</v>
+        <v>7039635</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6002,19 +5993,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6029,19 +6015,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122429005</v>
+        <v>122427407</v>
       </c>
       <c r="B50" t="n">
         <v>57384</v>
@@ -6077,7 +6063,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6086,13 +6072,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562522</v>
+        <v>562761</v>
       </c>
       <c r="R50" t="n">
-        <v>7039596</v>
+        <v>7039655</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6119,14 +6105,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6141,19 +6137,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122429000</v>
+        <v>122425242</v>
       </c>
       <c r="B51" t="n">
         <v>79741</v>
@@ -6189,17 +6185,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562984</v>
+        <v>562659</v>
       </c>
       <c r="R51" t="n">
-        <v>7039447</v>
+        <v>7039871</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6226,19 +6222,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6253,22 +6239,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122430062</v>
+        <v>122427743</v>
       </c>
       <c r="B52" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6281,37 +6267,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562624</v>
+        <v>562670</v>
       </c>
       <c r="R52" t="n">
-        <v>7039856</v>
+        <v>7039613</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6338,9 +6329,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6355,19 +6361,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122430719</v>
+        <v>122427605</v>
       </c>
       <c r="B53" t="n">
         <v>57384</v>
@@ -6412,10 +6418,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562835</v>
+        <v>562687</v>
       </c>
       <c r="R53" t="n">
-        <v>7039750</v>
+        <v>7039594</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,7 +6453,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6457,7 +6463,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6477,19 +6483,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122427743</v>
+        <v>122428074</v>
       </c>
       <c r="B54" t="n">
         <v>57384</v>
@@ -6534,10 +6540,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562670</v>
+        <v>562763</v>
       </c>
       <c r="R54" t="n">
-        <v>7039613</v>
+        <v>7039478</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6575,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,12 +6585,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,19 +6605,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122430816</v>
+        <v>122428307</v>
       </c>
       <c r="B55" t="n">
         <v>57384</v>
@@ -6656,13 +6662,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562845</v>
+        <v>562557</v>
       </c>
       <c r="R55" t="n">
-        <v>7039809</v>
+        <v>7039552</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6689,19 +6695,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:15</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6716,19 +6717,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122428074</v>
+        <v>122426220</v>
       </c>
       <c r="B56" t="n">
         <v>57384</v>
@@ -6773,13 +6774,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562763</v>
+        <v>562671</v>
       </c>
       <c r="R56" t="n">
-        <v>7039478</v>
+        <v>7039729</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6806,24 +6807,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6838,22 +6829,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122427401</v>
+        <v>122425536</v>
       </c>
       <c r="B57" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6866,21 +6857,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6890,13 +6881,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562674</v>
+        <v>562710</v>
       </c>
       <c r="R57" t="n">
-        <v>7039653</v>
+        <v>7039834</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6923,9 +6914,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6940,22 +6941,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122429998</v>
+        <v>122425310</v>
       </c>
       <c r="B58" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6968,39 +6969,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562999</v>
+        <v>562650</v>
       </c>
       <c r="R58" t="n">
-        <v>7039523</v>
+        <v>7039868</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7032,7 +7028,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7042,12 +7038,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7074,7 +7065,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122429996</v>
+        <v>122427418</v>
       </c>
       <c r="B59" t="n">
         <v>79741</v>
@@ -7114,10 +7105,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562622</v>
+        <v>562680</v>
       </c>
       <c r="R59" t="n">
-        <v>7039843</v>
+        <v>7039626</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7176,7 +7167,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122430000</v>
+        <v>122426080</v>
       </c>
       <c r="B60" t="n">
         <v>79741</v>
@@ -7216,13 +7207,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562623</v>
+        <v>562743</v>
       </c>
       <c r="R60" t="n">
-        <v>7039843</v>
+        <v>7039807</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7249,9 +7240,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7266,22 +7267,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122430036</v>
+        <v>122428148</v>
       </c>
       <c r="B61" t="n">
-        <v>79742</v>
+        <v>79741</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7294,21 +7295,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7318,13 +7319,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562621</v>
+        <v>562707</v>
       </c>
       <c r="R61" t="n">
-        <v>7039854</v>
+        <v>7039456</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,9 +7352,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7368,19 +7379,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427407</v>
+        <v>122427473</v>
       </c>
       <c r="B62" t="n">
         <v>57384</v>
@@ -7416,7 +7427,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7425,13 +7436,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562761</v>
+        <v>562684</v>
       </c>
       <c r="R62" t="n">
-        <v>7039655</v>
+        <v>7039617</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7458,24 +7469,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7490,22 +7491,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122426079</v>
+        <v>122428693</v>
       </c>
       <c r="B63" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7518,37 +7519,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562676</v>
+        <v>562933</v>
       </c>
       <c r="R63" t="n">
-        <v>7039760</v>
+        <v>7039394</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7575,9 +7581,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7592,22 +7613,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122428124</v>
+        <v>122427985</v>
       </c>
       <c r="B64" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7620,37 +7641,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562630</v>
+        <v>562695</v>
       </c>
       <c r="R64" t="n">
-        <v>7039565</v>
+        <v>7039574</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7677,9 +7703,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7694,22 +7735,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122429992</v>
+        <v>122428034</v>
       </c>
       <c r="B65" t="n">
-        <v>79741</v>
+        <v>57537</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7722,37 +7763,46 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562620</v>
+        <v>562674</v>
       </c>
       <c r="R65" t="n">
-        <v>7039839</v>
+        <v>7039543</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7779,9 +7829,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7796,19 +7856,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122426351</v>
+        <v>122427618</v>
       </c>
       <c r="B66" t="n">
         <v>57384</v>
@@ -7853,13 +7913,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562771</v>
+        <v>562674</v>
       </c>
       <c r="R66" t="n">
-        <v>7039744</v>
+        <v>7039582</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7886,24 +7946,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7918,19 +7968,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122425700</v>
+        <v>122430397</v>
       </c>
       <c r="B67" t="n">
         <v>57384</v>
@@ -7966,7 +8016,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7975,10 +8025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562678</v>
+        <v>562890</v>
       </c>
       <c r="R67" t="n">
-        <v>7039813</v>
+        <v>7039728</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8010,7 +8060,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8020,12 +8070,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8052,10 +8102,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122430780</v>
+        <v>122430183</v>
       </c>
       <c r="B68" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8068,16 +8118,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8097,10 +8147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562903</v>
+        <v>562911</v>
       </c>
       <c r="R68" t="n">
-        <v>7039567</v>
+        <v>7039598</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8132,7 +8182,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8142,7 +8192,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8157,19 +8212,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122430274</v>
+        <v>122428711</v>
       </c>
       <c r="B69" t="n">
         <v>57384</v>
@@ -8205,7 +8260,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8214,10 +8269,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562903</v>
+        <v>562889</v>
       </c>
       <c r="R69" t="n">
-        <v>7039649</v>
+        <v>7039463</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8249,7 +8304,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8259,12 +8314,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8291,7 +8346,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122425191</v>
+        <v>122427953</v>
       </c>
       <c r="B70" t="n">
         <v>79741</v>
@@ -8327,14 +8382,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562649</v>
+        <v>562661</v>
       </c>
       <c r="R70" t="n">
-        <v>7039883</v>
+        <v>7039580</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8393,10 +8448,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122427953</v>
+        <v>122425544</v>
       </c>
       <c r="B71" t="n">
-        <v>79741</v>
+        <v>78396</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8409,21 +8464,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8433,13 +8488,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562661</v>
+        <v>562672</v>
       </c>
       <c r="R71" t="n">
-        <v>7039580</v>
+        <v>7039840</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8466,9 +8521,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8483,22 +8548,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122425278</v>
+        <v>122425331</v>
       </c>
       <c r="B72" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8511,37 +8576,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562673</v>
+        <v>562650</v>
       </c>
       <c r="R72" t="n">
-        <v>7039869</v>
+        <v>7039856</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8568,19 +8633,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8595,22 +8650,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122428711</v>
+        <v>122427566</v>
       </c>
       <c r="B73" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8623,42 +8678,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562889</v>
+        <v>562663</v>
       </c>
       <c r="R73" t="n">
-        <v>7039463</v>
+        <v>7039574</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8685,24 +8735,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8717,22 +8752,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122425780</v>
+        <v>122429005</v>
       </c>
       <c r="B74" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8745,37 +8780,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562725</v>
+        <v>562522</v>
       </c>
       <c r="R74" t="n">
-        <v>7039812</v>
+        <v>7039596</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8802,24 +8842,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Lunglav på rönn</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8834,22 +8864,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122427645</v>
+        <v>122429819</v>
       </c>
       <c r="B75" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8862,21 +8892,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8886,13 +8916,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562693</v>
+        <v>562600</v>
       </c>
       <c r="R75" t="n">
-        <v>7039587</v>
+        <v>7039877</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8919,19 +8949,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8946,19 +8966,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122425328</v>
+        <v>122426187</v>
       </c>
       <c r="B76" t="n">
         <v>79741</v>
@@ -8994,14 +9014,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562678</v>
+        <v>562759</v>
       </c>
       <c r="R76" t="n">
-        <v>7039868</v>
+        <v>7039787</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9033,7 +9053,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9043,7 +9063,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9182,10 +9202,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122427605</v>
+        <v>122427401</v>
       </c>
       <c r="B78" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9198,42 +9218,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562687</v>
+        <v>562674</v>
       </c>
       <c r="R78" t="n">
-        <v>7039594</v>
+        <v>7039653</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9260,24 +9275,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9292,12 +9292,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -3904,10 +3904,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122430274</v>
+        <v>122425703</v>
       </c>
       <c r="B31" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562903</v>
+        <v>562654</v>
       </c>
       <c r="R31" t="n">
-        <v>7039649</v>
+        <v>7039819</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3982,24 +3982,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,22 +3999,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122425703</v>
+        <v>122430274</v>
       </c>
       <c r="B32" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4042,16 +4027,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4071,13 +4056,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562654</v>
+        <v>562903</v>
       </c>
       <c r="R32" t="n">
-        <v>7039819</v>
+        <v>7039649</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4104,9 +4089,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4121,12 +4121,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122425242</v>
+        <v>122427743</v>
       </c>
       <c r="B51" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6165,37 +6165,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Håsjöån, Håsjöån, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562659</v>
+        <v>562670</v>
       </c>
       <c r="R51" t="n">
-        <v>7039871</v>
+        <v>7039613</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6222,9 +6227,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6239,19 +6259,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122427743</v>
+        <v>122427605</v>
       </c>
       <c r="B52" t="n">
         <v>57384</v>
@@ -6296,10 +6316,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562670</v>
+        <v>562687</v>
       </c>
       <c r="R52" t="n">
-        <v>7039613</v>
+        <v>7039594</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6331,7 +6351,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6341,12 +6361,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6373,7 +6393,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122427605</v>
+        <v>122428074</v>
       </c>
       <c r="B53" t="n">
         <v>57384</v>
@@ -6418,10 +6438,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562687</v>
+        <v>562763</v>
       </c>
       <c r="R53" t="n">
-        <v>7039594</v>
+        <v>7039478</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6463,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6483,22 +6503,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122428074</v>
+        <v>122425242</v>
       </c>
       <c r="B54" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6511,42 +6531,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562763</v>
+        <v>562659</v>
       </c>
       <c r="R54" t="n">
-        <v>7039478</v>
+        <v>7039871</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6573,24 +6588,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6605,22 +6605,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122428307</v>
+        <v>122425536</v>
       </c>
       <c r="B55" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6633,42 +6633,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562557</v>
+        <v>562710</v>
       </c>
       <c r="R55" t="n">
-        <v>7039552</v>
+        <v>7039834</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6695,14 +6690,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6717,22 +6717,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122426220</v>
+        <v>122425310</v>
       </c>
       <c r="B56" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6745,42 +6745,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562671</v>
+        <v>562650</v>
       </c>
       <c r="R56" t="n">
-        <v>7039729</v>
+        <v>7039868</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6807,14 +6802,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gammeltall</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6829,22 +6829,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122425536</v>
+        <v>122428307</v>
       </c>
       <c r="B57" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6857,37 +6857,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562710</v>
+        <v>562557</v>
       </c>
       <c r="R57" t="n">
-        <v>7039834</v>
+        <v>7039552</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6914,19 +6919,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:56</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:56</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6941,22 +6941,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122425310</v>
+        <v>122426220</v>
       </c>
       <c r="B58" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6969,37 +6969,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562650</v>
+        <v>562671</v>
       </c>
       <c r="R58" t="n">
-        <v>7039868</v>
+        <v>7039729</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7026,19 +7031,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:45</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7053,22 +7053,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122427418</v>
+        <v>122428034</v>
       </c>
       <c r="B59" t="n">
-        <v>79741</v>
+        <v>57537</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7081,37 +7081,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562680</v>
+        <v>562674</v>
       </c>
       <c r="R59" t="n">
-        <v>7039626</v>
+        <v>7039543</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7138,9 +7147,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7155,22 +7174,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122426080</v>
+        <v>122427473</v>
       </c>
       <c r="B60" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7183,37 +7202,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562743</v>
+        <v>562684</v>
       </c>
       <c r="R60" t="n">
-        <v>7039807</v>
+        <v>7039617</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7240,19 +7264,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:16</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7267,22 +7286,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122428148</v>
+        <v>122428693</v>
       </c>
       <c r="B61" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7295,34 +7314,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562707</v>
+        <v>562933</v>
       </c>
       <c r="R61" t="n">
-        <v>7039456</v>
+        <v>7039394</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7354,7 +7378,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7364,7 +7388,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7391,7 +7420,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122427473</v>
+        <v>122427985</v>
       </c>
       <c r="B62" t="n">
         <v>57384</v>
@@ -7427,7 +7456,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7436,13 +7465,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562684</v>
+        <v>562695</v>
       </c>
       <c r="R62" t="n">
-        <v>7039617</v>
+        <v>7039574</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7469,14 +7498,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7491,22 +7530,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122428693</v>
+        <v>122427418</v>
       </c>
       <c r="B63" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7519,42 +7558,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562933</v>
+        <v>562680</v>
       </c>
       <c r="R63" t="n">
-        <v>7039394</v>
+        <v>7039626</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7581,24 +7615,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7613,22 +7632,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122427985</v>
+        <v>122426080</v>
       </c>
       <c r="B64" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7641,39 +7660,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562695</v>
+        <v>562743</v>
       </c>
       <c r="R64" t="n">
-        <v>7039574</v>
+        <v>7039807</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7705,7 +7719,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,12 +7729,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7747,10 +7756,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122428034</v>
+        <v>122428148</v>
       </c>
       <c r="B65" t="n">
-        <v>57537</v>
+        <v>79741</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7763,43 +7772,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562674</v>
+        <v>562707</v>
       </c>
       <c r="R65" t="n">
-        <v>7039543</v>
+        <v>7039456</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122430183</v>
+        <v>122427953</v>
       </c>
       <c r="B68" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8118,42 +8118,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562911</v>
+        <v>562661</v>
       </c>
       <c r="R68" t="n">
-        <v>7039598</v>
+        <v>7039580</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8180,24 +8175,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8212,22 +8192,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122428711</v>
+        <v>122425544</v>
       </c>
       <c r="B69" t="n">
-        <v>57384</v>
+        <v>78396</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8240,39 +8220,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562889</v>
+        <v>562672</v>
       </c>
       <c r="R69" t="n">
-        <v>7039463</v>
+        <v>7039840</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8304,7 +8279,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8314,12 +8289,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8346,10 +8316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122427953</v>
+        <v>122425331</v>
       </c>
       <c r="B70" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8362,21 +8332,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8386,10 +8356,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562661</v>
+        <v>562650</v>
       </c>
       <c r="R70" t="n">
-        <v>7039580</v>
+        <v>7039856</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8448,10 +8418,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122425544</v>
+        <v>122430183</v>
       </c>
       <c r="B71" t="n">
-        <v>78396</v>
+        <v>57384</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8464,34 +8434,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562672</v>
+        <v>562911</v>
       </c>
       <c r="R71" t="n">
-        <v>7039840</v>
+        <v>7039598</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8523,7 +8498,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8533,7 +8508,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8560,10 +8540,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122425331</v>
+        <v>122428711</v>
       </c>
       <c r="B72" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8576,37 +8556,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562650</v>
+        <v>562889</v>
       </c>
       <c r="R72" t="n">
-        <v>7039856</v>
+        <v>7039463</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8633,9 +8618,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8650,12 +8650,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -5915,10 +5915,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122425516</v>
+        <v>122429992</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5931,42 +5931,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562706</v>
+        <v>562620</v>
       </c>
       <c r="R49" t="n">
-        <v>7039810</v>
+        <v>7039839</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5993,24 +5988,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,19 +6005,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122429992</v>
+        <v>122429855</v>
       </c>
       <c r="B50" t="n">
         <v>79843</v>
@@ -6077,10 +6057,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562620</v>
+        <v>562619</v>
       </c>
       <c r="R50" t="n">
-        <v>7039839</v>
+        <v>7039840</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6139,10 +6119,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122429855</v>
+        <v>122425516</v>
       </c>
       <c r="B51" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6155,37 +6135,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562619</v>
+        <v>562706</v>
       </c>
       <c r="R51" t="n">
-        <v>7039840</v>
+        <v>7039810</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6212,9 +6197,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6229,12 +6229,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -8500,10 +8500,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122427566</v>
+        <v>122430719</v>
       </c>
       <c r="B72" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8516,37 +8516,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562663</v>
+        <v>562835</v>
       </c>
       <c r="R72" t="n">
-        <v>7039574</v>
+        <v>7039750</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8573,9 +8578,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8590,22 +8610,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122425754</v>
+        <v>122429056</v>
       </c>
       <c r="B73" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8618,16 +8638,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8638,22 +8658,22 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562652</v>
+        <v>562996</v>
       </c>
       <c r="R73" t="n">
-        <v>7039805</v>
+        <v>7039422</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8680,14 +8700,24 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Stor bohål i aso</t>
+          <t>Ringhack på tall, 6 m upp</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8702,22 +8732,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122430719</v>
+        <v>122427566</v>
       </c>
       <c r="B74" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8730,42 +8760,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562835</v>
+        <v>562663</v>
       </c>
       <c r="R74" t="n">
-        <v>7039750</v>
+        <v>7039574</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8792,24 +8817,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8824,22 +8834,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122429056</v>
+        <v>122425754</v>
       </c>
       <c r="B75" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8852,16 +8862,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8872,22 +8882,22 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562996</v>
+        <v>562652</v>
       </c>
       <c r="R75" t="n">
-        <v>7039422</v>
+        <v>7039805</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8914,24 +8924,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall, 6 m upp</t>
+          <t>Stor bohål i aso</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8946,12 +8946,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 46041-2022 artfynd.xlsx
+++ b/artfynd/A 46041-2022 artfynd.xlsx
@@ -2907,10 +2907,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122427473</v>
+        <v>122428148</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2923,42 +2923,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562684</v>
+        <v>562707</v>
       </c>
       <c r="R22" t="n">
-        <v>7039617</v>
+        <v>7039456</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,14 +2980,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,22 +3007,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122428148</v>
+        <v>122427473</v>
       </c>
       <c r="B23" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3035,37 +3035,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562707</v>
+        <v>562684</v>
       </c>
       <c r="R23" t="n">
-        <v>7039456</v>
+        <v>7039617</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3092,19 +3097,14 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:35</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,12 +3119,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122430000</v>
+        <v>122430780</v>
       </c>
       <c r="B34" t="n">
-        <v>79843</v>
+        <v>57494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4296,37 +4296,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562623</v>
+        <v>562903</v>
       </c>
       <c r="R34" t="n">
-        <v>7039843</v>
+        <v>7039567</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4353,9 +4358,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4370,19 +4385,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122427824</v>
+        <v>122430000</v>
       </c>
       <c r="B35" t="n">
         <v>79843</v>
@@ -4422,13 +4437,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562770</v>
+        <v>562623</v>
       </c>
       <c r="R35" t="n">
-        <v>7039566</v>
+      